--- a/src/sheet.xlsx
+++ b/src/sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/604ea001471daaea/Desktop/snuts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3885" documentId="11_23E5F1B2D340D77CEF592311595ED87656DCBE2C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FA89F73-092E-4EC4-8209-7D312D78ED84}"/>
+  <xr:revisionPtr revIDLastSave="3886" documentId="11_23E5F1B2D340D77CEF592311595ED87656DCBE2C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA0CCDEB-6512-4AD5-9D03-FE1832D64E57}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4015,9 +4015,6 @@
     <t>Nova</t>
   </si>
   <si>
-    <t>You call forth spirits to protect you. They flit around you to a distance of 15 feet for the duration. If you are good or neutral, their spectral form appears angelic or fey (your choice). If you are evil, they appear fiendish. When you cast this glyph, you can designate any number of creatures you can see to be unaffected by it. An affected creature's speed is halved in the area, and when the creature enters the area for the first time on a turn or starts its turn there, it must make a wits saving throw. On a failed save, the creature takes 3d8 radiant damage (if you are good or neutral) or 3d8 necrotic damage (if you are evil). On a successful save, the creature takes half as much damage.</t>
-  </si>
-  <si>
     <t>Nysh's Horrid Wilting</t>
   </si>
   <si>
@@ -5672,6 +5669,9 @@
   </si>
   <si>
     <t xml:space="preserve">At Higher Mana Cost: You can expend extra mana to increase the effects of the glyph, you can concentrate on this glyph for an additional 2 hours for every 3 additional mana expended. If you expend at least 27 Mana, the glyph becomes permanent. </t>
+  </si>
+  <si>
+    <t>You turn your Wellspring outwards, bombarding creatures in the area with your Affinity to a distance of 15 feet for the duration. When you cast this glyph, you can designate any number of creatures you can see to be unaffected by it. An affected creature's speed is halved in the area, and when the creature enters the area for the first time on a turn or starts its turn there, it must make a wits saving throw. On a failed save, the creature takes 3d8 damage of your Affinity's type. On a successful save, the creature takes half as much damage.</t>
   </si>
 </sst>
 </file>
@@ -24655,7 +24655,7 @@
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
     </row>
-    <row r="436" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" s="2" t="s">
         <v>1190</v>
       </c>
@@ -24690,7 +24690,7 @@
         <v>0</v>
       </c>
       <c r="L436" s="2" t="s">
-        <v>1191</v>
+        <v>1704</v>
       </c>
       <c r="M436" s="2" t="s">
         <v>1011</v>
@@ -24701,7 +24701,7 @@
     </row>
     <row r="437" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B437" s="2">
         <v>10</v>
@@ -24734,14 +24734,14 @@
         <v>0</v>
       </c>
       <c r="L437" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="M437" s="2"/>
       <c r="N437" s="2"/>
     </row>
     <row r="438" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B438" s="2">
         <v>5</v>
@@ -24774,14 +24774,14 @@
         <v>0</v>
       </c>
       <c r="L438" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="M438" s="2"/>
       <c r="N438" s="2"/>
     </row>
     <row r="439" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B439" s="2">
         <v>8</v>
@@ -24814,14 +24814,14 @@
         <v>0</v>
       </c>
       <c r="L439" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="M439" s="2"/>
       <c r="N439" s="2"/>
     </row>
     <row r="440" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B440" s="2">
         <v>7</v>
@@ -24854,14 +24854,14 @@
         <v>0</v>
       </c>
       <c r="L440" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="M440" s="2"/>
       <c r="N440" s="2"/>
     </row>
     <row r="441" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B441" s="2">
         <v>2</v>
@@ -24894,14 +24894,14 @@
         <v>0</v>
       </c>
       <c r="L441" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="M441" s="2"/>
       <c r="N441" s="2"/>
     </row>
     <row r="442" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B442" s="2">
         <v>6</v>
@@ -24934,14 +24934,14 @@
         <v>0</v>
       </c>
       <c r="L442" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="M442" s="2"/>
       <c r="N442" s="2"/>
     </row>
     <row r="443" spans="1:14" ht="344.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B443" s="2">
         <v>3</v>
@@ -24974,14 +24974,14 @@
         <v>0</v>
       </c>
       <c r="L443" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="M443" s="2"/>
       <c r="N443" s="2"/>
     </row>
     <row r="444" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B444" s="2">
         <v>5</v>
@@ -25014,7 +25014,7 @@
         <v>0</v>
       </c>
       <c r="L444" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="M444" s="2" t="s">
         <v>839</v>
@@ -25025,7 +25025,7 @@
     </row>
     <row r="445" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B445" s="2">
         <v>4</v>
@@ -25058,14 +25058,14 @@
         <v>1</v>
       </c>
       <c r="L445" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="M445" s="2"/>
       <c r="N445" s="2"/>
     </row>
     <row r="446" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A446" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B446" s="2">
         <v>5</v>
@@ -25098,14 +25098,14 @@
         <v>0</v>
       </c>
       <c r="L446" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="M446" s="2"/>
       <c r="N446" s="2"/>
     </row>
     <row r="447" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A447" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B447" s="2">
         <v>8</v>
@@ -25138,14 +25138,14 @@
         <v>0</v>
       </c>
       <c r="L447" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="M447" s="2"/>
       <c r="N447" s="2"/>
     </row>
     <row r="448" spans="1:14" ht="233.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B448" s="2">
         <v>6</v>
@@ -25178,18 +25178,18 @@
         <v>0</v>
       </c>
       <c r="L448" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="M448" s="2" t="s">
         <v>1215</v>
       </c>
-      <c r="M448" s="2" t="s">
-        <v>1216</v>
-      </c>
       <c r="N448" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="449" spans="1:14" ht="233.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A449" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B449" s="2">
         <v>10</v>
@@ -25222,14 +25222,14 @@
         <v>0</v>
       </c>
       <c r="L449" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="M449" s="2"/>
       <c r="N449" s="2"/>
     </row>
     <row r="450" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A450" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B450" s="2">
         <v>3</v>
@@ -25247,7 +25247,7 @@
         <v>0</v>
       </c>
       <c r="G450" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H450" s="2" t="b">
         <v>0</v>
@@ -25262,14 +25262,14 @@
         <v>0</v>
       </c>
       <c r="L450" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="M450" s="2"/>
       <c r="N450" s="2"/>
     </row>
     <row r="451" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A451" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B451" s="2">
         <v>0</v>
@@ -25302,14 +25302,14 @@
         <v>0</v>
       </c>
       <c r="L451" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M451" s="2"/>
       <c r="N451" s="2"/>
     </row>
     <row r="452" spans="1:14" ht="258.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A452" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B452" s="2">
         <v>5</v>
@@ -25342,14 +25342,14 @@
         <v>0</v>
       </c>
       <c r="L452" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="M452" s="2"/>
       <c r="N452" s="2"/>
     </row>
     <row r="453" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B453" s="2">
         <v>12</v>
@@ -25382,14 +25382,14 @@
         <v>0</v>
       </c>
       <c r="L453" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="M453" s="2"/>
       <c r="N453" s="2"/>
     </row>
     <row r="454" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A454" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B454" s="2">
         <v>12</v>
@@ -25422,14 +25422,14 @@
         <v>0</v>
       </c>
       <c r="L454" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="M454" s="2"/>
       <c r="N454" s="2"/>
     </row>
     <row r="455" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A455" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B455" s="2">
         <v>9</v>
@@ -25462,14 +25462,14 @@
         <v>0</v>
       </c>
       <c r="L455" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="M455" s="2"/>
       <c r="N455" s="2"/>
     </row>
     <row r="456" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A456" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B456" s="2">
         <v>10</v>
@@ -25502,14 +25502,14 @@
         <v>0</v>
       </c>
       <c r="L456" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="M456" s="2"/>
       <c r="N456" s="2"/>
     </row>
     <row r="457" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A457" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B457" s="2">
         <v>2</v>
@@ -25542,18 +25542,18 @@
         <v>0</v>
       </c>
       <c r="L457" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M457" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="M457" s="2" t="s">
-        <v>1236</v>
-      </c>
       <c r="N457" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="458" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A458" s="2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B458" s="2">
         <v>6</v>
@@ -25586,18 +25586,18 @@
         <v>0</v>
       </c>
       <c r="L458" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="M458" s="2" t="s">
         <v>1238</v>
       </c>
-      <c r="M458" s="2" t="s">
-        <v>1239</v>
-      </c>
       <c r="N458" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="459" spans="1:14" ht="172.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A459" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B459" s="2">
         <v>0</v>
@@ -25630,14 +25630,14 @@
         <v>0</v>
       </c>
       <c r="L459" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="M459" s="2"/>
       <c r="N459" s="2"/>
     </row>
     <row r="460" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A460" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B460" s="2">
         <v>0</v>
@@ -25670,18 +25670,18 @@
         <v>0</v>
       </c>
       <c r="L460" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="M460" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="M460" s="2" t="s">
-        <v>1244</v>
-      </c>
       <c r="N460" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="461" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A461" s="2" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B461" s="2">
         <v>1</v>
@@ -25721,7 +25721,7 @@
     </row>
     <row r="462" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" s="2" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B462" s="2">
         <v>8</v>
@@ -25754,14 +25754,14 @@
         <v>0</v>
       </c>
       <c r="L462" s="2" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="M462" s="2"/>
       <c r="N462" s="2"/>
     </row>
     <row r="463" spans="1:14" ht="332.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A463" s="2" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B463" s="2">
         <v>9</v>
@@ -25794,14 +25794,14 @@
         <v>0</v>
       </c>
       <c r="L463" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="M463" s="2"/>
       <c r="N463" s="2"/>
     </row>
     <row r="464" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B464" s="2">
         <v>12</v>
@@ -25834,14 +25834,14 @@
         <v>0</v>
       </c>
       <c r="L464" s="2" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="M464" s="2"/>
       <c r="N464" s="2"/>
     </row>
     <row r="465" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B465" s="2">
         <v>0</v>
@@ -25874,14 +25874,14 @@
         <v>0</v>
       </c>
       <c r="L465" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="M465" s="2"/>
       <c r="N465" s="2"/>
     </row>
     <row r="466" spans="1:14" ht="282.89999999999998" x14ac:dyDescent="0.55000000000000004">
       <c r="A466" s="2" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B466" s="2">
         <v>8</v>
@@ -25914,14 +25914,14 @@
         <v>0</v>
       </c>
       <c r="L466" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="M466" s="2"/>
       <c r="N466" s="2"/>
     </row>
     <row r="467" spans="1:14" ht="233.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A467" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B467" s="2">
         <v>9</v>
@@ -25948,20 +25948,20 @@
         <v>923</v>
       </c>
       <c r="J467" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K467" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L467" s="2" t="s">
         <v>1257</v>
-      </c>
-      <c r="K467" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L467" s="2" t="s">
-        <v>1258</v>
       </c>
       <c r="M467" s="2"/>
       <c r="N467" s="2"/>
     </row>
     <row r="468" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A468" s="2" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B468" s="2">
         <v>3</v>
@@ -25994,14 +25994,14 @@
         <v>0</v>
       </c>
       <c r="L468" s="2" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M468" s="2"/>
       <c r="N468" s="2"/>
     </row>
     <row r="469" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A469" s="2" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B469" s="2">
         <v>1</v>
@@ -26034,14 +26034,14 @@
         <v>0</v>
       </c>
       <c r="L469" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M469" s="2"/>
       <c r="N469" s="2"/>
     </row>
     <row r="470" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A470" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B470" s="2">
         <v>2</v>
@@ -26074,14 +26074,14 @@
         <v>0</v>
       </c>
       <c r="L470" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="M470" s="2"/>
       <c r="N470" s="2"/>
     </row>
     <row r="471" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A471" s="2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B471" s="2">
         <v>5</v>
@@ -26114,18 +26114,18 @@
         <v>0</v>
       </c>
       <c r="L471" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="M471" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="M471" s="2" t="s">
-        <v>1267</v>
-      </c>
       <c r="N471" s="2" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="472" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A472" s="2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B472" s="2">
         <v>12</v>
@@ -26158,14 +26158,14 @@
         <v>0</v>
       </c>
       <c r="L472" s="2" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="M472" s="2"/>
       <c r="N472" s="2"/>
     </row>
     <row r="473" spans="1:14" ht="196.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A473" s="2" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B473" s="2">
         <v>4</v>
@@ -26198,14 +26198,14 @@
         <v>0</v>
       </c>
       <c r="L473" s="2" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="M473" s="2"/>
       <c r="N473" s="2"/>
     </row>
     <row r="474" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A474" s="2" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B474" s="2">
         <v>4</v>
@@ -26238,18 +26238,18 @@
         <v>0</v>
       </c>
       <c r="L474" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="M474" s="2" t="s">
         <v>1273</v>
       </c>
-      <c r="M474" s="2" t="s">
-        <v>1274</v>
-      </c>
       <c r="N474" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="475" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A475" s="2" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B475" s="2">
         <v>1</v>
@@ -26282,14 +26282,14 @@
         <v>1</v>
       </c>
       <c r="L475" s="2" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="M475" s="2"/>
       <c r="N475" s="2"/>
     </row>
     <row r="476" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A476" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B476" s="2">
         <v>2</v>
@@ -26322,14 +26322,14 @@
         <v>0</v>
       </c>
       <c r="L476" s="2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="M476" s="2"/>
       <c r="N476" s="2"/>
     </row>
     <row r="477" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A477" s="2" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="B477" s="2">
         <v>1</v>
@@ -26362,18 +26362,18 @@
         <v>0</v>
       </c>
       <c r="L477" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="M477" s="2" t="s">
         <v>1703</v>
       </c>
-      <c r="M477" s="2" t="s">
-        <v>1704</v>
-      </c>
       <c r="N477" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="478" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A478" s="2" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B478" s="2">
         <v>0</v>
@@ -26406,18 +26406,18 @@
         <v>0</v>
       </c>
       <c r="L478" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M478" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="M478" s="2" t="s">
+      <c r="N478" s="2" t="s">
         <v>1282</v>
-      </c>
-      <c r="N478" s="2" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="479" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B479" s="2">
         <v>2</v>
@@ -26450,14 +26450,14 @@
         <v>0</v>
       </c>
       <c r="L479" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="M479" s="2"/>
       <c r="N479" s="2"/>
     </row>
     <row r="480" spans="1:14" ht="196.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A480" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B480" s="2">
         <v>7</v>
@@ -26490,14 +26490,14 @@
         <v>0</v>
       </c>
       <c r="L480" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="M480" s="2"/>
       <c r="N480" s="2"/>
     </row>
     <row r="481" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A481" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B481" s="2">
         <v>2</v>
@@ -26530,18 +26530,18 @@
         <v>0</v>
       </c>
       <c r="L481" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="M481" s="2" t="s">
         <v>1289</v>
       </c>
-      <c r="M481" s="2" t="s">
-        <v>1290</v>
-      </c>
       <c r="N481" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="482" spans="1:14" ht="258.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A482" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B482" s="2">
         <v>12</v>
@@ -26568,20 +26568,20 @@
         <v>117</v>
       </c>
       <c r="J482" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="K482" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L482" s="2" t="s">
         <v>1292</v>
-      </c>
-      <c r="K482" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L482" s="2" t="s">
-        <v>1293</v>
       </c>
       <c r="M482" s="2"/>
       <c r="N482" s="2"/>
     </row>
     <row r="483" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A483" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B483" s="2">
         <v>2</v>
@@ -26614,14 +26614,14 @@
         <v>0</v>
       </c>
       <c r="L483" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="M483" s="2"/>
       <c r="N483" s="2"/>
     </row>
     <row r="484" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A484" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B484" s="2">
         <v>0</v>
@@ -26654,14 +26654,14 @@
         <v>0</v>
       </c>
       <c r="L484" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="M484" s="2"/>
       <c r="N484" s="2"/>
     </row>
     <row r="485" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A485" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B485" s="2">
         <v>1</v>
@@ -26694,7 +26694,7 @@
         <v>0</v>
       </c>
       <c r="L485" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="M485" s="2" t="s">
         <v>769</v>
@@ -26705,7 +26705,7 @@
     </row>
     <row r="486" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A486" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B486" s="2">
         <v>10</v>
@@ -26738,14 +26738,14 @@
         <v>0</v>
       </c>
       <c r="L486" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="M486" s="2"/>
       <c r="N486" s="2"/>
     </row>
     <row r="487" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B487" s="2">
         <v>7</v>
@@ -26778,16 +26778,16 @@
         <v>0</v>
       </c>
       <c r="L487" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M487" s="2" t="s">
         <v>1303</v>
-      </c>
-      <c r="M487" s="2" t="s">
-        <v>1304</v>
       </c>
       <c r="N487" s="2"/>
     </row>
     <row r="488" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A488" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B488" s="2">
         <v>9</v>
@@ -26820,14 +26820,14 @@
         <v>0</v>
       </c>
       <c r="L488" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="M488" s="2"/>
       <c r="N488" s="2"/>
     </row>
     <row r="489" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A489" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B489" s="2">
         <v>5</v>
@@ -26860,18 +26860,18 @@
         <v>0</v>
       </c>
       <c r="L489" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="M489" s="2" t="s">
         <v>1308</v>
       </c>
-      <c r="M489" s="2" t="s">
+      <c r="N489" s="2" t="s">
         <v>1309</v>
-      </c>
-      <c r="N489" s="2" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="490" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A490" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B490" s="2">
         <v>7</v>
@@ -26904,14 +26904,14 @@
         <v>0</v>
       </c>
       <c r="L490" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="M490" s="2"/>
       <c r="N490" s="2"/>
     </row>
     <row r="491" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A491" s="2" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B491" s="2">
         <v>3</v>
@@ -26944,18 +26944,18 @@
         <v>0</v>
       </c>
       <c r="L491" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="M491" s="2" t="s">
         <v>1314</v>
       </c>
-      <c r="M491" s="2" t="s">
-        <v>1315</v>
-      </c>
       <c r="N491" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="492" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A492" s="2" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B492" s="2">
         <v>4</v>
@@ -26988,14 +26988,14 @@
         <v>0</v>
       </c>
       <c r="L492" s="2" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M492" s="2"/>
       <c r="N492" s="2"/>
     </row>
     <row r="493" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A493" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B493" s="2">
         <v>5</v>
@@ -27028,14 +27028,14 @@
         <v>0</v>
       </c>
       <c r="L493" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="M493" s="2"/>
       <c r="N493" s="2"/>
     </row>
     <row r="494" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A494" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B494" s="2">
         <v>0</v>
@@ -27068,14 +27068,14 @@
         <v>0</v>
       </c>
       <c r="L494" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="M494" s="2"/>
       <c r="N494" s="2"/>
     </row>
     <row r="495" spans="1:14" ht="196.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A495" s="2" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B495" s="2">
         <v>10</v>
@@ -27108,14 +27108,14 @@
         <v>0</v>
       </c>
       <c r="L495" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="M495" s="2"/>
       <c r="N495" s="2"/>
     </row>
     <row r="496" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" s="2" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B496" s="2">
         <v>9</v>
@@ -27148,14 +27148,14 @@
         <v>0</v>
       </c>
       <c r="L496" s="2" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="M496" s="2"/>
       <c r="N496" s="2"/>
     </row>
     <row r="497" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A497" s="2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B497" s="2">
         <v>2</v>
@@ -27188,14 +27188,14 @@
         <v>0</v>
       </c>
       <c r="L497" s="2" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="M497" s="2"/>
       <c r="N497" s="2"/>
     </row>
     <row r="498" spans="1:14" ht="172.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A498" s="2" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B498" s="2">
         <v>2</v>
@@ -27228,14 +27228,14 @@
         <v>0</v>
       </c>
       <c r="L498" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M498" s="2"/>
       <c r="N498" s="2"/>
     </row>
     <row r="499" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A499" s="2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B499" s="2">
         <v>1</v>
@@ -27268,14 +27268,14 @@
         <v>0</v>
       </c>
       <c r="L499" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="M499" s="2"/>
       <c r="N499" s="2"/>
     </row>
     <row r="500" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A500" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B500" s="2">
         <v>0</v>
@@ -27308,14 +27308,14 @@
         <v>0</v>
       </c>
       <c r="L500" s="2" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="M500" s="2"/>
       <c r="N500" s="2"/>
     </row>
     <row r="501" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A501" s="2" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B501" s="2">
         <v>7</v>
@@ -27348,14 +27348,14 @@
         <v>0</v>
       </c>
       <c r="L501" s="2" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="M501" s="2"/>
       <c r="N501" s="2"/>
     </row>
     <row r="502" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A502" s="2" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B502" s="2">
         <v>2</v>
@@ -27388,18 +27388,18 @@
         <v>0</v>
       </c>
       <c r="L502" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="M502" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="M502" s="2" t="s">
-        <v>1338</v>
-      </c>
       <c r="N502" s="2" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="503" spans="1:14" ht="381.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A503" s="2" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B503" s="2">
         <v>5</v>
@@ -27426,22 +27426,22 @@
         <v>28</v>
       </c>
       <c r="J503" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K503" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L503" s="2" t="s">
         <v>1340</v>
       </c>
-      <c r="K503" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L503" s="2" t="s">
+      <c r="M503" s="2" t="s">
         <v>1341</v>
-      </c>
-      <c r="M503" s="2" t="s">
-        <v>1342</v>
       </c>
       <c r="N503" s="2"/>
     </row>
     <row r="504" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A504" s="2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B504" s="2">
         <v>3</v>
@@ -27474,18 +27474,18 @@
         <v>0</v>
       </c>
       <c r="L504" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="M504" s="2" t="s">
         <v>1344</v>
       </c>
-      <c r="M504" s="2" t="s">
-        <v>1345</v>
-      </c>
       <c r="N504" s="2" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="505" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A505" s="2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B505" s="2">
         <v>1</v>
@@ -27518,18 +27518,18 @@
         <v>0</v>
       </c>
       <c r="L505" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M505" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="M505" s="2" t="s">
-        <v>1348</v>
-      </c>
       <c r="N505" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="506" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A506" s="2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B506" s="2">
         <v>2</v>
@@ -27562,14 +27562,14 @@
         <v>0</v>
       </c>
       <c r="L506" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="M506" s="2"/>
       <c r="N506" s="2"/>
     </row>
     <row r="507" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A507" s="2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B507" s="2">
         <v>3</v>
@@ -27602,18 +27602,18 @@
         <v>0</v>
       </c>
       <c r="L507" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M507" s="2" t="s">
         <v>1352</v>
       </c>
-      <c r="M507" s="2" t="s">
+      <c r="N507" s="2" t="s">
         <v>1353</v>
-      </c>
-      <c r="N507" s="2" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="508" spans="1:14" ht="258.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A508" s="2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B508" s="2">
         <v>6</v>
@@ -27646,14 +27646,14 @@
         <v>0</v>
       </c>
       <c r="L508" s="2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="M508" s="2"/>
       <c r="N508" s="2"/>
     </row>
     <row r="509" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A509" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B509" s="2">
         <v>4</v>
@@ -27686,18 +27686,18 @@
         <v>1</v>
       </c>
       <c r="L509" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M509" s="2" t="s">
         <v>1358</v>
       </c>
-      <c r="M509" s="2" t="s">
-        <v>1359</v>
-      </c>
       <c r="N509" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="510" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A510" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B510" s="2">
         <v>4</v>
@@ -27724,20 +27724,20 @@
         <v>17</v>
       </c>
       <c r="J510" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K510" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L510" s="2" t="s">
         <v>1361</v>
-      </c>
-      <c r="K510" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L510" s="2" t="s">
-        <v>1362</v>
       </c>
       <c r="M510" s="2"/>
       <c r="N510" s="2"/>
     </row>
     <row r="511" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A511" s="2" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="B511" s="2">
         <v>5</v>
@@ -27770,14 +27770,14 @@
         <v>0</v>
       </c>
       <c r="L511" s="2" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="M511" s="2"/>
       <c r="N511" s="2"/>
     </row>
     <row r="512" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A512" s="2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B512" s="2">
         <v>10</v>
@@ -27810,14 +27810,14 @@
         <v>0</v>
       </c>
       <c r="L512" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="M512" s="2"/>
       <c r="N512" s="2"/>
     </row>
     <row r="513" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A513" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B513" s="2">
         <v>3</v>
@@ -27850,18 +27850,18 @@
         <v>0</v>
       </c>
       <c r="L513" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="M513" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="M513" s="2" t="s">
-        <v>1369</v>
-      </c>
       <c r="N513" s="2" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="514" spans="1:14" ht="209.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A514" s="2" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B514" s="2">
         <v>4</v>
@@ -27879,13 +27879,13 @@
         <v>0</v>
       </c>
       <c r="G514" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H514" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I514" s="2" t="s">
         <v>1371</v>
-      </c>
-      <c r="H514" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I514" s="2" t="s">
-        <v>1372</v>
       </c>
       <c r="J514" s="2" t="s">
         <v>189</v>
@@ -27894,16 +27894,16 @@
         <v>1</v>
       </c>
       <c r="L514" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M514" s="2" t="s">
         <v>1373</v>
-      </c>
-      <c r="M514" s="2" t="s">
-        <v>1374</v>
       </c>
       <c r="N514" s="2"/>
     </row>
     <row r="515" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A515" s="2" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="B515" s="2">
         <v>5</v>
@@ -27936,14 +27936,14 @@
         <v>0</v>
       </c>
       <c r="L515" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="M515" s="2"/>
       <c r="N515" s="2"/>
     </row>
     <row r="516" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A516" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B516" s="2">
         <v>2</v>
@@ -27976,16 +27976,16 @@
         <v>0</v>
       </c>
       <c r="L516" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="M516" s="2" t="s">
         <v>1378</v>
-      </c>
-      <c r="M516" s="2" t="s">
-        <v>1379</v>
       </c>
       <c r="N516" s="2"/>
     </row>
     <row r="517" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A517" s="2" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B517" s="2">
         <v>1</v>
@@ -28018,7 +28018,7 @@
         <v>0</v>
       </c>
       <c r="L517" s="2" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="M517" s="2" t="s">
         <v>575</v>
@@ -28029,7 +28029,7 @@
     </row>
     <row r="518" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" s="2" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B518" s="2">
         <v>5</v>
@@ -28062,14 +28062,14 @@
         <v>0</v>
       </c>
       <c r="L518" s="2" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="M518" s="2"/>
       <c r="N518" s="2"/>
     </row>
     <row r="519" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A519" s="2" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B519" s="2">
         <v>0</v>
@@ -28102,14 +28102,14 @@
         <v>0</v>
       </c>
       <c r="L519" s="2" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="M519" s="2"/>
       <c r="N519" s="2"/>
     </row>
     <row r="520" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A520" s="2" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B520" s="2">
         <v>12</v>
@@ -28142,14 +28142,14 @@
         <v>0</v>
       </c>
       <c r="L520" s="2" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="M520" s="2"/>
       <c r="N520" s="2"/>
     </row>
     <row r="521" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A521" s="2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B521" s="2">
         <v>2</v>
@@ -28182,7 +28182,7 @@
         <v>0</v>
       </c>
       <c r="L521" s="2" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="M521" s="2" t="s">
         <v>591</v>
@@ -28193,7 +28193,7 @@
     </row>
     <row r="522" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A522" s="2" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B522" s="2">
         <v>1</v>
@@ -28211,7 +28211,7 @@
         <v>0</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H522" s="2" t="b">
         <v>0</v>
@@ -28226,14 +28226,14 @@
         <v>0</v>
       </c>
       <c r="L522" s="2" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="M522" s="2"/>
       <c r="N522" s="2"/>
     </row>
     <row r="523" spans="1:14" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A523" s="2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B523" s="2">
         <v>1</v>
@@ -28266,14 +28266,14 @@
         <v>0</v>
       </c>
       <c r="L523" s="2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="M523" s="2"/>
       <c r="N523" s="2"/>
     </row>
     <row r="524" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A524" s="2" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B524" s="2">
         <v>0</v>
@@ -28306,14 +28306,14 @@
         <v>0</v>
       </c>
       <c r="L524" s="2" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="M524" s="2"/>
       <c r="N524" s="2"/>
     </row>
     <row r="525" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A525" s="2" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B525" s="2">
         <v>0</v>
@@ -28346,7 +28346,7 @@
         <v>0</v>
       </c>
       <c r="L525" s="2" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="M525" s="2" t="s">
         <v>507</v>
@@ -28357,7 +28357,7 @@
     </row>
     <row r="526" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A526" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B526" s="2">
         <v>5</v>
@@ -28390,14 +28390,14 @@
         <v>0</v>
       </c>
       <c r="L526" s="2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="M526" s="2"/>
       <c r="N526" s="2"/>
     </row>
     <row r="527" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A527" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B527" s="2">
         <v>2</v>
@@ -28430,14 +28430,14 @@
         <v>1</v>
       </c>
       <c r="L527" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="M527" s="2"/>
       <c r="N527" s="2"/>
     </row>
     <row r="528" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A528" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B528" s="2">
         <v>7</v>
@@ -28470,14 +28470,14 @@
         <v>1</v>
       </c>
       <c r="L528" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="M528" s="2"/>
       <c r="N528" s="2"/>
     </row>
     <row r="529" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A529" s="2" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B529" s="2">
         <v>1</v>
@@ -28510,14 +28510,14 @@
         <v>0</v>
       </c>
       <c r="L529" s="2" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="M529" s="2"/>
       <c r="N529" s="2"/>
     </row>
     <row r="530" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A530" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B530" s="2">
         <v>1</v>
@@ -28535,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="G530" s="2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H530" s="2" t="b">
         <v>0</v>
@@ -28550,14 +28550,14 @@
         <v>0</v>
       </c>
       <c r="L530" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="M530" s="2"/>
       <c r="N530" s="2"/>
     </row>
     <row r="531" spans="1:14" ht="233.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A531" s="2" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B531" s="2">
         <v>10</v>
@@ -28575,7 +28575,7 @@
         <v>1</v>
       </c>
       <c r="G531" s="2" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H531" s="2" t="b">
         <v>0</v>
@@ -28590,14 +28590,14 @@
         <v>0</v>
       </c>
       <c r="L531" s="2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="M531" s="2"/>
       <c r="N531" s="2"/>
     </row>
     <row r="532" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A532" s="2" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B532" s="2">
         <v>6</v>
@@ -28630,14 +28630,14 @@
         <v>0</v>
       </c>
       <c r="L532" s="2" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="M532" s="2"/>
       <c r="N532" s="2"/>
     </row>
     <row r="533" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A533" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B533" s="2">
         <v>2</v>
@@ -28670,14 +28670,14 @@
         <v>1</v>
       </c>
       <c r="L533" s="2" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="M533" s="2"/>
       <c r="N533" s="2"/>
     </row>
     <row r="534" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A534" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B534" s="2">
         <v>1</v>
@@ -28710,18 +28710,18 @@
         <v>0</v>
       </c>
       <c r="L534" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="M534" s="2" t="s">
         <v>1418</v>
       </c>
-      <c r="M534" s="2" t="s">
-        <v>1419</v>
-      </c>
       <c r="N534" s="2" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="535" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A535" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B535" s="2">
         <v>3</v>
@@ -28754,14 +28754,14 @@
         <v>0</v>
       </c>
       <c r="L535" s="2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="M535" s="2"/>
       <c r="N535" s="2"/>
     </row>
     <row r="536" spans="1:14" ht="172.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A536" s="2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B536" s="2">
         <v>4</v>
@@ -28794,14 +28794,14 @@
         <v>0</v>
       </c>
       <c r="L536" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="M536" s="2"/>
       <c r="N536" s="2"/>
     </row>
     <row r="537" spans="1:14" ht="221.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A537" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B537" s="2">
         <v>5</v>
@@ -28834,18 +28834,18 @@
         <v>0</v>
       </c>
       <c r="L537" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="M537" s="2" t="s">
         <v>1425</v>
       </c>
-      <c r="M537" s="2" t="s">
-        <v>1426</v>
-      </c>
       <c r="N537" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="538" spans="1:14" ht="196.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A538" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B538" s="2">
         <v>1</v>
@@ -28878,14 +28878,14 @@
         <v>0</v>
       </c>
       <c r="L538" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="M538" s="2"/>
       <c r="N538" s="2"/>
     </row>
     <row r="539" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B539" s="2">
         <v>0</v>
@@ -28918,18 +28918,18 @@
         <v>0</v>
       </c>
       <c r="L539" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="M539" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="M539" s="2" t="s">
+      <c r="N539" s="2" t="s">
         <v>1431</v>
-      </c>
-      <c r="N539" s="2" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="540" spans="1:14" ht="344.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A540" s="2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B540" s="2">
         <v>8</v>
@@ -28947,7 +28947,7 @@
         <v>1</v>
       </c>
       <c r="G540" s="2" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H540" s="2" t="b">
         <v>0</v>
@@ -28962,14 +28962,14 @@
         <v>0</v>
       </c>
       <c r="L540" s="2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="M540" s="2"/>
       <c r="N540" s="2"/>
     </row>
     <row r="541" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A541" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B541" s="2">
         <v>7</v>
@@ -29002,14 +29002,14 @@
         <v>0</v>
       </c>
       <c r="L541" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="M541" s="2"/>
       <c r="N541" s="2"/>
     </row>
     <row r="542" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A542" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B542" s="2">
         <v>0</v>
@@ -29042,14 +29042,14 @@
         <v>0</v>
       </c>
       <c r="L542" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="M542" s="2"/>
       <c r="N542" s="2"/>
     </row>
     <row r="543" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A543" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B543" s="2">
         <v>1</v>
@@ -29082,14 +29082,14 @@
         <v>1</v>
       </c>
       <c r="L543" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="M543" s="2"/>
       <c r="N543" s="2"/>
     </row>
     <row r="544" spans="1:14" ht="221.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A544" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B544" s="2">
         <v>4</v>
@@ -29122,14 +29122,14 @@
         <v>0</v>
       </c>
       <c r="L544" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="M544" s="2"/>
       <c r="N544" s="2"/>
     </row>
     <row r="545" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A545" s="2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B545" s="2">
         <v>1</v>
@@ -29162,14 +29162,14 @@
         <v>0</v>
       </c>
       <c r="L545" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="M545" s="2"/>
       <c r="N545" s="2"/>
     </row>
     <row r="546" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A546" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B546" s="2">
         <v>2</v>
@@ -29202,14 +29202,14 @@
         <v>0</v>
       </c>
       <c r="L546" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="M546" s="2"/>
       <c r="N546" s="2"/>
     </row>
     <row r="547" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A547" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B547" s="2">
         <v>2</v>
@@ -29242,14 +29242,14 @@
         <v>0</v>
       </c>
       <c r="L547" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="M547" s="2"/>
       <c r="N547" s="2"/>
     </row>
     <row r="548" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A548" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B548" s="2">
         <v>2</v>
@@ -29282,18 +29282,18 @@
         <v>0</v>
       </c>
       <c r="L548" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="M548" s="2" t="s">
         <v>1451</v>
       </c>
-      <c r="M548" s="2" t="s">
-        <v>1452</v>
-      </c>
       <c r="N548" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="549" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A549" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B549" s="2">
         <v>2</v>
@@ -29326,7 +29326,7 @@
         <v>0</v>
       </c>
       <c r="L549" s="2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="M549" s="2" t="s">
         <v>996</v>
@@ -29337,7 +29337,7 @@
     </row>
     <row r="550" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A550" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B550" s="2">
         <v>5</v>
@@ -29370,14 +29370,14 @@
         <v>0</v>
       </c>
       <c r="L550" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="M550" s="2"/>
       <c r="N550" s="2"/>
     </row>
     <row r="551" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A551" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B551" s="2">
         <v>0</v>
@@ -29404,24 +29404,24 @@
         <v>35</v>
       </c>
       <c r="J551" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="K551" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L551" s="2" t="s">
         <v>1458</v>
       </c>
-      <c r="K551" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L551" s="2" t="s">
+      <c r="M551" s="2" t="s">
         <v>1459</v>
       </c>
-      <c r="M551" s="2" t="s">
-        <v>1460</v>
-      </c>
       <c r="N551" s="2" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="552" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A552" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B552" s="2">
         <v>0</v>
@@ -29454,14 +29454,14 @@
         <v>0</v>
       </c>
       <c r="L552" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="M552" s="2"/>
       <c r="N552" s="2"/>
     </row>
     <row r="553" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A553" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B553" s="2">
         <v>7</v>
@@ -29494,14 +29494,14 @@
         <v>0</v>
       </c>
       <c r="L553" s="2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="M553" s="2"/>
       <c r="N553" s="2"/>
     </row>
     <row r="554" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A554" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B554" s="2">
         <v>3</v>
@@ -29534,14 +29534,14 @@
         <v>0</v>
       </c>
       <c r="L554" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="M554" s="2"/>
       <c r="N554" s="2"/>
     </row>
     <row r="555" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A555" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B555" s="2">
         <v>0</v>
@@ -29574,7 +29574,7 @@
         <v>0</v>
       </c>
       <c r="L555" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="M555" s="2" t="s">
         <v>1136</v>
@@ -29585,7 +29585,7 @@
     </row>
     <row r="556" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A556" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B556" s="2">
         <v>5</v>
@@ -29618,14 +29618,14 @@
         <v>0</v>
       </c>
       <c r="L556" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="M556" s="2"/>
       <c r="N556" s="2"/>
     </row>
     <row r="557" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A557" s="2" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B557" s="2">
         <v>5</v>
@@ -29658,14 +29658,14 @@
         <v>0</v>
       </c>
       <c r="L557" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="M557" s="2"/>
       <c r="N557" s="2"/>
     </row>
     <row r="558" spans="1:14" ht="307.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A558" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B558" s="2">
         <v>12</v>
@@ -29698,14 +29698,14 @@
         <v>0</v>
       </c>
       <c r="L558" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="M558" s="2"/>
       <c r="N558" s="2"/>
     </row>
     <row r="559" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A559" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B559" s="2">
         <v>5</v>
@@ -29738,18 +29738,18 @@
         <v>0</v>
       </c>
       <c r="L559" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="M559" s="2" t="s">
         <v>1476</v>
       </c>
-      <c r="M559" s="2" t="s">
-        <v>1477</v>
-      </c>
       <c r="N559" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="560" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A560" s="2" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B560" s="2">
         <v>1</v>
@@ -29782,14 +29782,14 @@
         <v>0</v>
       </c>
       <c r="L560" s="2" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="M560" s="2"/>
       <c r="N560" s="2"/>
     </row>
     <row r="561" spans="1:14" ht="209.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" s="2" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B561" s="2">
         <v>3</v>
@@ -29822,14 +29822,14 @@
         <v>0</v>
       </c>
       <c r="L561" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="M561" s="2"/>
       <c r="N561" s="2"/>
     </row>
     <row r="562" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A562" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B562" s="2">
         <v>6</v>
@@ -29862,18 +29862,18 @@
         <v>0</v>
       </c>
       <c r="L562" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M562" s="2" t="s">
         <v>1483</v>
       </c>
-      <c r="M562" s="2" t="s">
-        <v>1484</v>
-      </c>
       <c r="N562" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="563" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A563" s="2" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B563" s="2">
         <v>6</v>
@@ -29906,18 +29906,18 @@
         <v>0</v>
       </c>
       <c r="L563" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="M563" s="2" t="s">
         <v>1486</v>
       </c>
-      <c r="M563" s="2" t="s">
-        <v>1487</v>
-      </c>
       <c r="N563" s="2" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="564" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A564" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B564" s="2">
         <v>7</v>
@@ -29950,18 +29950,18 @@
         <v>0</v>
       </c>
       <c r="L564" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="M564" s="2" t="s">
         <v>1489</v>
       </c>
-      <c r="M564" s="2" t="s">
-        <v>1490</v>
-      </c>
       <c r="N564" s="2" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="565" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A565" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="B565" s="2">
         <v>6</v>
@@ -29994,18 +29994,18 @@
         <v>0</v>
       </c>
       <c r="L565" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M565" s="2" t="s">
         <v>1492</v>
       </c>
-      <c r="M565" s="2" t="s">
-        <v>1493</v>
-      </c>
       <c r="N565" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="566" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A566" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B566" s="2">
         <v>5</v>
@@ -30038,18 +30038,18 @@
         <v>0</v>
       </c>
       <c r="L566" s="2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="M566" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="N566" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="567" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A567" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B567" s="2">
         <v>6</v>
@@ -30082,18 +30082,18 @@
         <v>0</v>
       </c>
       <c r="L567" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="M567" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="M567" s="2" t="s">
+      <c r="N567" s="2" t="s">
         <v>1498</v>
-      </c>
-      <c r="N567" s="2" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="568" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A568" s="2" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B568" s="2">
         <v>6</v>
@@ -30126,18 +30126,18 @@
         <v>0</v>
       </c>
       <c r="L568" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="M568" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="N568" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="569" spans="1:14" ht="282.89999999999998" x14ac:dyDescent="0.55000000000000004">
       <c r="A569" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B569" s="2">
         <v>6</v>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="I569" s="2" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="J569" s="2" t="s">
         <v>111</v>
@@ -30170,14 +30170,14 @@
         <v>1</v>
       </c>
       <c r="L569" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="M569" s="2"/>
       <c r="N569" s="2"/>
     </row>
     <row r="570" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A570" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B570" s="2">
         <v>5</v>
@@ -30210,18 +30210,18 @@
         <v>0</v>
       </c>
       <c r="L570" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="M570" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="N570" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="571" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A571" s="2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B571" s="2">
         <v>5</v>
@@ -30254,18 +30254,18 @@
         <v>0</v>
       </c>
       <c r="L571" s="2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="M571" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="N571" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="572" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A572" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B572" s="2">
         <v>8</v>
@@ -30298,14 +30298,14 @@
         <v>0</v>
       </c>
       <c r="L572" s="2" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="M572" s="2"/>
       <c r="N572" s="2"/>
     </row>
     <row r="573" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A573" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B573" s="2">
         <v>10</v>
@@ -30338,14 +30338,14 @@
         <v>0</v>
       </c>
       <c r="L573" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="M573" s="2"/>
       <c r="N573" s="2"/>
     </row>
     <row r="574" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A574" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B574" s="2">
         <v>2</v>
@@ -30378,18 +30378,18 @@
         <v>0</v>
       </c>
       <c r="L574" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="M574" s="2" t="s">
         <v>1514</v>
       </c>
-      <c r="M574" s="2" t="s">
-        <v>1515</v>
-      </c>
       <c r="N574" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="575" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A575" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B575" s="2">
         <v>6</v>
@@ -30422,14 +30422,14 @@
         <v>0</v>
       </c>
       <c r="L575" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="M575" s="2"/>
       <c r="N575" s="2"/>
     </row>
     <row r="576" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A576" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B576" s="2">
         <v>3</v>
@@ -30462,18 +30462,18 @@
         <v>0</v>
       </c>
       <c r="L576" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="M576" s="2" t="s">
         <v>1519</v>
       </c>
-      <c r="M576" s="2" t="s">
-        <v>1520</v>
-      </c>
       <c r="N576" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="577" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A577" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B577" s="2">
         <v>0</v>
@@ -30506,14 +30506,14 @@
         <v>0</v>
       </c>
       <c r="L577" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="M577" s="2"/>
       <c r="N577" s="2"/>
     </row>
     <row r="578" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A578" s="2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B578" s="2">
         <v>10</v>
@@ -30546,14 +30546,14 @@
         <v>0</v>
       </c>
       <c r="L578" s="2" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="M578" s="2"/>
       <c r="N578" s="2"/>
     </row>
     <row r="579" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A579" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B579" s="2">
         <v>6</v>
@@ -30586,14 +30586,14 @@
         <v>0</v>
       </c>
       <c r="L579" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="M579" s="2"/>
       <c r="N579" s="2"/>
     </row>
     <row r="580" spans="1:14" ht="332.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A580" s="2" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B580" s="2">
         <v>6</v>
@@ -30626,14 +30626,14 @@
         <v>0</v>
       </c>
       <c r="L580" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="M580" s="2"/>
       <c r="N580" s="2"/>
     </row>
     <row r="581" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A581" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B581" s="2">
         <v>10</v>
@@ -30660,20 +30660,20 @@
         <v>75</v>
       </c>
       <c r="J581" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K581" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L581" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="M581" s="2"/>
       <c r="N581" s="2"/>
     </row>
     <row r="582" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A582" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B582" s="2">
         <v>9</v>
@@ -30706,14 +30706,14 @@
         <v>0</v>
       </c>
       <c r="L582" s="2" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="M582" s="2"/>
       <c r="N582" s="2"/>
     </row>
     <row r="583" spans="1:14" ht="246" x14ac:dyDescent="0.55000000000000004">
       <c r="A583" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B583" s="2">
         <v>6</v>
@@ -30746,14 +30746,14 @@
         <v>0</v>
       </c>
       <c r="L583" s="2" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="M583" s="2"/>
       <c r="N583" s="2"/>
     </row>
     <row r="584" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A584" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B584" s="2">
         <v>9</v>
@@ -30786,14 +30786,14 @@
         <v>0</v>
       </c>
       <c r="L584" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="M584" s="2"/>
       <c r="N584" s="2"/>
     </row>
     <row r="585" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" s="2" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B585" s="2">
         <v>6</v>
@@ -30811,7 +30811,7 @@
         <v>1</v>
       </c>
       <c r="G585" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H585" s="2" t="b">
         <v>0</v>
@@ -30826,18 +30826,18 @@
         <v>0</v>
       </c>
       <c r="L585" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="M585" s="2" t="s">
         <v>1539</v>
       </c>
-      <c r="M585" s="2" t="s">
-        <v>1540</v>
-      </c>
       <c r="N585" s="2" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="586" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A586" s="2" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B586" s="2">
         <v>6</v>
@@ -30870,16 +30870,16 @@
         <v>0</v>
       </c>
       <c r="L586" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="M586" s="2" t="s">
         <v>1542</v>
-      </c>
-      <c r="M586" s="2" t="s">
-        <v>1543</v>
       </c>
       <c r="N586" s="2"/>
     </row>
     <row r="587" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A587" s="2" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B587" s="2">
         <v>9</v>
@@ -30912,14 +30912,14 @@
         <v>0</v>
       </c>
       <c r="L587" s="2" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M587" s="2"/>
       <c r="N587" s="2"/>
     </row>
     <row r="588" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A588" s="2" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B588" s="2">
         <v>0</v>
@@ -30952,14 +30952,14 @@
         <v>0</v>
       </c>
       <c r="L588" s="2" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="M588" s="2"/>
       <c r="N588" s="2"/>
     </row>
     <row r="589" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A589" s="2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B589" s="2">
         <v>0</v>
@@ -30992,14 +30992,14 @@
         <v>0</v>
       </c>
       <c r="L589" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="M589" s="2"/>
       <c r="N589" s="2"/>
     </row>
     <row r="590" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A590" s="2" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B590" s="2">
         <v>4</v>
@@ -31032,7 +31032,7 @@
         <v>0</v>
       </c>
       <c r="L590" s="2" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="M590" s="2" t="s">
         <v>285</v>
@@ -31043,7 +31043,7 @@
     </row>
     <row r="591" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A591" s="2" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B591" s="2">
         <v>0</v>
@@ -31076,14 +31076,14 @@
         <v>0</v>
       </c>
       <c r="L591" s="2" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="M591" s="2"/>
       <c r="N591" s="2"/>
     </row>
     <row r="592" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A592" s="2" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B592" s="2">
         <v>1</v>
@@ -31116,14 +31116,14 @@
         <v>0</v>
       </c>
       <c r="L592" s="2" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="M592" s="2"/>
       <c r="N592" s="2"/>
     </row>
     <row r="593" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A593" s="2" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B593" s="2">
         <v>1</v>
@@ -31150,13 +31150,13 @@
         <v>35</v>
       </c>
       <c r="J593" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K593" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L593" s="2" t="s">
         <v>1557</v>
-      </c>
-      <c r="K593" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L593" s="2" t="s">
-        <v>1558</v>
       </c>
       <c r="M593" s="2" t="s">
         <v>317</v>
@@ -31167,7 +31167,7 @@
     </row>
     <row r="594" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A594" s="2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B594" s="2">
         <v>3</v>
@@ -31200,14 +31200,14 @@
         <v>0</v>
       </c>
       <c r="L594" s="2" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="M594" s="2"/>
       <c r="N594" s="2"/>
     </row>
     <row r="595" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A595" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B595" s="2">
         <v>12</v>
@@ -31240,14 +31240,14 @@
         <v>0</v>
       </c>
       <c r="L595" s="2" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="M595" s="2"/>
       <c r="N595" s="2"/>
     </row>
     <row r="596" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A596" s="2" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B596" s="2">
         <v>6</v>
@@ -31271,7 +31271,7 @@
         <v>0</v>
       </c>
       <c r="I596" s="2" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J596" s="2" t="s">
         <v>118</v>
@@ -31280,14 +31280,14 @@
         <v>0</v>
       </c>
       <c r="L596" s="2" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="M596" s="2"/>
       <c r="N596" s="2"/>
     </row>
     <row r="597" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A597" s="2" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B597" s="2">
         <v>12</v>
@@ -31320,14 +31320,14 @@
         <v>0</v>
       </c>
       <c r="L597" s="2" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M597" s="2"/>
       <c r="N597" s="2"/>
     </row>
     <row r="598" spans="1:14" ht="209.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A598" s="2" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B598" s="2">
         <v>4</v>
@@ -31360,18 +31360,18 @@
         <v>0</v>
       </c>
       <c r="L598" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="M598" s="2" t="s">
         <v>1569</v>
       </c>
-      <c r="M598" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="N598" s="2" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="599" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A599" s="2" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B599" s="2">
         <v>5</v>
@@ -31404,14 +31404,14 @@
         <v>1</v>
       </c>
       <c r="L599" s="2" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="M599" s="2"/>
       <c r="N599" s="2"/>
     </row>
     <row r="600" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A600" s="2" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B600" s="2">
         <v>4</v>
@@ -31444,14 +31444,14 @@
         <v>0</v>
       </c>
       <c r="L600" s="2" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="M600" s="2"/>
       <c r="N600" s="2"/>
     </row>
     <row r="601" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A601" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B601" s="2">
         <v>3</v>
@@ -31484,14 +31484,14 @@
         <v>0</v>
       </c>
       <c r="L601" s="2" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="M601" s="2"/>
       <c r="N601" s="2"/>
     </row>
     <row r="602" spans="1:14" ht="332.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A602" s="2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B602" s="2">
         <v>6</v>
@@ -31524,14 +31524,14 @@
         <v>0</v>
       </c>
       <c r="L602" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="M602" s="2"/>
       <c r="N602" s="2"/>
     </row>
     <row r="603" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A603" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B603" s="2">
         <v>8</v>
@@ -31564,14 +31564,14 @@
         <v>0</v>
       </c>
       <c r="L603" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M603" s="2"/>
       <c r="N603" s="2"/>
     </row>
     <row r="604" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A604" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B604" s="2">
         <v>11</v>
@@ -31604,14 +31604,14 @@
         <v>0</v>
       </c>
       <c r="L604" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M604" s="2"/>
       <c r="N604" s="2"/>
     </row>
     <row r="605" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A605" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B605" s="2">
         <v>6</v>
@@ -31644,14 +31644,14 @@
         <v>0</v>
       </c>
       <c r="L605" s="2" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="M605" s="2"/>
       <c r="N605" s="2"/>
     </row>
     <row r="606" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A606" s="2" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="B606" s="2">
         <v>0</v>
@@ -31684,14 +31684,14 @@
         <v>0</v>
       </c>
       <c r="L606" s="2" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="M606" s="2"/>
       <c r="N606" s="2"/>
     </row>
     <row r="607" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A607" s="2" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B607" s="2">
         <v>12</v>
@@ -31724,14 +31724,14 @@
         <v>0</v>
       </c>
       <c r="L607" s="2" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="M607" s="2"/>
       <c r="N607" s="2"/>
     </row>
     <row r="608" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A608" s="2" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B608" s="2">
         <v>12</v>
@@ -31764,14 +31764,14 @@
         <v>0</v>
       </c>
       <c r="L608" s="2" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="M608" s="2"/>
       <c r="N608" s="2"/>
     </row>
     <row r="609" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A609" s="2" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B609" s="2">
         <v>8</v>
@@ -31804,14 +31804,14 @@
         <v>0</v>
       </c>
       <c r="L609" s="2" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="M609" s="2"/>
       <c r="N609" s="2"/>
     </row>
     <row r="610" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A610" s="2" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B610" s="2">
         <v>0</v>
@@ -31835,7 +31835,7 @@
         <v>1</v>
       </c>
       <c r="I610" s="2" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="J610" s="2" t="s">
         <v>43</v>
@@ -31844,14 +31844,14 @@
         <v>0</v>
       </c>
       <c r="L610" s="2" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="M610" s="2"/>
       <c r="N610" s="2"/>
     </row>
     <row r="611" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A611" s="2" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B611" s="2">
         <v>0</v>
@@ -31884,18 +31884,18 @@
         <v>0</v>
       </c>
       <c r="L611" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="M611" s="2" t="s">
         <v>1596</v>
       </c>
-      <c r="M611" s="2" t="s">
+      <c r="N611" s="2" t="s">
         <v>1597</v>
-      </c>
-      <c r="N611" s="2" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="612" spans="1:14" ht="246" x14ac:dyDescent="0.55000000000000004">
       <c r="A612" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B612" s="2">
         <v>10</v>
@@ -31919,7 +31919,7 @@
         <v>1</v>
       </c>
       <c r="I612" s="2" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="J612" s="2" t="s">
         <v>1144</v>
@@ -31928,14 +31928,14 @@
         <v>0</v>
       </c>
       <c r="L612" s="2" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="M612" s="2"/>
       <c r="N612" s="2"/>
     </row>
     <row r="613" spans="1:14" ht="270.60000000000002" x14ac:dyDescent="0.55000000000000004">
       <c r="A613" s="2" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B613" s="2">
         <v>5</v>
@@ -31968,18 +31968,18 @@
         <v>0</v>
       </c>
       <c r="L613" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="M613" s="2" t="s">
         <v>1603</v>
       </c>
-      <c r="M613" s="2" t="s">
-        <v>1604</v>
-      </c>
       <c r="N613" s="2" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="614" spans="1:14" ht="172.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A614" s="2" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B614" s="2">
         <v>3</v>
@@ -32006,20 +32006,20 @@
         <v>71</v>
       </c>
       <c r="J614" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="K614" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L614" s="2" t="s">
         <v>1606</v>
-      </c>
-      <c r="K614" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L614" s="2" t="s">
-        <v>1607</v>
       </c>
       <c r="M614" s="2"/>
       <c r="N614" s="2"/>
     </row>
     <row r="615" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A615" s="2" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B615" s="2">
         <v>6</v>
@@ -32052,14 +32052,14 @@
         <v>1</v>
       </c>
       <c r="L615" s="2" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="M615" s="2"/>
       <c r="N615" s="2"/>
     </row>
     <row r="616" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A616" s="2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B616" s="2">
         <v>2</v>
@@ -32092,18 +32092,18 @@
         <v>0</v>
       </c>
       <c r="L616" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="M616" s="2" t="s">
         <v>1611</v>
       </c>
-      <c r="M616" s="2" t="s">
-        <v>1612</v>
-      </c>
       <c r="N616" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="617" spans="1:14" ht="172.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A617" s="2" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B617" s="2">
         <v>1</v>
@@ -32136,14 +32136,14 @@
         <v>1</v>
       </c>
       <c r="L617" s="2" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="M617" s="2"/>
       <c r="N617" s="2"/>
     </row>
     <row r="618" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A618" s="2" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B618" s="2">
         <v>4</v>
@@ -32176,7 +32176,7 @@
         <v>0</v>
       </c>
       <c r="L618" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="M618" s="2" t="s">
         <v>713</v>
@@ -32187,7 +32187,7 @@
     </row>
     <row r="619" spans="1:14" ht="196.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A619" s="2" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B619" s="2">
         <v>2</v>
@@ -32220,16 +32220,16 @@
         <v>0</v>
       </c>
       <c r="L619" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="M619" s="2" t="s">
         <v>1618</v>
-      </c>
-      <c r="M619" s="2" t="s">
-        <v>1619</v>
       </c>
       <c r="N619" s="2"/>
     </row>
     <row r="620" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A620" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B620" s="2">
         <v>0</v>
@@ -32262,14 +32262,14 @@
         <v>0</v>
       </c>
       <c r="L620" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="M620" s="2"/>
       <c r="N620" s="2"/>
     </row>
     <row r="621" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A621" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B621" s="2">
         <v>0</v>
@@ -32302,14 +32302,14 @@
         <v>0</v>
       </c>
       <c r="L621" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M621" s="2"/>
       <c r="N621" s="2"/>
     </row>
     <row r="622" spans="1:14" ht="49.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A622" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B622" s="2">
         <v>0</v>
@@ -32342,14 +32342,14 @@
         <v>0</v>
       </c>
       <c r="L622" s="2" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="M622" s="2"/>
       <c r="N622" s="2"/>
     </row>
     <row r="623" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A623" s="2" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B623" s="2">
         <v>8</v>
@@ -32382,14 +32382,14 @@
         <v>0</v>
       </c>
       <c r="L623" s="2" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="M623" s="2"/>
       <c r="N623" s="2"/>
     </row>
     <row r="624" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A624" s="2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B624" s="2">
         <v>5</v>
@@ -32422,18 +32422,18 @@
         <v>0</v>
       </c>
       <c r="L624" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="M624" s="2" t="s">
         <v>1629</v>
       </c>
-      <c r="M624" s="2" t="s">
-        <v>1630</v>
-      </c>
       <c r="N624" s="2" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="625" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A625" s="2" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B625" s="2">
         <v>12</v>
@@ -32466,14 +32466,14 @@
         <v>0</v>
       </c>
       <c r="L625" s="2" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M625" s="2"/>
       <c r="N625" s="2"/>
     </row>
     <row r="626" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A626" s="2" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B626" s="2">
         <v>2</v>
@@ -32506,18 +32506,18 @@
         <v>0</v>
       </c>
       <c r="L626" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="M626" s="2" t="s">
         <v>1634</v>
       </c>
-      <c r="M626" s="2" t="s">
-        <v>1635</v>
-      </c>
       <c r="N626" s="2" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="627" spans="1:14" ht="270.60000000000002" x14ac:dyDescent="0.55000000000000004">
       <c r="A627" s="2" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B627" s="2">
         <v>9</v>
@@ -32550,18 +32550,18 @@
         <v>0</v>
       </c>
       <c r="L627" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="M627" s="2" t="s">
         <v>1637</v>
       </c>
-      <c r="M627" s="2" t="s">
-        <v>1638</v>
-      </c>
       <c r="N627" s="2" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="628" spans="1:14" ht="147.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A628" s="2" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B628" s="2">
         <v>5</v>
@@ -32594,7 +32594,7 @@
         <v>0</v>
       </c>
       <c r="L628" s="2" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="M628" s="2" t="s">
         <v>234</v>
@@ -32605,7 +32605,7 @@
     </row>
     <row r="629" spans="1:14" ht="172.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A629" s="2" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B629" s="2">
         <v>7</v>
@@ -32638,14 +32638,14 @@
         <v>0</v>
       </c>
       <c r="L629" s="2" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="M629" s="2"/>
       <c r="N629" s="2"/>
     </row>
     <row r="630" spans="1:14" ht="209.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A630" s="2" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B630" s="2">
         <v>7</v>
@@ -32678,18 +32678,18 @@
         <v>0</v>
       </c>
       <c r="L630" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M630" s="2" t="s">
         <v>1644</v>
       </c>
-      <c r="M630" s="2" t="s">
-        <v>1645</v>
-      </c>
       <c r="N630" s="2" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="631" spans="1:14" ht="233.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A631" s="2" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B631" s="2">
         <v>6</v>
@@ -32722,7 +32722,7 @@
         <v>0</v>
       </c>
       <c r="L631" s="2" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="M631" s="2" t="s">
         <v>333</v>
@@ -32733,7 +32733,7 @@
     </row>
     <row r="632" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A632" s="2" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="B632" s="2">
         <v>4</v>
@@ -32766,14 +32766,14 @@
         <v>0</v>
       </c>
       <c r="L632" s="2" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="M632" s="2"/>
       <c r="N632" s="2"/>
     </row>
     <row r="633" spans="1:14" ht="319.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A633" s="2" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B633" s="2">
         <v>6</v>
@@ -32806,14 +32806,14 @@
         <v>0</v>
       </c>
       <c r="L633" s="2" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="M633" s="2"/>
       <c r="N633" s="2"/>
     </row>
     <row r="634" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A634" s="2" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B634" s="2">
         <v>8</v>
@@ -32846,18 +32846,18 @@
         <v>0</v>
       </c>
       <c r="L634" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="M634" s="2" t="s">
         <v>1653</v>
       </c>
-      <c r="M634" s="2" t="s">
-        <v>1654</v>
-      </c>
       <c r="N634" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="635" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A635" s="2" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B635" s="2">
         <v>4</v>
@@ -32890,14 +32890,14 @@
         <v>0</v>
       </c>
       <c r="L635" s="2" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="M635" s="2"/>
       <c r="N635" s="2"/>
     </row>
     <row r="636" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A636" s="2" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="B636" s="2">
         <v>3</v>
@@ -32930,14 +32930,14 @@
         <v>0</v>
       </c>
       <c r="L636" s="2" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="M636" s="2"/>
       <c r="N636" s="2"/>
     </row>
     <row r="637" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A637" s="2" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B637" s="2">
         <v>2</v>
@@ -32970,14 +32970,14 @@
         <v>0</v>
       </c>
       <c r="L637" s="2" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="M637" s="2"/>
       <c r="N637" s="2"/>
     </row>
     <row r="638" spans="1:14" ht="36.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A638" s="2" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B638" s="2">
         <v>4</v>
@@ -33010,14 +33010,14 @@
         <v>1</v>
       </c>
       <c r="L638" s="2" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="M638" s="2"/>
       <c r="N638" s="2"/>
     </row>
     <row r="639" spans="1:14" ht="86.1" x14ac:dyDescent="0.55000000000000004">
       <c r="A639" s="2" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B639" s="2">
         <v>3</v>
@@ -33050,14 +33050,14 @@
         <v>1</v>
       </c>
       <c r="L639" s="2" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="M639" s="2"/>
       <c r="N639" s="2"/>
     </row>
     <row r="640" spans="1:14" ht="307.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A640" s="2" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B640" s="2">
         <v>5</v>
@@ -33090,14 +33090,14 @@
         <v>0</v>
       </c>
       <c r="L640" s="2" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="M640" s="2"/>
       <c r="N640" s="2"/>
     </row>
     <row r="641" spans="1:14" ht="196.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A641" s="2" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B641" s="2">
         <v>2</v>
@@ -33130,14 +33130,14 @@
         <v>0</v>
       </c>
       <c r="L641" s="2" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="M641" s="2"/>
       <c r="N641" s="2"/>
     </row>
     <row r="642" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A642" s="2" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B642" s="2">
         <v>12</v>
@@ -33170,14 +33170,14 @@
         <v>0</v>
       </c>
       <c r="L642" s="2" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="M642" s="2"/>
       <c r="N642" s="2"/>
     </row>
     <row r="643" spans="1:14" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A643" s="2" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B643" s="2">
         <v>9</v>
@@ -33201,7 +33201,7 @@
         <v>0</v>
       </c>
       <c r="I643" s="2" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J643" s="2" t="s">
         <v>92</v>
@@ -33210,14 +33210,14 @@
         <v>0</v>
       </c>
       <c r="L643" s="2" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="M643" s="2"/>
       <c r="N643" s="2"/>
     </row>
     <row r="644" spans="1:14" ht="258.3" x14ac:dyDescent="0.55000000000000004">
       <c r="A644" s="2" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B644" s="2">
         <v>9</v>
@@ -33250,14 +33250,14 @@
         <v>0</v>
       </c>
       <c r="L644" s="2" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="M644" s="2"/>
       <c r="N644" s="2"/>
     </row>
     <row r="645" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A645" s="2" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B645" s="2">
         <v>8</v>
@@ -33290,14 +33290,14 @@
         <v>0</v>
       </c>
       <c r="L645" s="2" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="M645" s="2"/>
       <c r="N645" s="2"/>
     </row>
     <row r="646" spans="1:14" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A646" s="2" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B646" s="2">
         <v>4</v>
@@ -33330,14 +33330,14 @@
         <v>0</v>
       </c>
       <c r="L646" s="2" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M646" s="2"/>
       <c r="N646" s="2"/>
     </row>
     <row r="647" spans="1:14" ht="110.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A647" s="2" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B647" s="2">
         <v>1</v>
@@ -33370,18 +33370,18 @@
         <v>0</v>
       </c>
       <c r="L647" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="M647" s="2" t="s">
         <v>1680</v>
       </c>
-      <c r="M647" s="2" t="s">
-        <v>1681</v>
-      </c>
       <c r="N647" s="2" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="648" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A648" s="2" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B648" s="2">
         <v>2</v>
@@ -33414,18 +33414,18 @@
         <v>0</v>
       </c>
       <c r="L648" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="M648" s="2" t="s">
         <v>1683</v>
       </c>
-      <c r="M648" s="2" t="s">
-        <v>1684</v>
-      </c>
       <c r="N648" s="2" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="649" spans="1:14" ht="159.9" x14ac:dyDescent="0.55000000000000004">
       <c r="A649" s="2" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B649" s="2">
         <v>8</v>
@@ -33458,18 +33458,18 @@
         <v>0</v>
       </c>
       <c r="L649" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="M649" s="2" t="s">
         <v>1686</v>
       </c>
-      <c r="M649" s="2" t="s">
-        <v>1687</v>
-      </c>
       <c r="N649" s="2" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="650" spans="1:14" ht="61.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A650" s="2" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B650" s="2">
         <v>0</v>
@@ -33502,14 +33502,14 @@
         <v>0</v>
       </c>
       <c r="L650" s="2" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="M650" s="2"/>
       <c r="N650" s="2"/>
     </row>
     <row r="651" spans="1:14" ht="123" x14ac:dyDescent="0.55000000000000004">
       <c r="A651" s="2" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B651" s="2">
         <v>7</v>
@@ -33542,14 +33542,14 @@
         <v>0</v>
       </c>
       <c r="L651" s="2" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="M651" s="2"/>
       <c r="N651" s="2"/>
     </row>
     <row r="652" spans="1:14" ht="233.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A652" s="2" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="B652" s="2">
         <v>6</v>
@@ -33582,14 +33582,14 @@
         <v>0</v>
       </c>
       <c r="L652" s="2" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="M652" s="2"/>
       <c r="N652" s="2"/>
     </row>
     <row r="653" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A653" s="2" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B653" s="2">
         <v>1</v>
@@ -33622,14 +33622,14 @@
         <v>0</v>
       </c>
       <c r="L653" s="2" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="M653" s="2"/>
       <c r="N653" s="2"/>
     </row>
     <row r="654" spans="1:14" ht="98.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A654" s="2" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B654" s="2">
         <v>2</v>
@@ -33662,14 +33662,14 @@
         <v>1</v>
       </c>
       <c r="L654" s="2" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="M654" s="2"/>
       <c r="N654" s="2"/>
     </row>
     <row r="655" spans="1:14" ht="73.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A655" s="2" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B655" s="2">
         <v>1</v>
@@ -33702,14 +33702,14 @@
         <v>0</v>
       </c>
       <c r="L655" s="2" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="M655" s="2"/>
       <c r="N655" s="2"/>
     </row>
     <row r="656" spans="1:14" ht="135.30000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A656" s="2" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B656" s="2">
         <v>2</v>
@@ -33742,7 +33742,7 @@
         <v>0</v>
       </c>
       <c r="L656" s="2" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="M656" s="2"/>
       <c r="N656" s="2"/>

--- a/src/sheet.xlsx
+++ b/src/sheet.xlsx
@@ -107,7 +107,7 @@
     <t>Arcane</t>
   </si>
   <si>
-    <t>Choose up to five willing creatures you can see within range. Each teleports up to 30 feet to an unoccupied space it can see. Any creature that teleports this way can immediately use its reaction to make one weapon attack.</t>
+    <t>Choose up to five willing creatures you can see within range. Each teleports up to 30 feet to an unoccupied space it can see. Any creature that teleports this way can immediately use 1 AP to make one weapon attack.</t>
   </si>
   <si>
     <t>Sunder Sigil</t>
@@ -580,7 +580,7 @@
     <t>Mind</t>
   </si>
   <si>
-    <t>You whisper magical words that antagonize one creature of your choice within range. The target must make a Wits saving throw. On a failed save, the target takes 4d4 psychic damage and must immediately use its reaction to make a melee attack against another creature of your choice that you can see. If the target can’t make this attack (for example, because there is no one within its reach or because its reaction is unavailable), the target instead has disadvantage on the next attack roll it makes before the start of your next turn. On a successful save, the target takes half as much damage only.</t>
+    <t>You whisper magical words that antagonize one creature of your choice within range. The target must make a Wits saving throw. On a failed save, the target takes 4d4 psychic damage and must immediately use 1 AP to make a melee attack against another creature of your choice that you can see. If the target can’t make this attack (for example, because there is no one within its reach or because 1 AP is unavailable), the target instead has disadvantage on the next attack roll it makes before the start of your next turn. On a successful save, the target takes half as much damage only.</t>
   </si>
   <si>
     <t>At higher Mana Cost: You can expend extra mana to increase the effects of the glyph, the damage increases by 1d4 for every 3 additional mana expended.</t>
@@ -1891,7 +1891,7 @@
     <t>Dissonant Whispers</t>
   </si>
   <si>
-    <t>You whisper a discordant melody that only one creature of your choice within range can hear, wracking it with terrible pain. The target must make a wits saving throw. On a failed save, it takes 3d6 psychic damage and must immediately use its reaction, if available, to move as far as its speed allows away from you. The creature doesn't move into obviously dangerous ground, such as a fire or a pit. On a successful save, the target takes half as much damage and doesn't have to move away. A deafened creature automatically succeeds on the save.</t>
+    <t>You whisper a discordant melody that only one creature of your choice within range can hear, wracking it with terrible pain. The target must make a wits saving throw. On a failed save, it takes 3d6 psychic damage and must immediately use 1 AP, if available, to move as far as its speed allows away from you. The creature doesn't move into obviously dangerous ground, such as a fire or a pit. On a successful save, the target takes half as much damage and doesn't have to move away. A deafened creature automatically succeeds on the save.</t>
   </si>
   <si>
     <t>Distort Recollection</t>
@@ -1915,7 +1915,7 @@
     <t>Divine Aid</t>
   </si>
   <si>
-    <t>Until the glyph ends choose one of the following effects, the targets gain a +2 bonus to its AC and Strength, Dexterity and Constitution saving throws, Its movement speed increases by 30 feet, or it gains an additional reaction on each of its turns. In addition, when it is targeted by an attack or a glyph (including by an area of effect), the target can expend its reaction to move up to 30 feet, potentially avoiding the effect.</t>
+    <t>Until the glyph ends choose one of the following effects, the targets gain a +2 bonus to its AC and Strength, Dexterity and Constitution saving throws, Its movement speed increases by 30 feet, or it gains 1 additional AP on each of its turns. In addition, when it is targeted by an attack or a glyph (including by an area of effect), the target can expend 1 AP to move up to 30 feet, potentially avoiding the effect.</t>
   </si>
   <si>
     <t>When you cast this glyph using a glyph of Tier 6 you may choose one additional affect. When you cast this glyph using a glyph tier of 8 you gain all effects.</t>
@@ -2378,7 +2378,7 @@
     <t>Find Familiar</t>
   </si>
   <si>
-    <t>You gain the service of a familiar, a fallen that takes an animal form you choose: bat, cat, crab, frog (toad), hawk, lizard, octopus, owl, poisonous snake, fish (quipper), rat, raven, sea horse, spider, or weasel. Appearing in an unoccupied space within range, the familiar has the statistics of the chosen form, though it is a celestial, fey, or Netherkin (your choice) instead of a beast. Your familiar acts independently of you, but it always obeys your commands. In combat, it rolls its own initiative and acts on its own turn. A familiar can't attack, but it can take other actions as normal. When the familiar drops to 0 hit points, it disappears, leaving behind no physical form. It reappears after you cast this glyph again. While your familiar is within 100 feet of you, you can communicate with it telepathically. Additionally, as an action, you can see through your familiar's eyes and hear what it hears until the start of your next turn, gaining the benefits of any special senses that the familiar has. During this time, you are deaf and blind with regard to your own senses. As an action, you can temporarily dismiss your familiar. It disappears into a pocket dimension where it awaits your summons. Alternatively, you can dismiss it forever. As an action while it is temporarily dismissed, you can cause it to reappear in any unoccupied space within 30 feet of you. You can't have more than one familiar at a time. If you cast this glyph while you already have a familiar, you instead cause it to adopt a new form. Choose one of the forms from the above list. Your familiar transforms into the chosen creature. Finally, when you cast a glyph with a range of touch, your familiar can deliver the glyph as if it had cast the glyph. Your familiar must be within 100 feet of you, and it must use its reaction to deliver the glyph when you cast it. If the glyph requires an attack roll, you use your attack modifier for the roll.</t>
+    <t>You gain the service of a familiar, a fallen that takes an animal form you choose: bat, cat, crab, frog (toad), hawk, lizard, octopus, owl, poisonous snake, fish (quipper), rat, raven, sea horse, spider, or weasel. Appearing in an unoccupied space within range, the familiar has the statistics of the chosen form, though it is a celestial, fey, or Netherkin (your choice) instead of a beast. Your familiar acts independently of you, but it always obeys your commands. In combat, it rolls its own initiative and acts on its own turn. A familiar can't attack, but it can take other actions as normal. When the familiar drops to 0 hit points, it disappears, leaving behind no physical form. It reappears after you cast this glyph again. While your familiar is within 100 feet of you, you can communicate with it telepathically. Additionally, as an action, you can see through your familiar's eyes and hear what it hears until the start of your next turn, gaining the benefits of any special senses that the familiar has. During this time, you are deaf and blind with regard to your own senses. As an action, you can temporarily dismiss your familiar. It disappears into a pocket dimension where it awaits your summons. Alternatively, you can dismiss it forever. As an action while it is temporarily dismissed, you can cause it to reappear in any unoccupied space within 30 feet of you. You can't have more than one familiar at a time. If you cast this glyph while you already have a familiar, you instead cause it to adopt a new form. Choose one of the forms from the above list. Your familiar transforms into the chosen creature. Finally, when you cast a glyph with a range of touch, your familiar can deliver the glyph as if it had cast the glyph. Your familiar must be within 100 feet of you, and it must use 1 AP to deliver the glyph when you cast it. If the glyph requires an attack roll, you use your attack modifier for the roll.</t>
   </si>
   <si>
     <t>Find Greater Steed</t>
@@ -4041,7 +4041,7 @@
     <t>Power Word Heal</t>
   </si>
   <si>
-    <t>A wave of healing energy washes over the creature you touch. The target regains all its hit points. If the creature is charmed, frightened, paralyzed, or stunned, the condition ends. If the creature is prone, it can use its reaction to stand up. This glyph has no effect on fallen or constructs.</t>
+    <t>A wave of healing energy washes over the creature you touch. The target regains all its hit points. If the creature is charmed, frightened, paralyzed, or stunned, the condition ends. If the creature is prone, it can use 1 AP to stand up. This glyph has no effect on fallen or constructs.</t>
   </si>
   <si>
     <t>Power Word Kill</t>
@@ -5382,7 +5382,7 @@
     <t>Wall of Stone</t>
   </si>
   <si>
-    <t>A nonmagical wall of solid stone springs into existence at a point you choose within range. The wall is 6 inches thick and is composed of ten 10-foot-by-10-foot panels. Each panel must be contiguous wilh at least one other panel. Alternatively, you can create 10-foot-by-20-foot panels that are only 3 inches thick. If the wall cuts through a creature's space when it appears, the creature is pushed to one side of the wall (your choice). If a creature would be surrounded on all sides by the wall (or the wall and another solid surface), that creature can make a agility saving throw. On a success, it can use its reaction to move up to its speed so that it is no longer enclosed by the wall. The wall can have any shape you desire, though it can't occupy the same space as a creature or object. The wall doesn't need to be vertical or rest on any firm foundation. It must, however, merge with and be solidly supported by existing stone. Thus, you can use this glyph to bridge a chasm or create a ramp. If you create a span greater than 20 feet in length, you must halve the size of each panel to create supports. You can crudely shape the wall to create crenellations, battlements, and so on. The wall is an object made of stone that can be damaged and thus breached. Each panel has AC 15 and 30 hit points per inch of thickness. Reducing a panel to 0 hit points destroys it and might cause connected panels to collapse at the DM's discretion. If you maintain your concentration on this glyph for its whole duration, the wall becomes permanent and can't be dispelled. Otherwise, the wall disappears when the glyph ends.</t>
+    <t>A nonmagical wall of solid stone springs into existence at a point you choose within range. The wall is 6 inches thick and is composed of ten 10-foot-by-10-foot panels. Each panel must be contiguous wilh at least one other panel. Alternatively, you can create 10-foot-by-20-foot panels that are only 3 inches thick. If the wall cuts through a creature's space when it appears, the creature is pushed to one side of the wall (your choice). If a creature would be surrounded on all sides by the wall (or the wall and another solid surface), that creature can make a agility saving throw. On a success, it can use 1 AP to move up to its speed so that it is no longer enclosed by the wall. The wall can have any shape you desire, though it can't occupy the same space as a creature or object. The wall doesn't need to be vertical or rest on any firm foundation. It must, however, merge with and be solidly supported by existing stone. Thus, you can use this glyph to bridge a chasm or create a ramp. If you create a span greater than 20 feet in length, you must halve the size of each panel to create supports. You can crudely shape the wall to create crenellations, battlements, and so on. The wall is an object made of stone that can be damaged and thus breached. Each panel has AC 15 and 30 hit points per inch of thickness. Reducing a panel to 0 hit points destroys it and might cause connected panels to collapse at the DM's discretion. If you maintain your concentration on this glyph for its whole duration, the wall becomes permanent and can't be dispelled. Otherwise, the wall disappears when the glyph ends.</t>
   </si>
   <si>
     <t>Wall of Thorns</t>
@@ -14439,7 +14439,7 @@
       <c r="K203" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="L203" s="12" t="s">
+      <c r="L203" s="13" t="s">
         <v>586</v>
       </c>
       <c r="M203" s="12" t="s">

--- a/src/sheet.xlsx
+++ b/src/sheet.xlsx
@@ -107,7 +107,7 @@
     <t>Arcane</t>
   </si>
   <si>
-    <t>Choose up to five willing creatures you can see within range. Each teleports up to 30 feet to an unoccupied space it can see. Any creature that teleports this way can immediately use 1 AP to make one weapon attack.</t>
+    <t>Choose up to five willing creatures you can see within range. Each teleports up to 30 feet to an unoccupied space it can see. Any creature that teleports this way can immediately use its reaction to make one weapon attack.</t>
   </si>
   <si>
     <t>Sunder Sigil</t>
@@ -161,7 +161,7 @@
   <si>
     <t>You split a lance of interlaced frost and flame into two bolts. Make a separate ranged spell attack for each bolt against one or two creatures you can see within range. On each hit, choose the damage profile for that bolt:
  Rime. The bolt explodes in hoarfrost, dealing 3d8 cold damage. The target’s speed is reduced by 10 feet and it can’t take reactions until the start of your next turn.
- Fire. The bolt detonates in cinders, dealing 3d8 fire damage. The target ignites; at the start of its next turn it takes 2d6 fire damage, then the flames gutter out. A creature can end the ignition early by using its action to douse itself or by taking any cold damage.
+ Fire. The bolt detonates in cinders, dealing 3d8 fire damage. The target ignites; at the start of its next turn it takes 2d6 fire damage, then the flames gutter out. A creature can end the ignition early by spending 2 AP to douse itself or by taking any cold damage.
  Elemental Detonation (both bolts on one target). If both bolts hit the same creature this turn, the conflicting energies make it explode in a rimefire burst. Immediately after resolving the second hit, the target and every creature within 10 feet of it must make a Agility saving throw against your glyph save DC. The target automatically fails this save.
  On a failure, a creature takes 2d6 cold + 2d6 fire damage and is knocked prone.
  On a success, a creature takes half as much damage and isn’t knocked prone.</t>
@@ -381,7 +381,7 @@
     <t>Agron's Storm Armor</t>
   </si>
   <si>
-    <t>You channel your arcane energy, creating a protective aura of crackling lightning that surrounds you until the glyph ends. Your base AC becomes 15 + your Agility modifier. The glyph ends if you don armor or dismiss it as an action. While this aura is active, your movement speed increases by 20 feet. Additionally, any creature that starts its turn within 5 feet of you must make a Agility saving throw. On a failed save, the creature takes 4d4 lightning damage, or half as much damage on a successful save.</t>
+    <t>You channel your arcane energy, creating a protective aura of crackling lightning that surrounds you until the glyph ends. Your base AC becomes 15 + your Agility modifier. The glyph ends if you don armor or dismiss it by spending 2 AP. While this aura is active, your movement speed increases by 20 feet. Additionally, any creature that starts its turn within 5 feet of you must make a Agility saving throw. On a failed save, the creature takes 4d4 lightning damage, or half as much damage on a successful save.</t>
   </si>
   <si>
     <t>When you cast this Glyph using 21 or more mana, the extra damage increases by 2d4 and the movement speed increases by 10 feet, for every 6 additional mana expended.</t>
@@ -470,7 +470,7 @@
     <t>Up to 1 hour</t>
   </si>
   <si>
-    <t>You assume a different form. When you cast the glyph, choose one of the following options, the effects of which last for the duration of the glyph. While the glyph lasts, you can end one option as an action to gain the benefits of a different one. Aquatic Adaptation. You adapt your body to an aquatic environment, sprouting gills and growing webbing between your fingers. You can breathe underwater and gain a swimming speed equal to your walking speed. Change Appearance. You transform your appearance. You decide what you look like, including your height, weight, facial features, sound of your voice, hair length, coloration, and distinguishing characteristics, if any. You can make yourself appear as a member of another race, though none of your statistics change. You also can't appear as a creature of a different size than you, and your basic shape stays the same; if you're bipedal, you can't use this glyph to become quadrupedal, for instance. At any time for the duration of the glyph, you can use your action to change your appearance in this way again. Natural Weapons. You grow claws, fangs, spines, horns, or a different natural weapon of your choice. Your unarmed strikes deal 1d6 bludgeoning, piercing, or slashing damage, as appropriate to the natural weapon you chose, and you are proficient with your unarmed strikes. Finally, the natural weapon you have is magic and you have a +1 bonus to the attack and damage rolls you make using it.</t>
+    <t>You assume a different form. When you cast the glyph, choose one of the following options, the effects of which last for the duration of the glyph. While the glyph lasts, you can end one option by spending 2 AP to gain the benefits of a different one. Aquatic Adaptation. You adapt your body to an aquatic environment, sprouting gills and growing webbing between your fingers. You can breathe underwater and gain a swimming speed equal to your walking speed. Change Appearance. You transform your appearance. You decide what you look like, including your height, weight, facial features, sound of your voice, hair length, coloration, and distinguishing characteristics, if any. You can make yourself appear as a member of another race, though none of your statistics change. You also can't appear as a creature of a different size than you, and your basic shape stays the same; if you're bipedal, you can't use this glyph to become quadrupedal, for instance. At any time for the duration of the glyph, you can spend 2 AP to change your appearance in this way again. Natural Weapons. You grow claws, fangs, spines, horns, or a different natural weapon of your choice. Your unarmed strikes deal 1d6 bludgeoning, piercing, or slashing damage, as appropriate to the natural weapon you chose, and you are proficient with your unarmed strikes. Finally, the natural weapon you have is magic and you have a +1 bonus to the attack and damage rolls you make using it.</t>
   </si>
   <si>
     <t>Amputation</t>
@@ -536,7 +536,7 @@
     <t>Up to 24 hours</t>
   </si>
   <si>
-    <t>Your magic turns others into beasts. Choose any number of willing creatures that you can see within range. You transform each target into the form of a Large or smaller beast with a challenge rating of 4 or lower. On subsequent turns, you can use your action to transform affected creatures into new forms. The transformation lasts for the duration for each target, or until the target drops to 0 hit points or dies. You can choose a different form for each target. A target's game statistics are replaced by the statistics of the chosen beast, though the target retains its alignment and mind, wits, and wellspring scores. The target assumes the hit points of its new form, and when it reverts to its normal form, it returns to the number of hit points it had before it transformed. If it reverts as a result of dropping to 0 hit points, any excess damage carries over to its normal form. As long as the excess damage doesn't reduce the creature's normal form to 0 hit points, it isn't knocked unconscious. The creature is limited in the actions it can perform by the nature of its new form, and it can't speak or cast glyphs. The target's gear melds into the new form. The target can't activate, wield, or otherwise benefit from any of its equipment.</t>
+    <t>Your magic turns others into beasts. Choose any number of willing creatures that you can see within range. You transform each target into the form of a Large or smaller beast with a challenge rating of 4 or lower. On subsequent turns, you can spend 2 AP to transform affected creatures into new forms. The transformation lasts for the duration for each target, or until the target drops to 0 hit points or dies. You can choose a different form for each target. A target's game statistics are replaced by the statistics of the chosen beast, though the target retains its alignment and mind, wits, and wellspring scores. The target assumes the hit points of its new form, and when it reverts to its normal form, it returns to the number of hit points it had before it transformed. If it reverts as a result of dropping to 0 hit points, any excess damage carries over to its normal form. As long as the excess damage doesn't reduce the creature's normal form to 0 hit points, it isn't knocked unconscious. The creature is limited in the actions it can perform by the nature of its new form, and it can't speak or cast glyphs. The target's gear melds into the new form. The target can't activate, wield, or otherwise benefit from any of its equipment.</t>
   </si>
   <si>
     <t>Animate Dead</t>
@@ -545,7 +545,7 @@
     <t>10 feet</t>
   </si>
   <si>
-    <t>This glyph creates an fallen servant. Choose a pile of bones or a corpse of a Medium or Small humanoid within range. Your glyph imbues the target with a foul mimicry of life, raising it as an fallen creature. The target becomes a fallen if you chose bones or a fallen if you chose a corpse (the DM has the creature's game statistics). On each of your turns, you can use a bonus action to mentally command any creature you made with this glyph if the creature is within 60 feet of you (if you control multiple creatures, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a general command, such as to guard a particular chamber or corridor. If you issue no commands, the creature only defends itself against hostile creatures. Once given an order, the creature continues to follow it until the task is complete. The creature is under your control for 24 hours, after which it stops obeying any command you've given it. To maintain control of the creature for another 24 hours, you must cast this glyph on the creature again before the current 24-hour period ends. This use of the glyph reasserts your control ovre up to four creatures you have animated with this glyph, rather than animating a new one.</t>
+    <t>This glyph creates an fallen servant. Choose a pile of bones or a corpse of a Medium or Small humanoid within range. Your glyph imbues the target with a foul mimicry of life, raising it as an fallen creature. The target becomes a fallen if you chose bones or a fallen if you chose a corpse (the DM has the creature's game statistics). On each of your turns, you can spend 1 AP to mentally command any creature you made with this glyph if the creature is within 60 feet of you (if you control multiple creatures, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a general command, such as to guard a particular chamber or corridor. If you issue no commands, the creature only defends itself against hostile creatures. Once given an order, the creature continues to follow it until the task is complete. The creature is under your control for 24 hours, after which it stops obeying any command you've given it. To maintain control of the creature for another 24 hours, you must cast this glyph on the creature again before the current 24-hour period ends. This use of the glyph reasserts your control ovre up to four creatures you have animated with this glyph, rather than animating a new one.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 4th level or higher, you animate or reassert control over two additional creatures for each slot level above 3rd. Each of the creatures must come from a different corpse or pile of bones.</t>
@@ -565,7 +565,7 @@
     <t>Up to 1 minute</t>
   </si>
   <si>
-    <t>Objects come to life at your command. Choose up to ten nonmagical objects within range that are not being worn or carried. Medium targets count as two objects, Large targets count as four objects, Huge targets count as eight objects. You can't animate any object larger than Huge. Each target animates and becomes a creature under your control until the glyph ends or until reduced to 0 hit points. As a bonus action, you can mentally command any creature you made with this glyph if the creature is within 500 feet of you (if you control multiple creatures, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a general command, such as to guard a particular chamber or corridor. If you issue no commands, the creature only defends itself against hostile creatures. Once given an order, the creature continues to follow it until its task is complete. An animated object is a construct with AC, hit points, attacks, Strength, and agility determined by its size. Its Constitution is 10 and its mind and wits are 3, and its wellspring is 1. Its speed is 30 feet; if the object lacks legs or other appendages it can use for locomotion, it instead has a flying speed of 30 feet and can hover. If the object is securely attached to a surface or a larger object, such as a chain bolted to a wall, its speed is 0. It has blindsight with a radius of 30 feet and is blind beyond that distance. When the animated object drops to 0 hit points, it reverts to its original object form, and any remaining damage carries over to its original object form. If you command an object to attack, it can make a single melee attack against a creature within 5 feet of it. It makes a slam attack with an attack bonus and bludgeoning damage determined by its size. The DM might rule that a specific object inflicts slashing or piercing damage based on its form.</t>
+    <t>Objects come to life at your command. Choose up to ten nonmagical objects within range that are not being worn or carried. Medium targets count as two objects, Large targets count as four objects, Huge targets count as eight objects. You can't animate any object larger than Huge. Each target animates and becomes a creature under your control until the glyph ends or until reduced to 0 hit points. by spending 1 AP, you can mentally command any creature you made with this glyph if the creature is within 500 feet of you (if you control multiple creatures, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a general command, such as to guard a particular chamber or corridor. If you issue no commands, the creature only defends itself against hostile creatures. Once given an order, the creature continues to follow it until its task is complete. An animated object is a construct with AC, hit points, attacks, Strength, and agility determined by its size. Its Constitution is 10 and its mind and wits are 3, and its wellspring is 1. Its speed is 30 feet; if the object lacks legs or other appendages it can use for locomotion, it instead has a flying speed of 30 feet and can hover. If the object is securely attached to a surface or a larger object, such as a chain bolted to a wall, its speed is 0. It has blindsight with a radius of 30 feet and is blind beyond that distance. When the animated object drops to 0 hit points, it reverts to its original object form, and any remaining damage carries over to its original object form. If you command an object to attack, it can make a single melee attack against a creature within 5 feet of it. It makes a slam attack with an attack bonus and bludgeoning damage determined by its size. The DM might rule that a specific object inflicts slashing or piercing damage based on its form.</t>
   </si>
   <si>
     <t>If you cast this Glyph using a Glyph slot of 6th level or higher, you can animate two additional objects for each slot level above 5th.</t>
@@ -580,7 +580,7 @@
     <t>Mind</t>
   </si>
   <si>
-    <t>You whisper magical words that antagonize one creature of your choice within range. The target must make a Wits saving throw. On a failed save, the target takes 4d4 psychic damage and must immediately use 1 AP to make a melee attack against another creature of your choice that you can see. If the target can’t make this attack (for example, because there is no one within its reach or because 1 AP is unavailable), the target instead has disadvantage on the next attack roll it makes before the start of your next turn. On a successful save, the target takes half as much damage only.</t>
+    <t>You whisper magical words that antagonize one creature of your choice within range. The target must make a Wits saving throw. On a failed save, the target takes 4d4 psychic damage and must immediately use its reaction to make a melee attack against another creature of your choice that you can see. If the target can’t make this attack (for example, because there is no one within its reach or because its reaction is unavailable), the target instead has disadvantage on the next attack roll it makes before the start of your next turn. On a successful save, the target takes half as much damage only.</t>
   </si>
   <si>
     <t>At higher Mana Cost: You can expend extra mana to increase the effects of the glyph, the damage increases by 1d4 for every 3 additional mana expended.</t>
@@ -668,7 +668,7 @@
     <t>500 feet</t>
   </si>
   <si>
-    <t>You create linked teleportation portals that remain open for the duration. Choose two points on the ground that you can see, one point within 10 feet of you and one point within 500 feet of you. A circular portal, 10 feet in diameter, opens over each point. If the portal would open in the space occupied by a creature, the glyph fails, and the casting is lost. The portals are two dimensional glowing rings filled with mist, hovering inches from the ground and perpendicular to it at the points you choose. A ring is visible only from one side (your choice), which is the side that functions as a portal. Any creature or object entering the portal exits from the other portal as if the two were adjacent to each other; passing through a portal from the nonportal side has no effect. The mist that fills each portal is opaque and blocks vision through it. On your turn, you can rotate the rings as a bonus action so that the active side faces in a different direction.</t>
+    <t>You create linked teleportation portals that remain open for the duration. Choose two points on the ground that you can see, one point within 10 feet of you and one point within 500 feet of you. A circular portal, 10 feet in diameter, opens over each point. If the portal would open in the space occupied by a creature, the glyph fails, and the casting is lost. The portals are two dimensional glowing rings filled with mist, hovering inches from the ground and perpendicular to it at the points you choose. A ring is visible only from one side (your choice), which is the side that functions as a portal. Any creature or object entering the portal exits from the other portal as if the two were adjacent to each other; passing through a portal from the nonportal side has no effect. The mist that fills each portal is opaque and blocks vision through it. On your turn, you can rotate the rings by spending 1 AP so that the active side faces in a different direction.</t>
   </si>
   <si>
     <t>Arcane Key</t>
@@ -709,7 +709,7 @@
     <t>Armor of the Red Prince</t>
   </si>
   <si>
-    <t>You touch a willing creature, enveloping them in a protective layer of force imbued with fiery energy. The target's Armor Class increases by +2 for the duration. Additionally, any creature that hits the target with a melee attack takes 1d6 fire damage. You can dismiss this glyph as a bonus action.</t>
+    <t>You touch a willing creature, enveloping them in a protective layer of force imbued with fiery energy. The target's Armor Class increases by +2 for the duration. Additionally, any creature that hits the target with a melee attack takes 1d6 fire damage. You can dismiss this glyph by spending 1 AP.</t>
   </si>
   <si>
     <t>At Higher Mana Cost: You can expend extra mana to increase the effects of the glyph, the damage increases by 1d6 for every 3 additional mana expended. If you expend an additional 9 mana the armor class bonus increases to +3. If you expend 13 additional mana the armor class bonus increases to +4.</t>
@@ -739,7 +739,7 @@
     <t>Astrions's Mind Whip</t>
   </si>
   <si>
-    <t>You psychically lash out at one creature you can see within range. The target must make an mind saving throw. On a failed save, the target takes 3d6 psychic damage, and it can't take a reaction until the end of its next turn. Moreover, on its next turn, it must choose whether it gets a move, an action, or a bonus action; it gets only one of the three. On a successful save, the target takes half as much damage and suffers none of the glyph's other effects.</t>
+    <t>You psychically lash out at one creature you can see within range. The target must make an mind saving throw. On a failed save, the target takes 3d6 psychic damage, and it can't take a reaction until the end of its next turn. Moreover, on its next turn, it must choose whether it gets a move, spends 2 AP, or spends 1 AP; it gets only one of the three. On a successful save, the target takes half as much damage and suffers none of the glyph's other effects.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 3rd level or higher, you can target one additional creature for each slot level above 2nd. The creatures must be within 30 feet of each other when you target them.</t>
@@ -763,7 +763,7 @@
     <t>Aura of Vitality</t>
   </si>
   <si>
-    <t>Healing energy radiates from you in an aura with a 30-foot radius. Until the glyph ends, the aura moves with you, centered on you. You can use a bonus action to cause one creature in the aura (including you) to regain 2d6 hit points.</t>
+    <t>Healing energy radiates from you in an aura with a 30-foot radius. Until the glyph ends, the aura moves with you, centered on you. You can spend 1 AP to cause one creature in the aura (including you) to regain 2d6 hit points.</t>
   </si>
   <si>
     <t>Awaken</t>
@@ -841,13 +841,13 @@
     <t>Beast Sense</t>
   </si>
   <si>
-    <t>You touch a willing beast. For the duration of the glyph, you can use your action to see through the beast's eyes and hear what it hears, and continue to do so until you use your action to return to your normal senses. While perceiving through the beast's senses, you gain the benefits of any special senses possessed by that creature, though you are blinded and deafened to your own surroundings.</t>
+    <t>You touch a willing beast. For the duration of the glyph, you can spend 2 AP to see through the beast's eyes and hear what it hears, and continue to do so until you spend 2 AP to return to your normal senses. While perceiving through the beast's senses, you gain the benefits of any special senses possessed by that creature, though you are blinded and deafened to your own surroundings.</t>
   </si>
   <si>
     <t>Bell of Judgment</t>
   </si>
   <si>
-    <t>You conjure a massive, radiant bell in an unoccupied space you can see within range. The bell is Large, glowing with divine light, and hums with celestial resonance. When the glyph is cast, and again on each of your turns as an action, you may cause the bell to toll.
+    <t>You conjure a massive, radiant bell in an unoccupied space you can see within range. The bell is Large, glowing with divine light, and hums with celestial resonance. When the glyph is cast, and again on each of your turns by spending 2 AP, you may cause the bell to toll.
  When the bell tolls, you choose any number of creatures within 60 feet of the bell. Each chosen creature must make a Constitution saving throw. On a failed save, the creature takes 3d8 thunder damage and 3d8 radiant damage, and is deafened for the duration of the glyph. On a successful save, the creature takes half damage and is not deafened.
  Netherkin and undead have disadvantage on this saving throw, as the bell’s radiant resonance tears at their corrupted essence.
  A deafened creature can repeat the saving throw at the end of each of its turns, ending the deafened condition on a success.
@@ -898,7 +898,7 @@
     <t>Blade of Disaster</t>
   </si>
   <si>
-    <t>You create a blade-shaped planar rift about 3 feet long in an unoccupied space you can see within range. The blade lasts for the duration. When you cast this glyph, you can make up to two melee glyph attacks with the blade, each one against a creature, loose object, or structure within 5 feet of the blade. On a hit, the target takes 4d12 force damage. This attack scores a critical hit if the number on the d20 is 18 or higher. On a critical hit, the blade deals an extra 8d12 force damage (for a total of 12d12 force damage). As a bonus action on your turn, you can move the blade up to 30 feet to an unoccupied space you can see and then make up to two melee glyph attacks with it again. The blade can harmlessly pass through any barrier, including a wall of force.</t>
+    <t>You create a blade-shaped planar rift about 3 feet long in an unoccupied space you can see within range. The blade lasts for the duration. When you cast this glyph, you can make up to two melee glyph attacks with the blade, each one against a creature, loose object, or structure within 5 feet of the blade. On a hit, the target takes 4d12 force damage. This attack scores a critical hit if the number on the d20 is 18 or higher. On a critical hit, the blade deals an extra 8d12 force damage (for a total of 12d12 force damage). by spending 1 AP on your turn, you can move the blade up to 30 feet to an unoccupied space you can see and then make up to two melee glyph attacks with it again. The blade can harmlessly pass through any barrier, including a wall of force.</t>
   </si>
   <si>
     <t>Blade Ward</t>
@@ -916,7 +916,7 @@
     <t>Blades of Shielding Blizzard</t>
   </si>
   <si>
-    <t>You conjure two blades of ice that hover around you for the duration, or until you use them to attack. While these ice blades are hovering around you, your Armor Class increases by +1 for each blade. As a bonus action on the turn you create them, and on each of your subsequent turns, you can send one of the blades flying toward a creature you can see within 60 feet of you. Make a ranged glyph attack against the target. On a hit, the target takes 1d8 slashing damage plus 2d8 cold damage. The blade shatters upon hitting the target or reaching the end of its range, and is lost. Additionally, when you take damage while at least one blade is hovering around you, you can use your reaction to sacrifice any number of your remaining ice blades. For each blade you sacrifice, you reduce the damage by 1d8.</t>
+    <t>You conjure two blades of ice that hover around you for the duration, or until you use them to attack. While these ice blades are hovering around you, your Armor Class increases by +1 for each blade. by spending 1 AP on the turn you create them, and on each of your subsequent turns, you can send one of the blades flying toward a creature you can see within 60 feet of you. Make a ranged glyph attack against the target. On a hit, the target takes 1d8 slashing damage plus 2d8 cold damage. The blade shatters upon hitting the target or reaching the end of its range, and is lost. Additionally, when you take damage while at least one blade is hovering around you, you can use your reaction to sacrifice any number of your remaining ice blades. For each blade you sacrifice, you reduce the damage by 1d8.</t>
   </si>
   <si>
     <t>At Higher Mana Cost: You can expend extra mana to increase the effects of the glyph, you conjure one additional ice blade for every 3 additional mana expended.</t>
@@ -998,7 +998,7 @@
     <t>Bones of the Earth</t>
   </si>
   <si>
-    <t>You cause up to six pillars of stone to burst from places on the ground that you can see within range. Each pillar is a cylinder that has a diameter of 5 feet and a height of up to 30 feet. The ground where a pillar appears must be wide enough for its diameter, and you can target the ground under a creature if that creature is Medium or smaller. Each pillar has AC 5 and 30 hit points. When reduced to 0 hit points, a pillar crumbles into rubble, which creates an area of difficult terrain with a 10-foot radius that lasts until the rubble is cleared. Each 5-foot-diameter portion of the area requires at least 1 minute to clear by hand. If a pillar is created under a creature, that creature must succeed on a agility saving throw or be lifted by the pillar. A creature can choose to fail the save. If a pillar is prevented from reaching its full height because of a ceiling or other obstacle, a creature on the pillar takes 6d6 bludgeoning damage and is restrained, pinched between the pillar and the obstacle. The restrained creature can use an action to make a Strength or agility check (the creature's choice) against the glyph's save DC. On a success, the creature is no longer restrained and must either move off the pillar or fall off it.</t>
+    <t>You cause up to six pillars of stone to burst from places on the ground that you can see within range. Each pillar is a cylinder that has a diameter of 5 feet and a height of up to 30 feet. The ground where a pillar appears must be wide enough for its diameter, and you can target the ground under a creature if that creature is Medium or smaller. Each pillar has AC 5 and 30 hit points. When reduced to 0 hit points, a pillar crumbles into rubble, which creates an area of difficult terrain with a 10-foot radius that lasts until the rubble is cleared. Each 5-foot-diameter portion of the area requires at least 1 minute to clear by hand. If a pillar is created under a creature, that creature must succeed on a agility saving throw or be lifted by the pillar. A creature can choose to fail the save. If a pillar is prevented from reaching its full height because of a ceiling or other obstacle, a creature on the pillar takes 6d6 bludgeoning damage and is restrained, pinched between the pillar and the obstacle. The restrained creature can spend 2 AP to make a Strength or agility check (the creature's choice) against the glyph's save DC. On a success, the creature is no longer restrained and must either move off the pillar or fall off it.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 7th level or higher, you can create two additional pillars for each slot level above 6th.</t>
@@ -1078,13 +1078,13 @@
     <t>Cache Wellspring</t>
   </si>
   <si>
-    <t>Your body falls into a catatonic state as your soul leaves it and enters the container you used for the glyph's material component. While your soul inhabits the container, you are aware of your surroundings as if you were in the container's space. You can't move or use reactions. The only action you can take is to project your soul up to 100 feet out of the container, either returning to your living body (and ending the glyph) or attempting to possess a humanoids body. You can attempt to possess any humanoid within 100 feet of you that you can see (creatures warded by a protection from evil and good or magic circle glyph can't be possessed). The target must make a wellspring saving throw. On a failure, your soul moves into the target's body, and the target's soul becomes trapped in the container. On a success, the target resists your efforts to possess it, and you can't attempt to possess it again for 24 hours. Once you possess a creature's body, you control it. Your game statistics are replaced by the statistics of the creature, though you retain your alignment and your mind, wits, and wellspring scores. You retain the benefit of your own class features. If the target has any class levels, you can't use any of its class features. Meanwhile, the possessed creature's soul can perceive from the container using its own senses, but it can't move or take actions at all. While possessing a body, you can use your action to return from the host body to the container if it is within 100 feet of you, returning the host creature's soul to its body. If the host body dies while you're in it, the creature dies, and you must make a wellspring saving throw against your own spellcasting DC. On a success, you return to the container if it is within 100 feet of you. Otherwise, you die. If the container is destroyed or the glyph ends, your soul immediately returns to your body. If your body is more than 100 feet away from you or if your body is dead when you attempt to return to it, you die. If another creature's soul is in the container when it is destroyed, the creature's soul returns to its body if the body is alive and within 100 feet. Otherwise, that creature dies. When the glyph ends, the container is destroyed.</t>
+    <t>Your body falls into a catatonic state as your soul leaves it and enters the container you used for the glyph's material component. While your soul inhabits the container, you are aware of your surroundings as if you were in the container's space. You can't move or use reactions. The only action you can take is to project your soul up to 100 feet out of the container, either returning to your living body (and ending the glyph) or attempting to possess a humanoids body. You can attempt to possess any humanoid within 100 feet of you that you can see (creatures warded by a protection from evil and good or magic circle glyph can't be possessed). The target must make a wellspring saving throw. On a failure, your soul moves into the target's body, and the target's soul becomes trapped in the container. On a success, the target resists your efforts to possess it, and you can't attempt to possess it again for 24 hours. Once you possess a creature's body, you control it. Your game statistics are replaced by the statistics of the creature, though you retain your alignment and your mind, wits, and wellspring scores. You retain the benefit of your own class features. If the target has any class levels, you can't use any of its class features. Meanwhile, the possessed creature's soul can perceive from the container using its own senses, but it can't move or take actions at all. While possessing a body, you can spend 2 AP to return from the host body to the container if it is within 100 feet of you, returning the host creature's soul to its body. If the host body dies while you're in it, the creature dies, and you must make a wellspring saving throw against your own spellcasting DC. On a success, you return to the container if it is within 100 feet of you. Otherwise, you die. If the container is destroyed or the glyph ends, your soul immediately returns to your body. If your body is more than 100 feet away from you or if your body is dead when you attempt to return to it, you die. If another creature's soul is in the container when it is destroyed, the creature's soul returns to its body if the body is alive and within 100 feet. Otherwise, that creature dies. When the glyph ends, the container is destroyed.</t>
   </si>
   <si>
     <t>Call Lightning</t>
   </si>
   <si>
-    <t>A storm cloud appears in the shape of a cylinder that is 10 feet tall with a 60-foot radius, centered on a point you can see 100 feet directly above you. The glyph fails if you can't see a point in the air where the storm cloud could appear (for example, if you are in a room that can't accommodate the cloud). When you cast the glyph, choose a point you can see within range. A ball of lightning flashes down from the cloud to that point. Each creature within 5 feet of that point must make a agility saving throw. A creature takes 3d10 lightning damage on a failed save, or half as much damage on a successful one. On each of your turns until the glyph ends, you can use your action to call down lightning in this way again, targeting the same point or a different one. If you are outdoors in stormy conditions when you cast this glyph, the glyph gives you control over the existing storm instead of creating a new one. Under such conditions, the glyph's damage increases by 1d10.</t>
+    <t>A storm cloud appears in the shape of a cylinder that is 10 feet tall with a 60-foot radius, centered on a point you can see 100 feet directly above you. The glyph fails if you can't see a point in the air where the storm cloud could appear (for example, if you are in a room that can't accommodate the cloud). When you cast the glyph, choose a point you can see within range. A ball of lightning flashes down from the cloud to that point. Each creature within 5 feet of that point must make a agility saving throw. A creature takes 3d10 lightning damage on a failed save, or half as much damage on a successful one. On each of your turns until the glyph ends, you can spend 2 AP to call down lightning in this way again, targeting the same point or a different one. If you are outdoors in stormy conditions when you cast this glyph, the glyph gives you control over the existing storm instead of creating a new one. Under such conditions, the glyph's damage increases by 1d10.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 4th level or higher, the damage increases by 1d10 for each slot level above 3rd.</t>
@@ -1108,7 +1108,7 @@
     <t>Catnap</t>
   </si>
   <si>
-    <t>You make a calming gesture, and up to three willing creatures of your choice that you can see within range fall unconscious for the glyph’s duration. The glyph ends on a target early if it takes damage or someone uses an action to shake or slap it awake. If a target remains unconscious for the full duration, that target gains the benefit of a short rest, and it can’t be affected by this glyph again until it finishes a long rest.</t>
+    <t>You make a calming gesture, and up to three willing creatures of your choice that you can see within range fall unconscious for the glyph’s duration. The glyph ends on a target early if it takes damage or someone spends 2 AP to shake or slap it awake. If a target remains unconscious for the full duration, that target gains the benefit of a short rest, and it can’t be affected by this glyph again until it finishes a long rest.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 4th level or higher, you can target one additional willing creature for each slot level above 3rd.</t>
@@ -1314,7 +1314,7 @@
     <t>Compulsion</t>
   </si>
   <si>
-    <t>Creatures of your choice that you can see within range and that can hear you must make a wits saving throw. A target automatically succeeds on this saving throw if it can't be charmed. On a failed save, a target is affected by this spelI. Until the speIl ends, you can use a bonus action on each of your turns to designate a direction that is horizontal to you. Each affected target must use as much of its movement as possible to move in that direction on its next turn. It can take its action before it moves. After moving in this way, it can make another wits saving to try to end the effect. A target isn't compelled to move into an obviously deadly hazard, such as a fire or pit, but it will provoke opportunity attacks to move in the designated direction.</t>
+    <t>Creatures of your choice that you can see within range and that can hear you must make a wits saving throw. A target automatically succeeds on this saving throw if it can't be charmed. On a failed save, a target is affected by this spelI. Until the speIl ends, you can spend 1 AP on each of your turns to designate a direction that is horizontal to you. Each affected target must use as much of its movement as possible to move in that direction on its next turn. It can spend 2 AP before it moves. After moving in this way, it can make another wits saving to try to end the effect. A target isn't compelled to move into an obviously deadly hazard, such as a fire or pit, but it will provoke opportunity attacks to move in the designated direction.</t>
   </si>
   <si>
     <t>Cone of Cold</t>
@@ -1401,7 +1401,7 @@
     <t>Contact Other Plane</t>
   </si>
   <si>
-    <t>You mentally contact a demigod, the fallen of a long-dead sage, or some other mysterious entity from another plane. Contacting this extraplanar mind can strain or even break your mind. When you cast this glyph, make a DC 15 lntelligence saving throw. On a failure, you take 6d6 psychic damage and are insane until you finish a long rest. While insane, you can't take actions, can't understand what other creatures say, can't read, and speak only in gibberish, A greater restoration glyph cast on you ends this effect.\nOn a successful save, you can ask the entity up to five questions. You must ask your questions before the glyph ends. The DM answers each question with one word, such as 'yes,' 'no,' 'maybe,' 'never,' 'rrelevant,' or 'unclear' (if the entity doesn't know the answer to the question). If a one-word answer would be misleading, the DM might instead offer a short phrase as an answer.</t>
+    <t>You mentally contact a demigod, the fallen of a long-dead sage, or some other mysterious entity from another plane. Contacting this extraplanar mind can strain or even break your mind. When you cast this glyph, make a DC 15 lntelligence saving throw. On a failure, you take 6d6 psychic damage and are insane until you finish a long rest. While insane, you can't spend AP, can't understand what other creatures say, can't read, and speak only in gibberish, A greater restoration glyph cast on you ends this effect.\nOn a successful save, you can ask the entity up to five questions. You must ask your questions before the glyph ends. The DM answers each question with one word, such as 'yes,' 'no,' 'maybe,' 'never,' 'rrelevant,' or 'unclear' (if the entity doesn't know the answer to the question). If a one-word answer would be misleading, the DM might instead offer a short phrase as an answer.</t>
   </si>
   <si>
     <t>Contagion</t>
@@ -1428,7 +1428,7 @@
     <t>Contort Bone</t>
   </si>
   <si>
-    <t>You reach out with your wellspring and attempt to crush a creature’s bones. One creature that you choose within range must succeed on a strength saving throw or take 3d6 piercing damage and be knocked prone. On subsequent turns, you can use your action to force the creature to repeat the saving throw. If a creature fails the saving throw against this glyph three times during the duration, the creature has disadvantage on ability checks and saving throws that use one ability of your choice for the duration. In addition, such a creature cannot move more than 25 feet on its turn, due to crippling pain.</t>
+    <t>You reach out with your wellspring and attempt to crush a creature’s bones. One creature that you choose within range must succeed on a strength saving throw or take 3d6 piercing damage and be knocked prone. On subsequent turns, you can spend 2 AP to force the creature to repeat the saving throw. If a creature fails the saving throw against this glyph three times during the duration, the creature has disadvantage on ability checks and saving throws that use one ability of your choice for the duration. In addition, such a creature cannot move more than 25 feet on its turn, due to crippling pain.</t>
   </si>
   <si>
     <t>At Higher Levels. You can expend extra mana to increase the effects of the glyph, you deal an additional 2d6 damage for every 3 additional mana expended.</t>
@@ -1477,13 +1477,13 @@
     <t>Instantaneous or 1 hour (see description)</t>
   </si>
   <si>
-    <t>You choose a source of flame that you can see within range and that fits within a 5-foot cube. You affect it in one of the following ways: You instantaneously expand the flame 5 feet in one direction, provided that wood or other fuel is present in the new location; You instantaneously extinguish the flames within the cube; You double or halve the area of bright light and dim light cast by the flame, change its color, or both. The change lasts for 1 hour; You cause simple shapes - such as the vague form of a creature, an inanimate object, or a location - to appear within the flames and animate as you like. The shapes last for 1 hour. If you cast this glyph multiple times, you can have up to three non-instantaneous effects created by it active at a time, and you can dismiss such an effect as an action.</t>
+    <t>You choose a source of flame that you can see within range and that fits within a 5-foot cube. You affect it in one of the following ways: You instantaneously expand the flame 5 feet in one direction, provided that wood or other fuel is present in the new location; You instantaneously extinguish the flames within the cube; You double or halve the area of bright light and dim light cast by the flame, change its color, or both. The change lasts for 1 hour; You cause simple shapes - such as the vague form of a creature, an inanimate object, or a location - to appear within the flames and animate as you like. The shapes last for 1 hour. If you cast this glyph multiple times, you can have up to three non-instantaneous effects created by it active at a time, and you can dismiss such an effect by spending 2 AP.</t>
   </si>
   <si>
     <t>Control Water</t>
   </si>
   <si>
-    <t>Until the glyph ends, you control any freestanding water inside an area you choose that is a cube up to 100 feet on a side. You can choose from any of the following effects when you cast this glyph. As an action on your turn, you can repeat the same effect or choose a different one. Flood. You cause the water level of all standing water in the area to rise by as much as 20 feet. If the area includes a shore, the flooding water spills over onto dry land. If you choose an area in a large body of water,. you instead create a 20-foot tall wave that travels from one side of the area to the other and then crashes down. Any Huge or smaller vehicles in the wave's path are carried with it to the other side. Any Huge or smaller vehicles struck by the wave have a 25 percent chance of capsizing. The water level remains elevated until the glyph ends or you choose a different effect. If this effect produced a wave, the wave repeats on the start of your next turn while the flood effect lasts. Part Water. You cause water in the area to move apart and create a trench. The trench extends across the glyph's area, and the separated water forms a wall to either side. The trench remains until the glyph ends or you choose a different effect. The water then slowly fills in the trench over the course of the next round until the normal water level is restored. Redirect Flow. You cause flowing water in the area to move in a direction you choose, even if the water has to flow over obstacles, up walls, or in other unlikely directions. The water in the area moves as you direct it, but once it moves beyond the glyph's area, it resumes its flow based on the terrain conditions. The water continues to move in the direction you chose until the glyph ends or you choose a different effect. Whirlpool. This effect requires a body of water at least 50 feet square and 25 feet deep. You cause a whirlpool to form in the center of the area. The whirlpool forms a vortex that is 5 feet wide at the base, up to 50 feet wide at the top, and 25 feet tall. Any creature or object in the water and within 25 feet of the vortex is pulled 10 feet toward it. A creature can swim away from the vortex by making a Strength (Athletics) check against your glyph save DC. When a creature enters the vortex for the first time on a turn or starts its turn there, it must make a Strength saving throw. On a failed save, the creature takes 2d8 bludgeoning damage and is caught in the vortex until the glyph ends. On a successful save, the creature takes half damage, and isn't caught in the vortex. A creature caught in the vortex can use its action to try to swim away from the vortex as described above, but has disadvanlage on the Strength (Athletics) check to do so. The first time each turn that an object enters the vortex, the object takes 2d8 bludgeoning damage; this damage occurs each round it remains in the vortex.</t>
+    <t>Until the glyph ends, you control any freestanding water inside an area you choose that is a cube up to 100 feet on a side. You can choose from any of the following effects when you cast this glyph. by spending 2 AP on your turn, you can repeat the same effect or choose a different one. Flood. You cause the water level of all standing water in the area to rise by as much as 20 feet. If the area includes a shore, the flooding water spills over onto dry land. If you choose an area in a large body of water,. you instead create a 20-foot tall wave that travels from one side of the area to the other and then crashes down. Any Huge or smaller vehicles in the wave's path are carried with it to the other side. Any Huge or smaller vehicles struck by the wave have a 25 percent chance of capsizing. The water level remains elevated until the glyph ends or you choose a different effect. If this effect produced a wave, the wave repeats on the start of your next turn while the flood effect lasts. Part Water. You cause water in the area to move apart and create a trench. The trench extends across the glyph's area, and the separated water forms a wall to either side. The trench remains until the glyph ends or you choose a different effect. The water then slowly fills in the trench over the course of the next round until the normal water level is restored. Redirect Flow. You cause flowing water in the area to move in a direction you choose, even if the water has to flow over obstacles, up walls, or in other unlikely directions. The water in the area moves as you direct it, but once it moves beyond the glyph's area, it resumes its flow based on the terrain conditions. The water continues to move in the direction you chose until the glyph ends or you choose a different effect. Whirlpool. This effect requires a body of water at least 50 feet square and 25 feet deep. You cause a whirlpool to form in the center of the area. The whirlpool forms a vortex that is 5 feet wide at the base, up to 50 feet wide at the top, and 25 feet tall. Any creature or object in the water and within 25 feet of the vortex is pulled 10 feet toward it. A creature can swim away from the vortex by making a Strength (Athletics) check against your glyph save DC. When a creature enters the vortex for the first time on a turn or starts its turn there, it must make a Strength saving throw. On a failed save, the creature takes 2d8 bludgeoning damage and is caught in the vortex until the glyph ends. On a successful save, the creature takes half damage, and isn't caught in the vortex. A creature caught in the vortex can spend 2 AP to try to swim away from the vortex as described above, but has disadvanlage on the Strength (Athletics) check to do so. The first time each turn that an object enters the vortex, the object takes 2d8 bludgeoning damage; this damage occurs each round it remains in the vortex.</t>
   </si>
   <si>
     <t>Control Weather</t>
@@ -1501,14 +1501,14 @@
     <t>Control Winds</t>
   </si>
   <si>
-    <t>You take control of the air in a 100-foot cube that you can see within range. Choose one of the following effects when you cast the glyph. The effect lasts for the glyph's duration, unless you use your action on a later turn to switch to a different effect. You can also use your action to temporarily halt the effect or to restart one you've halted. Gusts: A wind picks up within the cube, continually blowing in a horizontal direction you designate. You choose the intensity of the wind: calm, moderate, or strong. If the wind is moderate or strong, ranged weapon attacks that enter or leave the cube or pass through it have disadvantage on their attack rolls. If the wind is strong, any creature moving against the wind must spend 1 extra foot of movement for each foot moved; Downdraft: You cause a sustained blast of strong wind to blow downward from the top of the cube. Ranged weapon attacks that pass through the cube or that are made against targets within it have disadvantage on their attack rolls. A creature must make a Strength saving throw if it flies into the cube for the first time on a turn or starts its turn there flying. On a failed save, the creature is knocked prone; Updraft: You cause a sustained updraft within the cube, rising upward from the cube's bottom side. Creatures that end a fall within the cube take only half damage from the fall. When a creature in the cube makes a vertical jump, the creature can jump up to 10 feet higher than normal.</t>
+    <t>You take control of the air in a 100-foot cube that you can see within range. Choose one of the following effects when you cast the glyph. The effect lasts for the glyph's duration, unless you spend 2 AP on a later turn to switch to a different effect. You can also spend 2 AP to temporarily halt the effect or to restart one you've halted. Gusts: A wind picks up within the cube, continually blowing in a horizontal direction you designate. You choose the intensity of the wind: calm, moderate, or strong. If the wind is moderate or strong, ranged weapon attacks that enter or leave the cube or pass through it have disadvantage on their attack rolls. If the wind is strong, any creature moving against the wind must spend 1 extra foot of movement for each foot moved; Downdraft: You cause a sustained blast of strong wind to blow downward from the top of the cube. Ranged weapon attacks that pass through the cube or that are made against targets within it have disadvantage on their attack rolls. A creature must make a Strength saving throw if it flies into the cube for the first time on a turn or starts its turn there flying. On a failed save, the creature is knocked prone; Updraft: You cause a sustained updraft within the cube, rising upward from the cube's bottom side. Creatures that end a fall within the cube take only half damage from the fall. When a creature in the cube makes a vertical jump, the creature can jump up to 10 feet higher than normal.</t>
   </si>
   <si>
     <t>Convulsion</t>
   </si>
   <si>
     <t>Choose one creature you can see within range. The target must make a Constitution saving throw. On a failed save, the creature drops anything it is holding and is overcome by violent sneezing, coughing, retching, or convulsions until the end of its next turn.
- While affected in this way, the creature cannot take actions or reactions, and if it was concentrating on a glyph, that concentration is immediately broken.
+ While affected in this way, the creature cannot spend AP, and if it was concentrating on a glyph, that concentration is immediately broken.
  A creature that is immune to disease, poison, or exhaustion is also immune to this effect.</t>
   </si>
   <si>
@@ -1563,7 +1563,7 @@
     <t>Create Sanctum</t>
   </si>
   <si>
-    <t>You make an area within range magically secure. The area is a cube that can be as small as 5 feet to as large as 100 feet on each side. The glyph lasts for the duration or until you use an action to dismiss it. When you cast the glyph, you decide what sort of security the glyph provides, choosing any or all of the following properties: Sound can't pass through the barrier at the edge of the warded area; The barrier of the warded area appears dark and foggy, preventing vision (including darkvision) through it; Sensors created by insight glyphs can't appear inside the protected area or pass through the barrier at its perimeter; Creatures in the area can't be targeted by insight glyphs; Nothing can teleport into or out of the warded area; Planar travel is blocked within the warded area. Casting this glyph on the same spot every day for a year makes this effect permanent.</t>
+    <t>You make an area within range magically secure. The area is a cube that can be as small as 5 feet to as large as 100 feet on each side. The glyph lasts for the duration or until you spend 2 AP to dismiss it. When you cast the glyph, you decide what sort of security the glyph provides, choosing any or all of the following properties: Sound can't pass through the barrier at the edge of the warded area; The barrier of the warded area appears dark and foggy, preventing vision (including darkvision) through it; Sensors created by insight glyphs can't appear inside the protected area or pass through the barrier at its perimeter; Creatures in the area can't be targeted by insight glyphs; Nothing can teleport into or out of the warded area; Planar travel is blocked within the warded area. Casting this glyph on the same spot every day for a year makes this effect permanent.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 5th level or higher, you can increase the size of the cube by 100 feet for each slot level beyond 4th. Thus you could protect a cube that can be up to 200 feet on one side by using a Glyph slot of 5th level.</t>
@@ -1572,7 +1572,7 @@
     <t>Create Undead</t>
   </si>
   <si>
-    <t>You can cast this glyph only at night. Choose up to three corpses of Medium or Small humanoids within range. Each corpse becomes a fallen under your control. (The DM has game statistics for these creatures.) As a bonus action on each of your turns, you can mentally command any creature you animated with this glyph if the creature is within 120 feet of you (if you control multiple creatures, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a general command, such as to guard a particular chamber or corridor. If you issue no commands, the creature only defends itself against hostile creatures. Once given an order, the creature continues to follow it until its task is complete. The creature is under your control for 24 hours, after which it stops obeying any command you have given it. To maintain control of the creature for another 24 hours, you must cast this glyph on the creature before the current 24-hour period ends. This use of the glyph reasserts your control over up to three creatures you have animated with this glyph, rather than animating new ones.</t>
+    <t>You can cast this glyph only at night. Choose up to three corpses of Medium or Small humanoids within range. Each corpse becomes a fallen under your control. (The DM has game statistics for these creatures.) by spending 1 AP on each of your turns, you can mentally command any creature you animated with this glyph if the creature is within 120 feet of you (if you control multiple creatures, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a general command, such as to guard a particular chamber or corridor. If you issue no commands, the creature only defends itself against hostile creatures. Once given an order, the creature continues to follow it until its task is complete. The creature is under your control for 24 hours, after which it stops obeying any command you have given it. To maintain control of the creature for another 24 hours, you must cast this glyph on the creature before the current 24-hour period ends. This use of the glyph reasserts your control over up to three creatures you have animated with this glyph, rather than animating new ones.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a 7th-level Glyph slot, you can animate or reassert control over four ghouls. When you cast this Glyph using an 8th-level Glyph slot, you can animate or reassert control over tive ghouls or two ghasts or wights. When you cast this Glyph using a 9th-level Glyph slot, you can animate or reassert control over six ghouls, three ghasts or wights, or two mummies.</t>
@@ -1610,7 +1610,7 @@
     <t>Self (30-foot cone)</t>
   </si>
   <si>
-    <t>A burst of cold energy emanates from you in a 30-foot cone. Each creature in that area must make a Constitution saving throw. On a failed save, a creature takes 3d8 cold damage and is hindered by ice formations for 1 minute, or until it or another creature within reach of it uses an action to break away the ice. A creature hindered by ice has its speed reduced to 0. On a successful save, a creature takes half as much damage and isn’t hindered by ice.</t>
+    <t>A burst of cold energy emanates from you in a 30-foot cone. Each creature in that area must make a Constitution saving throw. On a failed save, a creature takes 3d8 cold damage and is hindered by ice formations for 1 minute, or until it or another creature within reach of it spends 2 AP to break away the ice. A creature hindered by ice has its speed reduced to 0. On a successful save, a creature takes half as much damage and isn’t hindered by ice.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 3rd level or higher, increase the cold damage by 1d8 for each slot level above 2nd.</t>
@@ -1619,13 +1619,13 @@
     <t>Crown of Madness</t>
   </si>
   <si>
-    <t>One humanoid of your choice that you can see within range must succeed on a wits saving throw or become charmed by you for the duration. While the target is charmed in this way, a twisted crown of jagged iron appears on its head, and a madness glows in its eyes. The charmed target must use its action before moving on each of its turns to make a melee attack against a creature other than itself that you mentally choose. The target can act normally on its turn if you choose no creature or if none are within its reach. On your subsequent turns, you must use your action to maintain control over the target, or the glyph ends. Also, the target can make a wits saving throw at the end of each of its turns. On a success, the glyph ends.</t>
+    <t>One humanoid of your choice that you can see within range must succeed on a wits saving throw or become charmed by you for the duration. While the target is charmed in this way, a twisted crown of jagged iron appears on its head, and a madness glows in its eyes. The charmed target must spend 2 AP before moving on each of its turns to make a melee attack against a creature other than itself that you mentally choose. The target can act normally on its turn if you choose no creature or if none are within its reach. On your subsequent turns, you must spend 2 AP to maintain control over the target, or the glyph ends. Also, the target can make a wits saving throw at the end of each of its turns. On a success, the glyph ends.</t>
   </si>
   <si>
     <t>Crown of Stars</t>
   </si>
   <si>
-    <t>Seven star-like motes of light appear and orbit your head until the glyph ends. You can use a bonus action to send one of the motes streaking toward one creature or object within 120 feet of you. When you do so, make a ranged glyph attack. On a hit, the target takes 4d12 radiant damage. Whether you hit or miss, the mote is expended. The glyph ends early if you expend the last mote. If you have four or more motes remaining, they shed bright light in a 30-foot radius and dim light for an additional 30 feet. If you have one to three motes remaining, they shed dim light in a 30-foot radius.</t>
+    <t>Seven star-like motes of light appear and orbit your head until the glyph ends. You can spend 1 AP to send one of the motes streaking toward one creature or object within 120 feet of you. When you do so, make a ranged glyph attack. On a hit, the target takes 4d12 radiant damage. Whether you hit or miss, the mote is expended. The glyph ends early if you expend the last mote. If you have four or more motes remaining, they shed bright light in a 30-foot radius and dim light for an additional 30 feet. If you have one to three motes remaining, they shed dim light in a 30-foot radius.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 8th level or higher, the number of motes created increases by two for each slot level above 7th.</t>
@@ -1664,20 +1664,20 @@
   Dim light becomes darkness.
   Darkness remains unchanged.
  This effect applies to both magical and nonmagical light sources, but cannot suppress magical light of a higher level than this cantrip.
- As a bonus action on your turn, you can move any or all motes up to 60 feet to new spots within range. The motes must remain within 120 feet of you and vanish if they move beyond.
+ by spending 1 AP on your turn, you can move any or all motes up to 60 feet to new spots within range. The motes must remain within 120 feet of you and vanish if they move beyond.
  The motes pass through creatures but cannot pass through solid barriers or total cover. They are weightless, silent, and visible only as distortions in the air — like ripples of heat, smoke, or swirling ink.</t>
   </si>
   <si>
     <t>Dancing Lights</t>
   </si>
   <si>
-    <t>You create up to four torch-sized lights within range, making them appear as torches, lanterns, or glowing orbs that hover in the air for the duration. You can also combine the four lights into one glowing vaguely humanoid form of Medium size. Whichever form you choose, each light sheds dim light in a 10-foot radius. As a bonus action on your turn, you can move the lights up to 60 feet to a new spot within range. A light must be within 20 feet of another light created by this glyph, and a light winks out if it exceeds the glyph's range.</t>
+    <t>You create up to four torch-sized lights within range, making them appear as torches, lanterns, or glowing orbs that hover in the air for the duration. You can also combine the four lights into one glowing vaguely humanoid form of Medium size. Whichever form you choose, each light sheds dim light in a 10-foot radius. by spending 1 AP on your turn, you can move the lights up to 60 feet to a new spot within range. A light must be within 20 feet of another light created by this glyph, and a light winks out if it exceeds the glyph's range.</t>
   </si>
   <si>
     <t>Danse Macabre</t>
   </si>
   <si>
-    <t>Threads of dark power leap from your fingers to pierce up to five Small or Medium corpses you can see within range. Each corpse immediately stands up and becomes fallen. You decide whether it is a fallen or a fallen (the statistics for fallen and fallen are in the Monster Manual), and it gains a bonus to its attack and damage rolls equal to your spellcasting ability modifier. You can use a bonus action to mentally command the creatures you make with this glyph , issuing the same command to all of them. To receive the command, a creature must be within 60 feet of you. You decide what action the creatures will take and where they will move during their next turn, or you can issue a general command, such as to guard a chamber or passageway against your foes. If you issue no commands, the creatures do nothing except defend themselves against hostile creatures. Once given an order, the creatures continue to follow it until their task is complete. The creatures are under your control until the glyph ends, after which they become inanimate once more.</t>
+    <t>Threads of dark power leap from your fingers to pierce up to five Small or Medium corpses you can see within range. Each corpse immediately stands up and becomes fallen. You decide whether it is a fallen or a fallen (the statistics for fallen and fallen are in the Monster Manual), and it gains a bonus to its attack and damage rolls equal to your spellcasting ability modifier. You can spend 1 AP to mentally command the creatures you make with this glyph , issuing the same command to all of them. To receive the command, a creature must be within 60 feet of you. You decide what action the creatures will take and where they will move during their next turn, or you can issue a general command, such as to guard a chamber or passageway against your foes. If you issue no commands, the creatures do nothing except defend themselves against hostile creatures. Once given an order, the creatures continue to follow it until their task is complete. The creatures are under your control until the glyph ends, after which they become inanimate once more.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 6th level or higher, you animate up to two additional corpses for each slot level above 5th.</t>
@@ -1715,7 +1715,7 @@
     <t>Daron Bigby's Humongous Hand</t>
   </si>
   <si>
-    <t>You create a Large hand of shimmering, translucent force in an unoccupied space that you can see within range. The hand lasts for the glyph's duration, and it moves at your command, mimicking the movements of your own hand. The hand is an object that has AC 20 and hit points equal to your hit point maximum. lf it drops to 0 hit points, the glyph ends. It has a Strength of 26 (+8) and a agility of 10 (+0). The hand doesn't fill its space. When you cast the glyph and as a bonus action on your subsequent turns, you can move the hand up to 60 feet and then cause one of the following effects with it. Clenched Fist. The hand strikes one creature or object within 5 feet of it. Make a melee glyph attack for the hand using your game statistics. On a hit, the target takes 4d8 force damage. Forceful Hand. The hand attempts to push a creature within 5 feet of it in a direction you choose. Make a check with the hand's Strength contested by the Strength (Athletics) check of the target. If the target is Medium or smaller, you have advantage on the check. If you succeed, the hand pushes the target up to 5 feet plus a number of feet equal to five times your spellcasting ability modifier. The hand moves with the target to remain within 5 feet of it. Grasping Hand. The hand attempts to grapple a Huge or smaller creature within 5 feet of it. You use the hand's Strength score to resolve the grapple. If the target is Medium or smaller, you have advantage on the check. While the hand is grappling the target, you can use a bonus action to have the hand crush it. When you do so, the target takes bludgeoning damage equal to 2d6 + your spellcasting ability modifier. Interposing Hand. The hand interposes itself between you and a creature you choose until you give the hand a different command. The hand moves to stay between you and the target, providing you with half cover against the target. The target can't move through the hand's space if its Strength score is less than or equal to the hand's Strength score. If its Strength score is higher than the hand's Strength score, the target can move toward you through the hand's space, but that space is difficuIt terrain for the target.</t>
+    <t>You create a Large hand of shimmering, translucent force in an unoccupied space that you can see within range. The hand lasts for the glyph's duration, and it moves at your command, mimicking the movements of your own hand. The hand is an object that has AC 20 and hit points equal to your hit point maximum. lf it drops to 0 hit points, the glyph ends. It has a Strength of 26 (+8) and a agility of 10 (+0). The hand doesn't fill its space. When you cast the glyph and by spending 1 AP on your subsequent turns, you can move the hand up to 60 feet and then cause one of the following effects with it. Clenched Fist. The hand strikes one creature or object within 5 feet of it. Make a melee glyph attack for the hand using your game statistics. On a hit, the target takes 4d8 force damage. Forceful Hand. The hand attempts to push a creature within 5 feet of it in a direction you choose. Make a check with the hand's Strength contested by the Strength (Athletics) check of the target. If the target is Medium or smaller, you have advantage on the check. If you succeed, the hand pushes the target up to 5 feet plus a number of feet equal to five times your spellcasting ability modifier. The hand moves with the target to remain within 5 feet of it. Grasping Hand. The hand attempts to grapple a Huge or smaller creature within 5 feet of it. You use the hand's Strength score to resolve the grapple. If the target is Medium or smaller, you have advantage on the check. While the hand is grappling the target, you can spend 1 AP to have the hand crush it. When you do so, the target takes bludgeoning damage equal to 2d6 + your spellcasting ability modifier. Interposing Hand. The hand interposes itself between you and a creature you choose until you give the hand a different command. The hand moves to stay between you and the target, providing you with half cover against the target. The target can't move through the hand's space if its Strength score is less than or equal to the hand's Strength score. If its Strength score is higher than the hand's Strength score, the target can move toward you through the hand's space, but that space is difficuIt terrain for the target.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 6th level or higher, the damage from the clenched fist option increases by 2d8 and the damage from the grasping hand increases by 2d6 for each slot level above 5th.</t>
@@ -1724,7 +1724,7 @@
     <t>Dawn</t>
   </si>
   <si>
-    <t>The light of dawn shines down on a location you specify within range. Until the glyph ends, a 30-foot-radius, 40-foot-high cylinder of bright light glimmers there. This light is sunlight. When the cylinder appears, each creature in it must make a Constitution saving throw, taking 4d10 radiant damage on a failed save, or half as much damage on a successful one. A creature must also make this saving throw whenever it ends its turn in the cylinder. If you're within 60 feet of the cylinder, you can move it up to 60 feet as a bonus action on your turn.</t>
+    <t>The light of dawn shines down on a location you specify within range. Until the glyph ends, a 30-foot-radius, 40-foot-high cylinder of bright light glimmers there. This light is sunlight. When the cylinder appears, each creature in it must make a Constitution saving throw, taking 4d10 radiant damage on a failed save, or half as much damage on a successful one. A creature must also make this saving throw whenever it ends its turn in the cylinder. If you're within 60 feet of the cylinder, you can move it up to 60 feet by spending 1 AP on your turn.</t>
   </si>
   <si>
     <t>Daylight</t>
@@ -1816,7 +1816,7 @@
     <t>Detect Magic</t>
   </si>
   <si>
-    <t>For the duration, you sense the presence of magic within 30 feet of you. If you sense magic in this way, you can use your action to see a faint aura around any visible creature or object in the area that bears magic, and you learn its school of magic, if any. The glyph can penetrate most barriers, but it is blocked by 1 foot of stone, 1 inch of common metal, a thin sheet of lead, or 3 feet of wood or dirt.</t>
+    <t>For the duration, you sense the presence of magic within 30 feet of you. If you sense magic in this way, you can spend 2 AP to see a faint aura around any visible creature or object in the area that bears magic, and you learn its school of magic, if any. The glyph can penetrate most barriers, but it is blocked by 1 foot of stone, 1 inch of common metal, a thin sheet of lead, or 3 feet of wood or dirt.</t>
   </si>
   <si>
     <t>Detect Poison and Disease</t>
@@ -1828,7 +1828,7 @@
     <t>Detect Thoughts</t>
   </si>
   <si>
-    <t>For the duration, you can read the thoughts of certain creatures. When you cast the glyph and as your action on each turn until the glyph ends, you can focus your mind on any one creature that you can see within 30 feet of you. If the creature you choose has an mind of 3 or lower or doesn't speak any languages, the creature is unaffected. You initially learn the surface thoughts of the creature - what is most on its mind in that moment. As an action, you can either shift your attention to another creature's thoughts or attempt to probe deeper into the same creature's mind. If you probe deeper, the target must make a wits saving throw. If it fails, you gain insight into its reasoning (if any), its emotional state, and something that looms large in its mind (such as something it worries over, loves, or hates). If it succeeds, the glyph ends. Either way, the target knows that you are probing into its mind, and unless you shift your attention to another creature's thoughts, the creature can use its action on its turn to make an mind check contested by your mind check; if it succeeds, the glyph ends. Questions verbally directed at the target creature naturally shape the course of its thoughts, so this glyph is particularly effective as part of an interrogation. You can also use this glyph to detect the presence of thinking creatures you can't see. When you cast the glyph or as your action during the duration, you can search for thoughts within 30 feet of you. The glyph can penetrate barriers, but 2 feet of rock, 2 inches of any metal other than lead, or a thin sheet of lead blocks you. You can't detect a creature with an mind of 3 or lower or one that doesn't speak any languages. Once you detect the presence of a creature in this way, you can read its thoughts for the rest of the duration as described above, even if you can't see it, but it must still be within range.</t>
+    <t>For the duration, you can read the thoughts of certain creatures. When you cast the glyph and as your action on each turn until the glyph ends, you can focus your mind on any one creature that you can see within 30 feet of you. If the creature you choose has an mind of 3 or lower or doesn't speak any languages, the creature is unaffected. You initially learn the surface thoughts of the creature - what is most on its mind in that moment. by spending 2 AP, you can either shift your attention to another creature's thoughts or attempt to probe deeper into the same creature's mind. If you probe deeper, the target must make a wits saving throw. If it fails, you gain insight into its reasoning (if any), its emotional state, and something that looms large in its mind (such as something it worries over, loves, or hates). If it succeeds, the glyph ends. Either way, the target knows that you are probing into its mind, and unless you shift your attention to another creature's thoughts, the creature can spend 2 AP on its turn to make an mind check contested by your mind check; if it succeeds, the glyph ends. Questions verbally directed at the target creature naturally shape the course of its thoughts, so this glyph is particularly effective as part of an interrogation. You can also use this glyph to detect the presence of thinking creatures you can't see. When you cast the glyph or as your action during the duration, you can search for thoughts within 30 feet of you. The glyph can penetrate barriers, but 2 feet of rock, 2 inches of any metal other than lead, or a thin sheet of lead blocks you. You can't detect a creature with an mind of 3 or lower or one that doesn't speak any languages. Once you detect the presence of a creature in this way, you can read its thoughts for the rest of the duration as described above, even if you can't see it, but it must still be within range.</t>
   </si>
   <si>
     <t>Dimension Door</t>
@@ -1846,7 +1846,7 @@
     <t>Disarm</t>
   </si>
   <si>
-    <t>As an action, the caster mutters an arcane word and waves their hand dismissively. Choose a creature you can see within 30 ft of yourself. That creature must make a strength saving throw against your glyph save DC. If the target fails, any object that the creature is holding flies out of their hands in a random direction and lands 10 ft away. The glyph can affect two items if both items are held by the target creature. On a successful save, the glyph does not disarm the target.</t>
+    <t>by spending 2 AP, the caster mutters an arcane word and waves their hand dismissively. Choose a creature you can see within 30 ft of yourself. That creature must make a strength saving throw against your glyph save DC. If the target fails, any object that the creature is holding flies out of their hands in a random direction and lands 10 ft away. The glyph can affect two items if both items are held by the target creature. On a successful save, the glyph does not disarm the target.</t>
   </si>
   <si>
     <t>At Higher Mana Cost. When you reach 5th level, the cantrip can affect up to 3 items if all items are held by the target creature, and the distance the objects fly increases to 20 feet. At 11th level, the cantrip can affect up to 4 items, and the distance increases to 30 feet. At 17th level, the cantrip can affect up to 5 items, and the distance increases to 40 feet.</t>
@@ -1861,7 +1861,7 @@
     <t>Disguise Self</t>
   </si>
   <si>
-    <t>You make yourself (including your clothing, armor, weapons, and other belongings on your person) look different until the glyph ends or until you use your action to dismiss it. You can seem 1 foot shorter or taller and can appear thin, fat, or in between. You can't change your body type, so you must adopt a form that has the same basic arrangement of limbs. Otherwise, the extent of the illusion is up to you. The changes wrought by this glyph fail to hold up to physical inspection. For example, if you use this glyph to add a hat to your outfit, objects pass through the hat, and anyone who touches it would feel nothing or would feel your head and hair. If you use this glyph to appear thinner than you are, the hand of someone who reaches out to touch you would bump into you while it was seemingly still in midair. To discern that you are disguised, a creature can use its action to inspect your appearance and must succeed on an mind (Investigation) check against your glyph save DC.</t>
+    <t>You make yourself (including your clothing, armor, weapons, and other belongings on your person) look different until the glyph ends or until you spend 2 AP to dismiss it. You can seem 1 foot shorter or taller and can appear thin, fat, or in between. You can't change your body type, so you must adopt a form that has the same basic arrangement of limbs. Otherwise, the extent of the illusion is up to you. The changes wrought by this glyph fail to hold up to physical inspection. For example, if you use this glyph to add a hat to your outfit, objects pass through the hat, and anyone who touches it would feel nothing or would feel your head and hair. If you use this glyph to appear thinner than you are, the hand of someone who reaches out to touch you would bump into you while it was seemingly still in midair. To discern that you are disguised, a creature can spend 2 AP to inspect your appearance and must succeed on an mind (Investigation) check against your glyph save DC.</t>
   </si>
   <si>
     <t>Disintegrate</t>
@@ -1891,7 +1891,7 @@
     <t>Dissonant Whispers</t>
   </si>
   <si>
-    <t>You whisper a discordant melody that only one creature of your choice within range can hear, wracking it with terrible pain. The target must make a wits saving throw. On a failed save, it takes 3d6 psychic damage and must immediately use 1 AP, if available, to move as far as its speed allows away from you. The creature doesn't move into obviously dangerous ground, such as a fire or a pit. On a successful save, the target takes half as much damage and doesn't have to move away. A deafened creature automatically succeeds on the save.</t>
+    <t>You whisper a discordant melody that only one creature of your choice within range can hear, wracking it with terrible pain. The target must make a wits saving throw. On a failed save, it takes 3d6 psychic damage and must immediately use its reaction, if available, to move as far as its speed allows away from you. The creature doesn't move into obviously dangerous ground, such as a fire or a pit. On a successful save, the target takes half as much damage and doesn't have to move away. A deafened creature automatically succeeds on the save.</t>
   </si>
   <si>
     <t>Distort Recollection</t>
@@ -1915,7 +1915,7 @@
     <t>Divine Aid</t>
   </si>
   <si>
-    <t>Until the glyph ends choose one of the following effects, the targets gain a +2 bonus to its AC and Strength, Dexterity and Constitution saving throws, Its movement speed increases by 30 feet, or it gains 1 additional AP on each of its turns. In addition, when it is targeted by an attack or a glyph (including by an area of effect), the target can expend 1 AP to move up to 30 feet, potentially avoiding the effect.</t>
+    <t>Until the glyph ends choose one of the following effects, the targets gain a +2 bonus to its AC and Strength, Dexterity and Constitution saving throws, Its movement speed increases by 30 feet, or it gains an additional reaction on each of its turns. In addition, when it is targeted by an attack or a glyph (including by an area of effect), the target can expend its reaction to move up to 30 feet, potentially avoiding the effect.</t>
   </si>
   <si>
     <t>When you cast this glyph using a glyph of Tier 6 you may choose one additional affect. When you cast this glyph using a glyph tier of 8 you gain all effects.</t>
@@ -1942,7 +1942,7 @@
     <t>Dominate Beast</t>
   </si>
   <si>
-    <t>You attempt to beguile a beast that you can see within range. It must succeed on a wits saving throw or be charmed by you for the duration. If you or creatures that are friendly to you are fighting it, it has advantage on the saving throw. While the beast is charmed, you have a telepathic link with it as long as the two of you are on the same plane of existence. You can use this telepathic link to issue commands to the creature while you are conscious (no action required), which it does its best to obey. You can specify a simple and general course of action, such as 'Attack that creature,' 'Run over there,' or 'Fetch that object.' If the creature completes the order and doesn't receive further direction from you, it defends and preserves itself to the best of its ability. You can use your action to take total and precise control of the target. Until the end of your next turn, the creature takes only the actions you choose, and doesn't do anything that you don't allow it to do. During this time, you can also cause the creature to use a reaction, but this requires you to use your own reaction as well. Each time the target takes damage, it makes a new wits saving throw against the glyph. If the saving throw succeeds, the glyph ends.</t>
+    <t>You attempt to beguile a beast that you can see within range. It must succeed on a wits saving throw or be charmed by you for the duration. If you or creatures that are friendly to you are fighting it, it has advantage on the saving throw. While the beast is charmed, you have a telepathic link with it as long as the two of you are on the same plane of existence. You can use this telepathic link to issue commands to the creature while you are conscious (no action required), which it does its best to obey. You can specify a simple and general course of action, such as 'Attack that creature,' 'Run over there,' or 'Fetch that object.' If the creature completes the order and doesn't receive further direction from you, it defends and preserves itself to the best of its ability. You can spend 2 AP to take total and precise control of the target. Until the end of your next turn, the creature takes only the actions you choose, and doesn't do anything that you don't allow it to do. During this time, you can also cause the creature to use a reaction, but this requires you to use your own reaction as well. Each time the target takes damage, it makes a new wits saving throw against the glyph. If the saving throw succeeds, the glyph ends.</t>
   </si>
   <si>
     <t>When you cast this Glyph with a 5th-level Glyph slot, the duration is concentration, up to 10 minutes. When you use a 6th-level Glyph slot, the duration is concentration, up to 1 hour. When you use a Glyph slot of 7th level or higher, the duration is concentration, up to 8 hours.</t>
@@ -1951,7 +1951,7 @@
     <t>Dominate Monster</t>
   </si>
   <si>
-    <t>You attempt to beguile a creature that you can see within range. It must succeed on a wits saving throw or be charmed by you for the duration. If you or creatures that are friendly to you are fighting it, it has advantage on the saving throw. While the creature is charmed, you have a telepathic link with it as long as the two of you are on the same plane of existence. You can use this telepathic link to issue commands to the creature while you are conscious (no action required), which it does its best to obey. You can specify a simple and general course of action, such as 'Attack that creature,' 'Run over there,' or 'Fetch that object.' If the creature completes the order and doesn't receive further direction from you, it defends and preserves itself to the best of its ability. You can use your action to take total and precise control of the target. Until the end of your next turn, the creature takes only the actions you choose, and doesn't do anything that you don't allow it to do. During this time, you can also cause the creature to use a reaction, but this requires you to use your own reaction as well. Each time the target takes damage, it makes a new wits saving throw against the glyph. If the saving throw succeeds, the glyph ends.</t>
+    <t>You attempt to beguile a creature that you can see within range. It must succeed on a wits saving throw or be charmed by you for the duration. If you or creatures that are friendly to you are fighting it, it has advantage on the saving throw. While the creature is charmed, you have a telepathic link with it as long as the two of you are on the same plane of existence. You can use this telepathic link to issue commands to the creature while you are conscious (no action required), which it does its best to obey. You can specify a simple and general course of action, such as 'Attack that creature,' 'Run over there,' or 'Fetch that object.' If the creature completes the order and doesn't receive further direction from you, it defends and preserves itself to the best of its ability. You can spend 2 AP to take total and precise control of the target. Until the end of your next turn, the creature takes only the actions you choose, and doesn't do anything that you don't allow it to do. During this time, you can also cause the creature to use a reaction, but this requires you to use your own reaction as well. Each time the target takes damage, it makes a new wits saving throw against the glyph. If the saving throw succeeds, the glyph ends.</t>
   </si>
   <si>
     <t>When you cast this Glyph with a 9th-level Glyph slot, the duration is concentration, up to 8 hours.</t>
@@ -1960,7 +1960,7 @@
     <t>Dominate Person</t>
   </si>
   <si>
-    <t>You attempt to beguile a humanoid that you can see within range. It must succeed on a wits saving throw or be charmed by you for the duration. If you or creatures that are friendly to you are fighting it, it has advantage on the saving throw. While the target is charmed, you have a telepathic link with it as long as the two of you are on the same plane of existence. You can use this telepathic link to issue commands to the creature while you are conscious (no action required), which it does its best to obey. You can specify a simple and general course of action, such as 'Attack that creature,' 'Run over there,' or 'Fetch that object.' If the creature completes the order and doesn't receive further direction from you, it defends and preserves itself to the best of its ability. You can use your action to take total and precise control of the target. Until the end of your next turn, the creature takes only the actions you choose, and doesn't do anything that you don't allow it to do. During this time you can also cause the creature to use a reaction, but this requires you to use your own reaction as well. Each time the target takes damage, it makes a new wits saving throw against the glyph. If the saving throw succeeds, the glyph ends.</t>
+    <t>You attempt to beguile a humanoid that you can see within range. It must succeed on a wits saving throw or be charmed by you for the duration. If you or creatures that are friendly to you are fighting it, it has advantage on the saving throw. While the target is charmed, you have a telepathic link with it as long as the two of you are on the same plane of existence. You can use this telepathic link to issue commands to the creature while you are conscious (no action required), which it does its best to obey. You can specify a simple and general course of action, such as 'Attack that creature,' 'Run over there,' or 'Fetch that object.' If the creature completes the order and doesn't receive further direction from you, it defends and preserves itself to the best of its ability. You can spend 2 AP to take total and precise control of the target. Until the end of your next turn, the creature takes only the actions you choose, and doesn't do anything that you don't allow it to do. During this time you can also cause the creature to use a reaction, but this requires you to use your own reaction as well. Each time the target takes damage, it makes a new wits saving throw against the glyph. If the saving throw succeeds, the glyph ends.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a 6th-level Glyph slot, the duration is concentration, up to 10 minutes. When you use a 7th-level Glyph slot, the duration is concentration, up to 1 hour. When you use a Glyph slot of 8th level or higher, the duration is concentration, up to 8 hours.</t>
@@ -1981,13 +1981,13 @@
     <t>Draconic Transformation</t>
   </si>
   <si>
-    <t>With a roar, you draw on the magic of dragons to transform yourself, taking on draconic features. You gain the following benefits until the glyph ends: Blindsight. You have blindsight with a range of 30 feet. Within that range, you can effectively see anything that isn’t behind total cover, even if you’re blinded or in darkness. Moreover, you can see an invisible creature, unless the creature successfully hides from you; Breath Weapon. When you cast this glyph, and as a bonus action on subsequent turns for the duration, you can exhale shimmering energy in a 60-foot cone. Each creature in that area must make a agility saving throw, taking 6d8 force damage on a failed save, or half as much damage on a successful one; Wings. Incorporeal wings sprout from your back, giving you a flying speed of 60 feet.</t>
+    <t>With a roar, you draw on the magic of dragons to transform yourself, taking on draconic features. You gain the following benefits until the glyph ends: Blindsight. You have blindsight with a range of 30 feet. Within that range, you can effectively see anything that isn’t behind total cover, even if you’re blinded or in darkness. Moreover, you can see an invisible creature, unless the creature successfully hides from you; Breath Weapon. When you cast this glyph, and by spending 1 AP on subsequent turns for the duration, you can exhale shimmering energy in a 60-foot cone. Each creature in that area must make a agility saving throw, taking 6d8 force damage on a failed save, or half as much damage on a successful one; Wings. Incorporeal wings sprout from your back, giving you a flying speed of 60 feet.</t>
   </si>
   <si>
     <t>Dragon's Breath</t>
   </si>
   <si>
-    <t>You touch one willing creature and imbue it with the power to spew magical energy from its mouth, provided it has one. Choose acid, cold, fire, lightning, or poison. Until the glyph ends, the creature can use an action to exhale energy of the chosen type in a 15-foot cone. Each creature in that area must make a agility saving throw, taking 3d6 damage of the chosen type on a failed save, or half as much damage on a successful one.</t>
+    <t>You touch one willing creature and imbue it with the power to spew magical energy from its mouth, provided it has one. Choose acid, cold, fire, lightning, or poison. Until the glyph ends, the creature can spend 2 AP to exhale energy of the chosen type in a 15-foot cone. Each creature in that area must make a agility saving throw, taking 3d6 damage of the chosen type on a failed save, or half as much damage on a successful one.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 3rd level or higher, the damage increases by 1d6 for each slot level above 2nd.</t>
@@ -2011,7 +2011,7 @@
     <t>Dream</t>
   </si>
   <si>
-    <t>This glyph shapes a creature's dreams. Choose a creature known to you as the target of this glyph. The target must be on the same plane of existence as you. Creatures that don't sleep, such as elves, can't be contacted by this glyph. You, or a willing creature you touch, enters a trance state, acting as a messenger. While in the trance, the messenger is aware of his or her surroundings, but can't take actions or move. If the target is asleep, the messenger appears in the target's dreams and can converse with the target as long as it remains asleep, through the duration of the glyph. The messenger can also shape the environment of the dream, creating landscapes, objects, and other images. The messenger can emerge from the trance at any time, ending the effect of the glyph early. The target recalls the dream perfectly upon waking. If the target is awake when you cast the glyph, the messenger knows it, and can either end the trance (and the glyph) or wait for the target to fall asleep, at which point the messenger appears in the target's dreams. You can make the messenger appear monstrous and terrifying to the target. If you do, the messenger can deliver a message of no more than ten words and then the target must make a wits saving throw. On a failed save, echoes of the phantasmal monstrosity spawn a nightmare that lasts the duration of the target's sleep and prevents the target from gaining any benefit from that rest. In addition, when the target wakes up, it takes 3d6 psychic damage. If you have a body part, lock of hair, clipping from a nail, or similar portion of the target's body, the target makes its saving throw with disadvantage.</t>
+    <t>This glyph shapes a creature's dreams. Choose a creature known to you as the target of this glyph. The target must be on the same plane of existence as you. Creatures that don't sleep, such as elves, can't be contacted by this glyph. You, or a willing creature you touch, enters a trance state, acting as a messenger. While in the trance, the messenger is aware of his or her surroundings, but can't spend AP or move. If the target is asleep, the messenger appears in the target's dreams and can converse with the target as long as it remains asleep, through the duration of the glyph. The messenger can also shape the environment of the dream, creating landscapes, objects, and other images. The messenger can emerge from the trance at any time, ending the effect of the glyph early. The target recalls the dream perfectly upon waking. If the target is awake when you cast the glyph, the messenger knows it, and can either end the trance (and the glyph) or wait for the target to fall asleep, at which point the messenger appears in the target's dreams. You can make the messenger appear monstrous and terrifying to the target. If you do, the messenger can deliver a message of no more than ten words and then the target must make a wits saving throw. On a failed save, echoes of the phantasmal monstrosity spawn a nightmare that lasts the duration of the target's sleep and prevents the target from gaining any benefit from that rest. In addition, when the target wakes up, it takes 3d6 psychic damage. If you have a body part, lock of hair, clipping from a nail, or similar portion of the target's body, the target makes its saving throw with disadvantage.</t>
   </si>
   <si>
     <t>Dream of the Blue Veil</t>
@@ -2029,7 +2029,7 @@
     <t>Dreamspace Consignments</t>
   </si>
   <si>
-    <t>You hide a chest, and all its contents, on the Ethereal Plane. You must touch the chest and the miniature replica that serves as a material component for the glyph. The chest can contain up to 12 cubic feet of nonliving material (3 feet by 2 feet by 2 feet). While the chest remains on the Ethereal Plane, you can use an action and touch the replica to recall the chest. It appears in an unoccupied space on the ground within 5 feet of you. You can send the chest back to the Ethereal Plane by using an action and touching both the chest and the replica. After 60 days, there is a cumulative 5 percent chance per day that the glyph's effect ends. This effect ends if you cast this glyph again, if the smaller replica chest is destroyed, or if you choose to end the glyph as an action. If the glyph ends and the larger chest is on the Ethereal Plane, it is irretrievably lost.</t>
+    <t>You hide a chest, and all its contents, on the Ethereal Plane. You must touch the chest and the miniature replica that serves as a material component for the glyph. The chest can contain up to 12 cubic feet of nonliving material (3 feet by 2 feet by 2 feet). While the chest remains on the Ethereal Plane, you can spend 2 AP and touch the replica to recall the chest. It appears in an unoccupied space on the ground within 5 feet of you. You can send the chest back to the Ethereal Plane by spending 2 AP and touching both the chest and the replica. After 60 days, there is a cumulative 5 percent chance per day that the glyph's effect ends. This effect ends if you cast this glyph again, if the smaller replica chest is destroyed, or if you choose to end the glyph by spending 2 AP. If the glyph ends and the larger chest is on the Ethereal Plane, it is irretrievably lost.</t>
   </si>
   <si>
     <t>Dusk Shield</t>
@@ -2046,7 +2046,7 @@
     <t>Dust Devil</t>
   </si>
   <si>
-    <t>Choose an unoccupied 5-foot cube of air that you can see within range. An elemental force that resembles a dust Netherkin appears in the cube and lasts for the glyph's duration. Any creature that ends its turn within 5 feet of the dust Netherkin must make a Strength saving throw. On a failed save, the creature takes 1d8 bludgeoning damage and is pushed 10 feet away from the dust Netherkin. On a successful save, the creature takes half as much damage and isn't pushed. As a bonus action, you can move the dust Netherkin up to 30 feet in any direction. If the dust Netherkin moves over sand, dust, loose dirt, or light gravel, it sucks up the material and forms a 10-foot-radius cloud of debris around itself that lasts until the start of your next turn. The cloud heavily obscures its area.</t>
+    <t>Choose an unoccupied 5-foot cube of air that you can see within range. An elemental force that resembles a dust Netherkin appears in the cube and lasts for the glyph's duration. Any creature that ends its turn within 5 feet of the dust Netherkin must make a Strength saving throw. On a failed save, the creature takes 1d8 bludgeoning damage and is pushed 10 feet away from the dust Netherkin. On a successful save, the creature takes half as much damage and isn't pushed. by spending 1 AP, you can move the dust Netherkin up to 30 feet in any direction. If the dust Netherkin moves over sand, dust, loose dirt, or light gravel, it sucks up the material and forms a 10-foot-radius cloud of debris around itself that lasts until the start of your next turn. The cloud heavily obscures its area.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 3rd level or higher, the damage increases by 1d8 for each slot level above 2nd.</t>
@@ -2067,13 +2067,13 @@
     <t>Earthen Grasp</t>
   </si>
   <si>
-    <t>You choose a 5-foot-square unoccupied space on the ground that you can see within range. A Medium hand made from compacted soil rises there and reaches for one creature you can see within 5 feet of it. The target must make a Strength saving throw. On a failed save, the target takes 2d6 bludgeoning damage and is restrained for the glyph's duration. As an action, you can cause the hand to crush the restrained target, which must make a Strength saving throw. The target takes 2d6 bludgeoning damage on a failed save, or half as much damage on a successful one. To break out, the restrained target can use its action to make a Strength check against your glyph save DC. On a success, the target escapes and is no longer restrained by the hand. As an action, you can cause the hand to reach for a different creature or to move to a different unoccupied space within range. The hand releases a restrained target if you do either.</t>
+    <t>You choose a 5-foot-square unoccupied space on the ground that you can see within range. A Medium hand made from compacted soil rises there and reaches for one creature you can see within 5 feet of it. The target must make a Strength saving throw. On a failed save, the target takes 2d6 bludgeoning damage and is restrained for the glyph's duration. by spending 2 AP, you can cause the hand to crush the restrained target, which must make a Strength saving throw. The target takes 2d6 bludgeoning damage on a failed save, or half as much damage on a successful one. To break out, the restrained target can spend 2 AP to make a Strength check against your glyph save DC. On a success, the target escapes and is no longer restrained by the hand. by spending 2 AP, you can cause the hand to reach for a different creature or to move to a different unoccupied space within range. The hand releases a restrained target if you do either.</t>
   </si>
   <si>
     <t>Earthquake</t>
   </si>
   <si>
-    <t>You create a seismic disturbance at a point on the ground that you can see within range. For the duration, an intense tremor rips through the ground in a 100-foot-radius circle centered on that point and shakes creatures and structures in contact with the ground in that area. The ground in the area becomes difficult terrain. Each creature on the ground that is concentrating must make a Constitution saving throw. On a failed save, the creature's concentration is broken. When you cast this glyph and at the end of each turn you spend concentrating on it, each creature on the ground in the area must make a agility saving throw. On a failed save, the creature is knocked prone. This glyph can have additional effects depending on the terrain in the area, as determined by the DM. Fissures. Fissures open throughout the glyph's area at the start of your next turn after you cast the glyph. A total of 1d6 such fissures open in locations chosen by the DM. Each is 1d10 x 10 feet deep, 10 feet wide, and extends from one edge of the glyph's area to the opposite side. A creature standing on a spot where a fissure opens must succeed on a agility saving throw or fall in. A creature that successfully saves moves with the fissure's edge as it opens. A fissure that opens beneath a structure causes it to automatically collapse (see below). Structures. The tremor deals 50 bludgeoning damage to any structure in contact with the ground in the area when you cast the glyph and at the start of each of your turns until the glyph ends. If a structure drops to 0 hit points, it collapses and potentially damages nearby creatures. A creature within half the distance of a structure's height must make a agility saving throw. On a failed save, the creature takes 5d6 bludgeoning damage, is knocked prone, and is buried in the rubble, requiring a DC 20 Strength (Athletics) check as an action to escape. The DM can adjust the DC higher or lower, depending on the nature of the rubble. On a successful save, the creature takes half as much damage and doesn't fall prone or become buried.</t>
+    <t>You create a seismic disturbance at a point on the ground that you can see within range. For the duration, an intense tremor rips through the ground in a 100-foot-radius circle centered on that point and shakes creatures and structures in contact with the ground in that area. The ground in the area becomes difficult terrain. Each creature on the ground that is concentrating must make a Constitution saving throw. On a failed save, the creature's concentration is broken. When you cast this glyph and at the end of each turn you spend concentrating on it, each creature on the ground in the area must make a agility saving throw. On a failed save, the creature is knocked prone. This glyph can have additional effects depending on the terrain in the area, as determined by the DM. Fissures. Fissures open throughout the glyph's area at the start of your next turn after you cast the glyph. A total of 1d6 such fissures open in locations chosen by the DM. Each is 1d10 x 10 feet deep, 10 feet wide, and extends from one edge of the glyph's area to the opposite side. A creature standing on a spot where a fissure opens must succeed on a agility saving throw or fall in. A creature that successfully saves moves with the fissure's edge as it opens. A fissure that opens beneath a structure causes it to automatically collapse (see below). Structures. The tremor deals 50 bludgeoning damage to any structure in contact with the ground in the area when you cast the glyph and at the start of each of your turns until the glyph ends. If a structure drops to 0 hit points, it collapses and potentially damages nearby creatures. A creature within half the distance of a structure's height must make a agility saving throw. On a failed save, the creature takes 5d6 bludgeoning damage, is knocked prone, and is buried in the rubble, requiring a DC 20 Strength (Athletics) check by spending 2 AP to escape. The DM can adjust the DC higher or lower, depending on the nature of the rubble. On a successful save, the creature takes half as much damage and doesn't fall prone or become buried.</t>
   </si>
   <si>
     <t>Echo Mute</t>
@@ -2148,7 +2148,7 @@
     <t>Enervation</t>
   </si>
   <si>
-    <t>A tendril of inky darkness reaches out from you, touching a creature you can see within range to drain life from it. The target must make a agility saving throw. On a successful save, the target takes 2d8 necrotic damage, and the glyph ends. On a failed save, the target takes 4d8 necrotic damage, and until the glyph ends, you can use your action on each of your turns to automatically deal 4d8 necrotic damage to the target. The glyph ends if you use your action to do anything else, if the target is ever outside the glyph's range, or if the target has total cover from you. Whenever the glyph deals damage to a target, you regain hit points equal to half the amount of necrotic damage the target takes.</t>
+    <t>A tendril of inky darkness reaches out from you, touching a creature you can see within range to drain life from it. The target must make a agility saving throw. On a successful save, the target takes 2d8 necrotic damage, and the glyph ends. On a failed save, the target takes 4d8 necrotic damage, and until the glyph ends, you can spend 2 AP on each of your turns to automatically deal 4d8 necrotic damage to the target. The glyph ends if you spend 2 AP to do anything else, if the target is ever outside the glyph's range, or if the target has total cover from you. Whenever the glyph deals damage to a target, you regain hit points equal to half the amount of necrotic damage the target takes.</t>
   </si>
   <si>
     <t>Enhance Ability</t>
@@ -2175,7 +2175,7 @@
     <t>Ensnaring Strike</t>
   </si>
   <si>
-    <t>The next time you hit a creature with a weapon attack before this glyph ends, a writhing mass of thorny vines appears at the point of impact, and the target must succeed on a Strength saving throw or be restrained by the magical vines until the glyph ends. A Large or larger creature has advantage on this saving throw. If the target succeeds on the save, the vines shrivel away. While restrained by this glyph, the target takes 1d6 piercing damage at the start of each of its turns. A creature restrained by the vines or one that can touch the creature can use its action to make a Strength check against your glyph save DC. On a success, the target is freed.</t>
+    <t>The next time you hit a creature with a weapon attack before this glyph ends, a writhing mass of thorny vines appears at the point of impact, and the target must succeed on a Strength saving throw or be restrained by the magical vines until the glyph ends. A Large or larger creature has advantage on this saving throw. If the target succeeds on the save, the vines shrivel away. While restrained by this glyph, the target takes 1d6 piercing damage at the start of each of its turns. A creature restrained by the vines or one that can touch the creature can spend 2 AP to make a Strength check against your glyph save DC. On a success, the target is freed.</t>
   </si>
   <si>
     <t>If you cast this Glyph using a Glyph slot of 2nd level or higher, the damage increases by 1d6 for each slot level above 1st.</t>
@@ -2187,7 +2187,7 @@
     <t>Entangle</t>
   </si>
   <si>
-    <t>Grasping weeds and vines sprout from the ground in a 20-foot square starting from a point within range. For the duration, these plants turn the ground in the area into difficult terrain. A creature in the area when you cast the glyph must succeed on a Strength saving throw or be restrained by the entangling plants until the glyph ends. A creature restrained by the plants can use its action to make a Strength check against your glyph save DC. On a success, it frees itself. When the glyph ends, the conjured plants wilt away.</t>
+    <t>Grasping weeds and vines sprout from the ground in a 20-foot square starting from a point within range. For the duration, these plants turn the ground in the area into difficult terrain. A creature in the area when you cast the glyph must succeed on a Strength saving throw or be restrained by the entangling plants until the glyph ends. A creature restrained by the plants can spend 2 AP to make a Strength check against your glyph save DC. On a success, it frees itself. When the glyph ends, the conjured plants wilt away.</t>
   </si>
   <si>
     <t>Enthrall</t>
@@ -2263,7 +2263,7 @@
     <t>Expeditious Retreat</t>
   </si>
   <si>
-    <t>This glyph allows you to move at an incredible pace. When you cast this glyph, and then as a bonus action on each of your turns until the glyph ends, you can take the Dash action.</t>
+    <t>This glyph allows you to move at an incredible pace. When you cast this glyph, and then by spending 1 AP on each of your turns until the glyph ends, you can take the Dash action.</t>
   </si>
   <si>
     <t>Explosive Glacier</t>
@@ -2294,7 +2294,7 @@
     <t>Eyebite</t>
   </si>
   <si>
-    <t>For the glyph's duration, your eyes become an inky void imbued with dread power. One creature of your choice within 60 feet of you that you can see must succeed on a wits saving throw or be affected by one of the following effects of your choice for the duration. On each of your turns until the glyph ends, you can use your action to target another creature but can't target a creature again if it has succeeded on a saving throw against this casting of eyebite. Asleep. The target falls unconscious, it wakes up if it takes any damage or if another creature uses its action to shake the sleeper awake. Panicked. The target is frightened of you. On each of its turns, the frightened creature must take the Dash action and move away from you by the safest and shortest available route, unless there is nowhere to move. If the target moves to a place at least 60 feet away from you where it can no longer see you, this effect ends. Sickened. The target has disadvantage ou attack rolls and ability checks. At the end of each of its turns, it can make another wits saving throw. If it succeeds, the effect ends.</t>
+    <t>For the glyph's duration, your eyes become an inky void imbued with dread power. One creature of your choice within 60 feet of you that you can see must succeed on a wits saving throw or be affected by one of the following effects of your choice for the duration. On each of your turns until the glyph ends, you can spend 2 AP to target another creature but can't target a creature again if it has succeeded on a saving throw against this casting of eyebite. Asleep. The target falls unconscious, it wakes up if it takes any damage or if another creature uses its action to shake the sleeper awake. Panicked. The target is frightened of you. On each of its turns, the frightened creature must take the Dash action and move away from you by the safest and shortest available route, unless there is nowhere to move. If the target moves to a place at least 60 feet away from you where it can no longer see you, this effect ends. Sickened. The target has disadvantage ou attack rolls and ability checks. At the end of each of its turns, it can make another wits saving throw. If it succeeds, the effect ends.</t>
   </si>
   <si>
     <t>Fabricate</t>
@@ -2321,7 +2321,7 @@
     <t>Far Step</t>
   </si>
   <si>
-    <t>You teleport up to 60 feet to an unoccupied space you can see. On each of your turns before the glyph ends, you can use a bonus action to teleport in this way again.</t>
+    <t>You teleport up to 60 feet to an unoccupied space you can see. On each of your turns before the glyph ends, you can spend 1 AP to teleport in this way again.</t>
   </si>
   <si>
     <t>Farseeing</t>
@@ -2363,7 +2363,7 @@
     <t>Feign Death</t>
   </si>
   <si>
-    <t>You touch a willing creature and put it into a cataleptic state that is indistinguishable from death. For the glyph's duration, or until you use an action to touch the target and dismiss the glyph, the target appears dead to all outward inspection and to glyphs used to determine the target's status. The target is blinded and incapacitated, and its speed drops to 0. The target has resistance to all damage except psychic damage. If the target is diseased or poisoned when you cast the glyph, or becomes diseased or poisoned while under the glyph's effect, the disease and poison have no effect until the glyph ends.</t>
+    <t>You touch a willing creature and put it into a cataleptic state that is indistinguishable from death. For the glyph's duration, or until you spend 2 AP to touch the target and dismiss the glyph, the target appears dead to all outward inspection and to glyphs used to determine the target's status. The target is blinded and incapacitated, and its speed drops to 0. The target has resistance to all damage except psychic damage. If the target is diseased or poisoned when you cast the glyph, or becomes diseased or poisoned while under the glyph's effect, the disease and poison have no effect until the glyph ends.</t>
   </si>
   <si>
     <t>Fell Aura</t>
@@ -2378,19 +2378,19 @@
     <t>Find Familiar</t>
   </si>
   <si>
-    <t>You gain the service of a familiar, a fallen that takes an animal form you choose: bat, cat, crab, frog (toad), hawk, lizard, octopus, owl, poisonous snake, fish (quipper), rat, raven, sea horse, spider, or weasel. Appearing in an unoccupied space within range, the familiar has the statistics of the chosen form, though it is a celestial, fey, or Netherkin (your choice) instead of a beast. Your familiar acts independently of you, but it always obeys your commands. In combat, it rolls its own initiative and acts on its own turn. A familiar can't attack, but it can take other actions as normal. When the familiar drops to 0 hit points, it disappears, leaving behind no physical form. It reappears after you cast this glyph again. While your familiar is within 100 feet of you, you can communicate with it telepathically. Additionally, as an action, you can see through your familiar's eyes and hear what it hears until the start of your next turn, gaining the benefits of any special senses that the familiar has. During this time, you are deaf and blind with regard to your own senses. As an action, you can temporarily dismiss your familiar. It disappears into a pocket dimension where it awaits your summons. Alternatively, you can dismiss it forever. As an action while it is temporarily dismissed, you can cause it to reappear in any unoccupied space within 30 feet of you. You can't have more than one familiar at a time. If you cast this glyph while you already have a familiar, you instead cause it to adopt a new form. Choose one of the forms from the above list. Your familiar transforms into the chosen creature. Finally, when you cast a glyph with a range of touch, your familiar can deliver the glyph as if it had cast the glyph. Your familiar must be within 100 feet of you, and it must use 1 AP to deliver the glyph when you cast it. If the glyph requires an attack roll, you use your attack modifier for the roll.</t>
+    <t>You gain the service of a familiar, a fallen that takes an animal form you choose: bat, cat, crab, frog (toad), hawk, lizard, octopus, owl, poisonous snake, fish (quipper), rat, raven, sea horse, spider, or weasel. Appearing in an unoccupied space within range, the familiar has the statistics of the chosen form, though it is a celestial, fey, or Netherkin (your choice) instead of a beast. Your familiar acts independently of you, but it always obeys your commands. In combat, it rolls its own initiative and acts on its own turn. A familiar can't attack, but it can take other actions as normal. When the familiar drops to 0 hit points, it disappears, leaving behind no physical form. It reappears after you cast this glyph again. While your familiar is within 100 feet of you, you can communicate with it telepathically. Additionally, by spending 2 AP, you can see through your familiar's eyes and hear what it hears until the start of your next turn, gaining the benefits of any special senses that the familiar has. During this time, you are deaf and blind with regard to your own senses. by spending 2 AP, you can temporarily dismiss your familiar. It disappears into a pocket dimension where it awaits your summons. Alternatively, you can dismiss it forever. by spending 2 AP while it is temporarily dismissed, you can cause it to reappear in any unoccupied space within 30 feet of you. You can't have more than one familiar at a time. If you cast this glyph while you already have a familiar, you instead cause it to adopt a new form. Choose one of the forms from the above list. Your familiar transforms into the chosen creature. Finally, when you cast a glyph with a range of touch, your familiar can deliver the glyph as if it had cast the glyph. Your familiar must be within 100 feet of you, and it must use its reaction to deliver the glyph when you cast it. If the glyph requires an attack roll, you use your attack modifier for the roll.</t>
   </si>
   <si>
     <t>Find Greater Steed</t>
   </si>
   <si>
-    <t>You summon a spirit that assumes the form of a loyal, majestic mount. Appearing in an unoccupied space within range, the spirit takes on a form you choose: Which can be any medium or larger Beast, Monstrosity, Celestial, Daya, or Netherkin. The creature has the statistics provided in the Hunter's Manual for the chosen form, though it is a Celestial, a Daya, or a Netherkin (your choice) instead of its normal creature type. Additionally, if it has a Mind score of 5 or lower, its Mind becomes 6, and it gains the ability to understand one language of your choice that you speak. You control the mount in combat. While the mount is within 1 mile of you, you can communicate with it telepathically. While mounted on it, you can make any glyph you cast that targets only you also target the mount. The mount disappears temporarily when it drops to 0 hit points or when you dismiss it as an action. Casting this glyph again resummons the bonded mount, with all its hit points restored and any conditions removed. You can't have more than one mount bonded by this glyph or find steed at the same time. As an action, you can release a mount from its bond, causing it to disappear permanently. Whenever the mount disappears, it leaves behind any objects it was wearing or carrying.</t>
+    <t>You summon a spirit that assumes the form of a loyal, majestic mount. Appearing in an unoccupied space within range, the spirit takes on a form you choose: Which can be any medium or larger Beast, Monstrosity, Celestial, Daya, or Netherkin. The creature has the statistics provided in the Hunter's Manual for the chosen form, though it is a Celestial, a Daya, or a Netherkin (your choice) instead of its normal creature type. Additionally, if it has a Mind score of 5 or lower, its Mind becomes 6, and it gains the ability to understand one language of your choice that you speak. You control the mount in combat. While the mount is within 1 mile of you, you can communicate with it telepathically. While mounted on it, you can make any glyph you cast that targets only you also target the mount. The mount disappears temporarily when it drops to 0 hit points or when you dismiss it by spending 2 AP. Casting this glyph again resummons the bonded mount, with all its hit points restored and any conditions removed. You can't have more than one mount bonded by this glyph or find steed at the same time. by spending 2 AP, you can release a mount from its bond, causing it to disappear permanently. Whenever the mount disappears, it leaves behind any objects it was wearing or carrying.</t>
   </si>
   <si>
     <t>Find Steed</t>
   </si>
   <si>
-    <t>You summon a spirit that assumes the form of an unusually intelligent, strong, and loyal steed, creating a long-lasting bond with it. Appearing in an unoccupied space within range, the steed takes on a form that you choose, which can be any medium or large sized Beast whose CR is no higher than 0.5. The steed has the statistics of the chosen form, though it is a Celestial, Daya, or Netherkin (your choice) instead of its normal type. Additionally, if your steed has a Mind of 5 or less, its Mind becomes 6, and it gains the ability to understand one language of your choice that you speak. Your steed serves you as a mount, both in combat and out, and you have an instinctive bond with it that allows you to fight as a seamless unit. While mounted on your steed, you can make any glyph you cast that targets only you also target your steed. When the steed drops to 0 hit points, it disappears, leaving behind no physical form. You can also dismiss your steed at any time as an action, causing it to disappear. In either case, casting this glyph again summons the same steed, restored to its hit point maximum. While your steed is within 1 mile of you, you can communicate with it telepathically. You can't have more than one steed bonded by this glyph at a time. As an action, you can release the steed from its bond at any time, causing it to disappear.</t>
+    <t>You summon a spirit that assumes the form of an unusually intelligent, strong, and loyal steed, creating a long-lasting bond with it. Appearing in an unoccupied space within range, the steed takes on a form that you choose, which can be any medium or large sized Beast whose CR is no higher than 0.5. The steed has the statistics of the chosen form, though it is a Celestial, Daya, or Netherkin (your choice) instead of its normal type. Additionally, if your steed has a Mind of 5 or less, its Mind becomes 6, and it gains the ability to understand one language of your choice that you speak. Your steed serves you as a mount, both in combat and out, and you have an instinctive bond with it that allows you to fight as a seamless unit. While mounted on your steed, you can make any glyph you cast that targets only you also target your steed. When the steed drops to 0 hit points, it disappears, leaving behind no physical form. You can also dismiss your steed at any time by spending 2 AP, causing it to disappear. In either case, casting this glyph again summons the same steed, restored to its hit point maximum. While your steed is within 1 mile of you, you can communicate with it telepathically. You can't have more than one steed bonded by this glyph at a time. by spending 2 AP, you can release the steed from its bond at any time, causing it to disappear.</t>
   </si>
   <si>
     <t>Find Traps</t>
@@ -2414,7 +2414,7 @@
     <t>Fire Shield</t>
   </si>
   <si>
-    <t>Thin and wispy flames wreathe your body for the duration, shedding bright light in a 10-foot radius and dim light for an additional 10 feet. You can end the glyph early by using an action to dismiss it. The flames provide you with a warm shield or a chill shield, as you choose. The warm shield grants you resistanee to cold damage, and the chill shield grants you resistanee to fire damage. In addition, whenever a creature within 5 feet of you hits you with a melee attaek, the shield erupts with flame. The attacker takes 2d8 fire damage from a warm shield, or 2d8 cold damage from a cold shield.</t>
+    <t>Thin and wispy flames wreathe your body for the duration, shedding bright light in a 10-foot radius and dim light for an additional 10 feet. You can end the glyph early by spending 2 AP to dismiss it. The flames provide you with a warm shield or a chill shield, as you choose. The warm shield grants you resistanee to cold damage, and the chill shield grants you resistanee to fire damage. In addition, whenever a creature within 5 feet of you hits you with a melee attaek, the shield erupts with flame. The attacker takes 2d8 fire damage from a warm shield, or 2d8 cold damage from a cold shield.</t>
   </si>
   <si>
     <t>Fire Storm</t>
@@ -2454,7 +2454,7 @@
     <t>Flame Blade</t>
   </si>
   <si>
-    <t>You evoke a fiery blade in your free hand. The blade is similar in size and shape to a scimitar, and it lasts for the duration. If you let go of the blade, it disappears, but you can evoke the blade again as a bonus action. You can use your action to make a melee glyph attack with the fiery blade. On a hit, the target takes 3d6 fire damage. The flaming blade sheds bright light in a 10-foot radius and dim light for an additional 10 feet.</t>
+    <t>You evoke a fiery blade in your free hand. The blade is similar in size and shape to a scimitar, and it lasts for the duration. If you let go of the blade, it disappears, but you can evoke the blade again by spending 1 AP. You can spend 2 AP to make a melee glyph attack with the fiery blade. On a hit, the target takes 3d6 fire damage. The flaming blade sheds bright light in a 10-foot radius and dim light for an additional 10 feet.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 4th level or higher, the damage inereases by 1d6 for every two slot levels above 2nd.</t>
@@ -2472,7 +2472,7 @@
     <t>Flaming Sphere</t>
   </si>
   <si>
-    <t>A 5-foot-diameter sphere of fire appears in an unoccupied space of your choice within range and lasts for the duration. Any creature that ends its turn within 5 feet of the sphere must make a agility saving throw. The creature takes 2d6 fire damage on a failed save, or half as much damage on a successful one. As a bonus action, you can move the sphere up to 30 feel. If you ram the sphere into a creature, that creature must make the saving throw against the sphere's damage, and the sphere stops moving this turn. When you move the sphere, you can direct it over barriers up to 5 feet tall and jump it across pits up to 10 feet wide. The sphere ignites flammable objects not being worn or carried, and it sheds bright light in a 20-foot radius and dim light for an additional 20 feel.</t>
+    <t>A 5-foot-diameter sphere of fire appears in an unoccupied space of your choice within range and lasts for the duration. Any creature that ends its turn within 5 feet of the sphere must make a agility saving throw. The creature takes 2d6 fire damage on a failed save, or half as much damage on a successful one. by spending 1 AP, you can move the sphere up to 30 feel. If you ram the sphere into a creature, that creature must make the saving throw against the sphere's damage, and the sphere stops moving this turn. When you move the sphere, you can direct it over barriers up to 5 feet tall and jump it across pits up to 10 feet wide. The sphere ignites flammable objects not being worn or carried, and it sheds bright light in a 20-foot radius and dim light for an additional 20 feel.</t>
   </si>
   <si>
     <t>Flare Star</t>
@@ -2576,7 +2576,7 @@
     <t>Forge Form</t>
   </si>
   <si>
-    <t>Using the art of illusion you may appear different to others. You make one of the alterations to your body; Your hair/facial hair seems to change in length and/or style, You appear to alter the color of your skin, hair, lips or eyes, You fabricate a facial blemish such as a scar, You appear to lose a tooth or multiple teeth, You fabricate a distinct body marking or tattoo. If you cast this glyph multiple times you may have up to three of its effects active at a time, you may dismiss one or multiple effects as an action.</t>
+    <t>Using the art of illusion you may appear different to others. You make one of the alterations to your body; Your hair/facial hair seems to change in length and/or style, You appear to alter the color of your skin, hair, lips or eyes, You fabricate a facial blemish such as a scar, You appear to lose a tooth or multiple teeth, You fabricate a distinct body marking or tattoo. If you cast this glyph multiple times you may have up to three of its effects active at a time, you may dismiss one or multiple effects by spending 2 AP.</t>
   </si>
   <si>
     <t>Fortune's Favor</t>
@@ -2594,7 +2594,7 @@
     <t>Freezing Sphere</t>
   </si>
   <si>
-    <t>A frigid globe of cold energy streaks from your fingertips to a point of your choice within range, where it explodes in a 60-foot-radius sphere. Each creature within the area must make a Constitution saving throw. On a failed save, a creature takes 10d6 cold damage. On a successful save, it takes half as much damage. If the globe strikes a body of water or a liquid that is principally water (not including water-based creatures), it freezes the liquid to a depth of 6 inches over an area 30 feet square. This ice lasts for 1 minute. Creatures that were swimming on the surface of frozen water are trapped in the ice. A trapped creature can use an action to make a Strength check against your glyph save DC to break free. You can refrain from firing the globe after completing the glyph, if you wish. A small globe about the size of a sling stone, cool to the touch, appears in your hand. At any time, you or a creature you give the globe to can throw the globe (to a range of 40 feet) or hurl it with a sling (to the sling's normal range). It shatters on impact, with the same effect as the normal casting of the glyph. You can also set the globe down without shattering it. After 1 minute, if the globe hasn't already shattered, it explodes.</t>
+    <t>A frigid globe of cold energy streaks from your fingertips to a point of your choice within range, where it explodes in a 60-foot-radius sphere. Each creature within the area must make a Constitution saving throw. On a failed save, a creature takes 10d6 cold damage. On a successful save, it takes half as much damage. If the globe strikes a body of water or a liquid that is principally water (not including water-based creatures), it freezes the liquid to a depth of 6 inches over an area 30 feet square. This ice lasts for 1 minute. Creatures that were swimming on the surface of frozen water are trapped in the ice. A trapped creature can spend 2 AP to make a Strength check against your glyph save DC to break free. You can refrain from firing the globe after completing the glyph, if you wish. A small globe about the size of a sling stone, cool to the touch, appears in your hand. At any time, you or a creature you give the globe to can throw the globe (to a range of 40 feet) or hurl it with a sling (to the sling's normal range). It shatters on impact, with the same effect as the normal casting of the glyph. You can also set the globe down without shattering it. After 1 minute, if the globe hasn't already shattered, it explodes.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 7th level or higher, the damage increases by 1d6 for each slot level above 6th.</t>
@@ -2684,7 +2684,7 @@
     <t>30 days</t>
   </si>
   <si>
-    <t>You place a magical command on a creature that you can see within range, forcing it to carry out some service or refrain fram some action or course of activity as you decide. If the creature can understand you, it must succeed on a wits saving throw or become charmed by you for the duration. While the creature is charmed by you, it takes 5d10 psychic damage each time it acts in a manner directly counter to your instructions, but no more than once each day. A creature that can't understand you is unaffected by the glyph. You can issue any command you choose, short of an activity that would result in certain death. Should you issue a suicidal command, the glyph ends. You can end the glyph early by using an action to dismiss it. A remove curse, greater restoration, or wish glyph also ends it.</t>
+    <t>You place a magical command on a creature that you can see within range, forcing it to carry out some service or refrain fram some action or course of activity as you decide. If the creature can understand you, it must succeed on a wits saving throw or become charmed by you for the duration. While the creature is charmed by you, it takes 5d10 psychic damage each time it acts in a manner directly counter to your instructions, but no more than once each day. A creature that can't understand you is unaffected by the glyph. You can issue any command you choose, short of an activity that would result in certain death. Should you issue a suicidal command, the glyph ends. You can end the glyph early by spending 2 AP to dismiss it. A remove curse, greater restoration, or wish glyph also ends it.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 7th or 8th level, the duration is 1 year. When you cast this Glyph using a Glyph slot of 9th level, the Glyph lasts until it is ended by one of the spells mentioned above.</t>
@@ -2699,7 +2699,7 @@
     <t>Ghostwalk</t>
   </si>
   <si>
-    <t>As you activate a stopwatch, you seemingly vanish from existence, leaving behind only the memory of your starting point. You become invisible for the duration, or until you attack, cast a spell, or take damage. While invisible, you can move freely, and when the spell ends, you teleport back to the location where you originally cast the spell. As a bonus action, you can click the stopwatch to immediately teleport back to your original position. You can also choose to end the spell without teleporting, remaining where you are. Even if the invisibility ends early, the teleportation effect still triggers at the conclusion of the spell's duration. You can end the spell early as a bonus action, teleporting back to your original position.</t>
+    <t>As you activate a stopwatch, you seemingly vanish from existence, leaving behind only the memory of your starting point. You become invisible for the duration, or until you attack, cast a spell, or take damage. While invisible, you can move freely, and when the spell ends, you teleport back to the location where you originally cast the spell. by spending 1 AP, you can click the stopwatch to immediately teleport back to your original position. You can also choose to end the spell without teleporting, remaining where you are. Even if the invisibility ends early, the teleportation effect still triggers at the conclusion of the spell's duration. You can end the spell early by spending 1 AP, teleporting back to your original position.</t>
   </si>
   <si>
     <t>At Higher Mana Cost. You can expend extra mana to increase the effects of the glyph, for every 3 additional mana expended the duration of the glyph increases by 1 minute.</t>
@@ -2735,7 +2735,7 @@
     <t>Giant Insect</t>
   </si>
   <si>
-    <t>You transform up to ten centipedes, three spiders, five wasps, or one scorpion within range into giant versions of their natural forms for the duration. A centipede becomes a giant centipede, a spider becomes a giant spider, a wasp becomes a giant wasp, and a scorpion becomes a giant scorpion. Each creature obeys your verbal commands, and in combat, they act on your turn each round. The DM has the statistics for these creatures and resolves their actions and movement. A creature remains in its giant size for the duration, until it draps to 0 hit points, or until you use an action to dismiss the effect on it. The DM might allow you to choose different targets. For example, if you transform a bee, its giant version might have the same statistics as a giant wasp.</t>
+    <t>You transform up to ten centipedes, three spiders, five wasps, or one scorpion within range into giant versions of their natural forms for the duration. A centipede becomes a giant centipede, a spider becomes a giant spider, a wasp becomes a giant wasp, and a scorpion becomes a giant scorpion. Each creature obeys your verbal commands, and in combat, they act on your turn each round. The DM has the statistics for these creatures and resolves their actions and movement. A creature remains in its giant size for the duration, until it draps to 0 hit points, or until you spend 2 AP to dismiss the effect on it. The DM might allow you to choose different targets. For example, if you transform a bee, its giant version might have the same statistics as a giant wasp.</t>
   </si>
   <si>
     <t>Gift of Alacrity</t>
@@ -2783,7 +2783,7 @@
     <t>Goodberry</t>
   </si>
   <si>
-    <t>Up to ten berries appear in your hand and are infused with magic for the duration. A creature can use its action to eat one berry. Eating a berry restores 1 hit point, and the berry provides enough nourishment to sustain a creature for one day. The berries lose their potency if they have not been consumed within 24 hours of the casting of this glyph.</t>
+    <t>Up to ten berries appear in your hand and are infused with magic for the duration. A creature can spend 2 AP to eat one berry. Eating a berry restores 1 hit point, and the berry provides enough nourishment to sustain a creature for one day. The berries lose their potency if they have not been consumed within 24 hours of the casting of this glyph.</t>
   </si>
   <si>
     <t>Grasping Shadow</t>
@@ -2791,7 +2791,7 @@
   <si>
     <t>You command your shadow to slip across the ground and seize that of another creature within range. Make a melee glyph attack against a creature you can see. On a hit, the target’s shadow is bound, and it becomes grappled for the duration.
  While the target remains grappled by this glyph, you can spend 1 AP on your turn to deal 4d6 void damage to it.
- The target may attempt to escape by using its action to make a Strength (Athletics) or Agility (Acrobatics) check against your glyph save DC. You do not contest this check. The glyph immediately ends if the target is exposed to bright light created by a glyph of tier 3 or higher, or if the grapple is broken by any means.</t>
+ The target may attempt to escape by spending 2 AP to make a Strength (Athletics) or Agility (Acrobatics) check against your glyph save DC. You do not contest this check. The glyph immediately ends if the target is exposed to bright light created by a glyph of tier 3 or higher, or if the grapple is broken by any means.</t>
   </si>
   <si>
     <t>When you cast this glyph using a tier 4 or higher, its damage increases by 1d6 per tier above 3.</t>
@@ -2800,7 +2800,7 @@
     <t>Grasping Vine</t>
   </si>
   <si>
-    <t>You conjure a vine that sprouts from the ground in an unoccupied space of your choice that you can see within range. When you cast this glyph, you can direct the vine to lash out at a creature within 30 feet of it that you can see. That creature must succeed on a agility saving throw or be pulled 20 feet directly toward the vine. Until the glyph ends, you can direct the vine to lash out at the same creature or another one as a bonus action on each of your turns.</t>
+    <t>You conjure a vine that sprouts from the ground in an unoccupied space of your choice that you can see within range. When you cast this glyph, you can direct the vine to lash out at a creature within 30 feet of it that you can see. That creature must succeed on a agility saving throw or be pulled 20 feet directly toward the vine. Until the glyph ends, you can direct the vine to lash out at the same creature or another one by spending 1 AP on each of your turns.</t>
   </si>
   <si>
     <t>Grasping Void</t>
@@ -2813,7 +2813,7 @@
  The area becomes difficult terrain for the duration.
  Each creature of your choice in the area when the glyph is activated must succeed on a Strength saving throw or take 2d6 void damage plus your glyphcasting ability modifier, and be pulled prone. On a successful save, the creature takes half as much damage and is not knocked prone.
  Flying creatures make this saving throw with disadvantage, as the hands reach unnaturally toward anything above ground.
- A creature that is already prone when the glyph activates automatically fails the saving throw and is grappled by the spectral hands until the start of your next turn. While grappled in this way, a creature can use its action to make a Strength check against your glyph save DC, ending the grapple on a success.</t>
+ A creature that is already prone when the glyph activates automatically fails the saving throw and is grappled by the spectral hands until the start of your next turn. While grappled in this way, a creature can spend 2 AP to make a Strength check against your glyph save DC, ending the grapple on a success.</t>
   </si>
   <si>
     <t>Gravity Fissure</t>
@@ -2918,7 +2918,7 @@
     <t>Self (60-foot line)</t>
   </si>
   <si>
-    <t>A line of strong wind 60 feet long and 10 feet wide blasts from you in a direction you choose for the glyph's duration. Each creature that starts its turn in the line must succeed on a Strength saving throw or be pushed 15 feet away from you in a direction following the line. Any creature in the line must spend 2 feet of movement for every 1 foot it moves when moving closer to you. The gust disperses gas or vapor, and it extinguishes candles, torches, and similar unprotected flames in the area. It causes protected flames, such as those of lanterns, to dance wildly and has a 50 percent chance to extinguish them. As a bonus action on each of your turns before the glyph ends, you can change the direction in which the line blasts from you.</t>
+    <t>A line of strong wind 60 feet long and 10 feet wide blasts from you in a direction you choose for the glyph's duration. Each creature that starts its turn in the line must succeed on a Strength saving throw or be pushed 15 feet away from you in a direction following the line. Any creature in the line must spend 2 feet of movement for every 1 foot it moves when moving closer to you. The gust disperses gas or vapor, and it extinguishes candles, torches, and similar unprotected flames in the area. It causes protected flames, such as those of lanterns, to dance wildly and has a 50 percent chance to extinguish them. by spending 1 AP on each of your turns before the glyph ends, you can change the direction in which the line blasts from you.</t>
   </si>
   <si>
     <t>Hail of Thorns</t>
@@ -2957,7 +2957,7 @@
     <t>Haste</t>
   </si>
   <si>
-    <t>Choose a willing creature that you can see within range. Until the glyph ends, the target's speed is doubled, it gains a +2 bonus to AC, it has advantage on agility saving throws, and it gains an additional action on each of its turns. That action can be used only to take the Attack (one weapon attack only), Dash, Disengage, Hide, or Use an Object action. When the glyph ends, the target can't move or take actions until after its next turn, as a wave of lethargy sweeps over it.</t>
+    <t>Choose a willing creature that you can see within range. Until the glyph ends, the target's speed is doubled, it gains a +2 bonus to AC, it has advantage on agility saving throws, and it gains an additional 2 AP on each of its turns. This AP can be used only to take the Attack (one weapon attack only), Dash, Disengage, Hide, or Use an Object action. When the glyph ends, the target can't move or spend AP until after its next turn, as a wave of lethargy sweeps over it.</t>
   </si>
   <si>
     <t>Heal</t>
@@ -2982,7 +2982,7 @@
     <t>Healing Spirit</t>
   </si>
   <si>
-    <t>You call forth a nature fallen to soothe the wounded. The intangible fallen appears in a space that is a 5-foot cube you can see within range. The fallen looks like a transparent beast or fey (your choice). Until the glyph ends, whenever you or a creature you can see moves into the fallen's space for the first time on a turn or starts its turn there, you can cause the fallen to restore 1d6 hit points to that creature (no action required). The fallen can't heal constructs or fallen. As a bonus action on your turn, you can move the fallen up to 30 feet to a space you can see.</t>
+    <t>You call forth a nature fallen to soothe the wounded. The intangible fallen appears in a space that is a 5-foot cube you can see within range. The fallen looks like a transparent beast or fey (your choice). Until the glyph ends, whenever you or a creature you can see moves into the fallen's space for the first time on a turn or starts its turn there, you can cause the fallen to restore 1d6 hit points to that creature (no action required). The fallen can't heal constructs or fallen. by spending 1 AP on your turn, you can move the fallen up to 30 feet to a space you can see.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a s pell slot of 3rd level or higher, the healing increases by 1d6 for each slot level above 2nd.</t>
@@ -3000,7 +3000,7 @@
     <t>Heat Metal</t>
   </si>
   <si>
-    <t>Choose a manufactured metal object, such as a metal weapon or a suit of heavy or medium metal armor, that you can see within range. You cause the object to glow red-hot. Any creature in physical contact with the object takes 2d8 fire damage when you cast the glyph. Until the glyph ends, you can use a bonus action on each of your subsequent turns to cause this damage again. If a creature is holding or wearing the object and takes the damage from it, the creature must succeed on a Constitution saving throw or drop the object if it can. If it doesn't drop the object, it has disadvantage on attack rolls and ability checks until the start of your next turn.</t>
+    <t>Choose a manufactured metal object, such as a metal weapon or a suit of heavy or medium metal armor, that you can see within range. You cause the object to glow red-hot. Any creature in physical contact with the object takes 2d8 fire damage when you cast the glyph. Until the glyph ends, you can spend 1 AP on each of your subsequent turns to cause this damage again. If a creature is holding or wearing the object and takes the damage from it, the creature must succeed on a Constitution saving throw or drop the object if it can. If it doesn't drop the object, it has disadvantage on attack rolls and ability checks until the start of your next turn.</t>
   </si>
   <si>
     <t>Hellish Rebuke</t>
@@ -3018,7 +3018,7 @@
     <t>Helping Hand</t>
   </si>
   <si>
-    <t>A spectral, floating hand appears at a point you choose within range. The hand lasts for the duration or until you dismiss it as an action. The hand vanishes if it is ever more than 30 feet away from you or if you cast this glyph again. You can use your action to control the hand. You can use the hand to manipulate an object, open an unlocked doar or container, stow or retrieve an item from an open container, or pour the contents out of a vial. You can move the hand up to 30 feet each time you use it. The hand can't attack, activate magic items, or carry more than 10 pounds.</t>
+    <t>A spectral, floating hand appears at a point you choose within range. The hand lasts for the duration or until you dismiss it by spending 2 AP. The hand vanishes if it is ever more than 30 feet away from you or if you cast this glyph again. You can spend 2 AP to control the hand. You can use the hand to manipulate an object, open an unlocked doar or container, stow or retrieve an item from an open container, or pour the contents out of a vial. You can move the hand up to 30 feet each time you use it. The hand can't attack, activate magic items, or carry more than 10 pounds.</t>
   </si>
   <si>
     <t>Heroes' Feast</t>
@@ -3066,7 +3066,7 @@
     <t>Holy Weapon</t>
   </si>
   <si>
-    <t>You imbue a weapon you touch with holy power. Until the glyph ends, the weapon emits bright light in a 30-foot radius and dim light for an additional 30 feet. In addition, weapon attacks made with it deal an extra 2d8 radiant damage on a hit. If the weapon isn't already a magic weapon, it becomes one for the duration. As a bonus action on your turn, you can dismiss this glyph and cause the weapon to emit a burst of radiance. Each creature of your choice that you can see within 30 feet of you must make a Constitution saving throw. On a failed save, a creature takes 4d8 radiant damage, and it is blinded for 1 minute. On a successful save, a creature takes half as much damage and isn't blinded. At the end of each of its turns, a blinded creature can make a Constitution saving throw, ending the effect on itself on a success.</t>
+    <t>You imbue a weapon you touch with holy power. Until the glyph ends, the weapon emits bright light in a 30-foot radius and dim light for an additional 30 feet. In addition, weapon attacks made with it deal an extra 2d8 radiant damage on a hit. If the weapon isn't already a magic weapon, it becomes one for the duration. by spending 1 AP on your turn, you can dismiss this glyph and cause the weapon to emit a burst of radiance. Each creature of your choice that you can see within 30 feet of you must make a Constitution saving throw. On a failed save, a creature takes 4d8 radiant damage, and it is blinded for 1 minute. On a successful save, a creature takes half as much damage and isn't blinded. At the end of each of its turns, a blinded creature can make a Constitution saving throw, ending the effect on itself on a success.</t>
   </si>
   <si>
     <t>Host Wellspring</t>
@@ -3103,7 +3103,7 @@
     <t>Hypnotic Pattern</t>
   </si>
   <si>
-    <t>You create a twisting pattern of colors that weaves through the air inside a 30-foot cube within range. The pattern appears for a moment and vanishes. Each creature in the area who sees the pattern must make a wits saving throw. On a failed save, the creature becomes charmed for the duration. While charmed by this glyph, the creature is incapacitated and has a speed of 0. The glyph ends for an affected creature if it takes any damage or if someone else uses an action to shake the creature out of its stupor.</t>
+    <t>You create a twisting pattern of colors that weaves through the air inside a 30-foot cube within range. The pattern appears for a moment and vanishes. Each creature in the area who sees the pattern must make a wits saving throw. On a failed save, the creature becomes charmed for the duration. While charmed by this glyph, the creature is incapacitated and has a speed of 0. The glyph ends for an affected creature if it takes any damage or if someone else spends 2 AP to shake the creature out of its stupor.</t>
   </si>
   <si>
     <t>Ice Beam</t>
@@ -3142,7 +3142,7 @@
     <t>Illusory Dragon</t>
   </si>
   <si>
-    <t>By gathering threads of shadow material from the Shadowfell, you create a Huge shadowy dragon in an unoccupied space that you can see within range. The illusion lasts for the glyph's duration and occupies its space, as if it were a creature. When the illusion appears, any of your enemies that can see it must succeed on a wits saving throw or become frightened of it for 1 minute. If a frightened creature ends its turn in a location where it doesn't have line of sight to the illusion, it can repeat the saving throw, ending the effect on itself on a success. As a bonus action on your turn, you can move the illusion up to 60 feet. At any point during its movement, you can cause it to exhale a blast of energy in a 60-foot cone originating from its space. When you create the dragon, choose a damage type: acid, cold, fire, lightning, necrotic, or poison. Each creature in the cone must make an mind saving throw, taking 7d6 damage of the chosen damage type on a failed save, or half as much damage on a successful one. The illusion is tangible because of the shadow stuff used to create it, but attacks miss it automatically, it succeeds on all saving throws, and it is immune to all damage and conditions. A creature that uses an action to examine the dragon can determine that it is an illusion by succeeding on an mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through it and has advantage on saving throws against its breath.</t>
+    <t>By gathering threads of shadow material from the Shadowfell, you create a Huge shadowy dragon in an unoccupied space that you can see within range. The illusion lasts for the glyph's duration and occupies its space, as if it were a creature. When the illusion appears, any of your enemies that can see it must succeed on a wits saving throw or become frightened of it for 1 minute. If a frightened creature ends its turn in a location where it doesn't have line of sight to the illusion, it can repeat the saving throw, ending the effect on itself on a success. by spending 1 AP on your turn, you can move the illusion up to 60 feet. At any point during its movement, you can cause it to exhale a blast of energy in a 60-foot cone originating from its space. When you create the dragon, choose a damage type: acid, cold, fire, lightning, necrotic, or poison. Each creature in the cone must make an mind saving throw, taking 7d6 damage of the chosen damage type on a failed save, or half as much damage on a successful one. The illusion is tangible because of the shadow stuff used to create it, but attacks miss it automatically, it succeeds on all saving throws, and it is immune to all damage and conditions. A creature that spends 2 AP to examine the dragon can determine that it is an illusion by succeeding on an mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through it and has advantage on saving throws against its breath.</t>
   </si>
   <si>
     <t>Illusory Script</t>
@@ -3172,7 +3172,7 @@
     <t>Immovable Object</t>
   </si>
   <si>
-    <t>You touch an object that weighs no more than 10 pounds and cause it to become magically fixed in place. You and the creatures you designate when you cast this glyph can move the object normally. You can also set a password that, when spoken within 5 feet of the object, suppresses this glyph for 1 minute. If the object is fixed in the air, it can hold up to 4000 pounds of weight. More weight causes the object to fall. Otherwise, a creature can use an action to make a Strength check against your glyph save DC. On a success, the creature can move the object up to 10 feet.</t>
+    <t>You touch an object that weighs no more than 10 pounds and cause it to become magically fixed in place. You and the creatures you designate when you cast this glyph can move the object normally. You can also set a password that, when spoken within 5 feet of the object, suppresses this glyph for 1 minute. If the object is fixed in the air, it can hold up to 4000 pounds of weight. More weight causes the object to fall. Otherwise, a creature can spend 2 AP to make a Strength check against your glyph save DC. On a success, the creature can move the object up to 10 feet.</t>
   </si>
   <si>
     <t>If you cast this Glyph using a Glyph slot of 4th or 5th level, the DC to move the object increases by 5, it can carry up to 8000 pounds of weight, and the duration increases to 24 hours. If you cast this Glyph using a Glyph slot of 6th level or higher, the DC to move the object increases by 10, it can carry up to 20000 pounds of weight, and the effect is permanent until dispelled.</t>
@@ -3226,25 +3226,25 @@
     <t>Investiture of Flame</t>
   </si>
   <si>
-    <t>Flames race across your body, shedding bright light in a 30-foot radius and dim light for an additional 30 feet for the glyph's duration. The flames don't harm you. Until the glyph ends, you gain the following benefits: You are immune to fire damage and have resistance to cold damage; Any creature that moves within 5 feet of you for the first time on a turn or ends its turn there takes 1d10 fire damage; You can use your action to create a line of fire 15 feet long and 5 feet wide extending from you in a direction you choose. Each creature in the line must make a agility saving throw. A creature takes 4d8 fire damage on a failed save, or half as much damage on a successful one.</t>
+    <t>Flames race across your body, shedding bright light in a 30-foot radius and dim light for an additional 30 feet for the glyph's duration. The flames don't harm you. Until the glyph ends, you gain the following benefits: You are immune to fire damage and have resistance to cold damage; Any creature that moves within 5 feet of you for the first time on a turn or ends its turn there takes 1d10 fire damage; You can spend 2 AP to create a line of fire 15 feet long and 5 feet wide extending from you in a direction you choose. Each creature in the line must make a agility saving throw. A creature takes 4d8 fire damage on a failed save, or half as much damage on a successful one.</t>
   </si>
   <si>
     <t>Investiture of Ice</t>
   </si>
   <si>
-    <t>Until the glyph ends, ice rimes your body, and you gain the following benefits: You are immune to cold damage and have resistance to fire damage; You can move across difficult terrain created by ice or snow without spending extra movement; The ground in a 10-foot radius around you is icy and is difficult terra in for creatures other than you. The radius moves with you; You can use your action to create a 15-foot cone of freezing wind extending from your outstretched hand in a direction you choose. Each creature in the cone must make a Constitution saving throw. A creature takes 4d6 cold damage on a failed save, or half as much damage on a successful one. A creature that fails its save against this effect has its speed halved until the start of your next turn.</t>
+    <t>Until the glyph ends, ice rimes your body, and you gain the following benefits: You are immune to cold damage and have resistance to fire damage; You can move across difficult terrain created by ice or snow without spending extra movement; The ground in a 10-foot radius around you is icy and is difficult terra in for creatures other than you. The radius moves with you; You can spend 2 AP to create a 15-foot cone of freezing wind extending from your outstretched hand in a direction you choose. Each creature in the cone must make a Constitution saving throw. A creature takes 4d6 cold damage on a failed save, or half as much damage on a successful one. A creature that fails its save against this effect has its speed halved until the start of your next turn.</t>
   </si>
   <si>
     <t>Investiture of Stone</t>
   </si>
   <si>
-    <t>Until the glyph ends, bits of rock spread across your body, and you gain the following benefits: You have resistance to bludgeoning, piercing, and slashing damage from nonmagical attacks; You can use your action to create a small earthquake on the ground in a 15-foot radius centered on you. Other creatures on that ground must succeed on a agility saving throw or be knocked prone; You can move across difficult terrain made of earth or stone without spending extra movement. You can move through solid earth or stone as if it was air and without destabilizing it, but you can't end your movement there. If you do so, you are ejected to the nearest unoccupied space, this glyph ends, and you are stunned until the end of your next turn.</t>
+    <t>Until the glyph ends, bits of rock spread across your body, and you gain the following benefits: You have resistance to bludgeoning, piercing, and slashing damage from nonmagical attacks; You can spend 2 AP to create a small earthquake on the ground in a 15-foot radius centered on you. Other creatures on that ground must succeed on a agility saving throw or be knocked prone; You can move across difficult terrain made of earth or stone without spending extra movement. You can move through solid earth or stone as if it was air and without destabilizing it, but you can't end your movement there. If you do so, you are ejected to the nearest unoccupied space, this glyph ends, and you are stunned until the end of your next turn.</t>
   </si>
   <si>
     <t>Investiture of Wind</t>
   </si>
   <si>
-    <t>Until the glyph ends, wind whirls a round you, and you gain the following benefits: Ranged weapon attacks made against you have disadvantage on the attack roll; You gain a flying speed of 60 feet. If you are still flying when the glyph ends, you fall, unless you can somehow prevent it; You can use your action to create a 15-foot cube of swirling wind centered on a point you can see within 60 feet of you. Each creature in that area must make a Constitution saving throw. A creature takes 2d10 bludgeoning damage on a failed save, or half as much damage on a successful one. If a Large or smaller creature fails the save, that creature is also pushed up to 10 feet away from the center of the cube.</t>
+    <t>Until the glyph ends, wind whirls a round you, and you gain the following benefits: Ranged weapon attacks made against you have disadvantage on the attack roll; You gain a flying speed of 60 feet. If you are still flying when the glyph ends, you fall, unless you can somehow prevent it; You can spend 2 AP to create a 15-foot cube of swirling wind centered on a point you can see within 60 feet of you. Each creature in that area must make a Constitution saving throw. A creature takes 2d10 bludgeoning damage on a failed save, or half as much damage on a successful one. If a Large or smaller creature fails the save, that creature is also pushed up to 10 feet away from the center of the cube.</t>
   </si>
   <si>
     <t>Invisibility</t>
@@ -3323,7 +3323,7 @@
     <t>Levitate</t>
   </si>
   <si>
-    <t>One creature or object of your choice that you can see within range rises vertically, up to 20 feet, and remains suspended there for the duration. The glyph can levitate a target that weighs up to 500 pounds. An unwilling creature that succeeds on a Constitution saving throw is unaffected. The target can move only by pushing or pulling against a fixed object or surface within reach (such as a wall or a ceiling), which allows it to move as if it were climbing. You can change the target's altitude by up to 20 feet in either direction on your turn. If you are the target, you can move up or down as part of your move. Otherwise, you can use your action to move the target, which must remain within the glyph's range. When the glyph ends, the target floats gently to the ground if it is still aloft.</t>
+    <t>One creature or object of your choice that you can see within range rises vertically, up to 20 feet, and remains suspended there for the duration. The glyph can levitate a target that weighs up to 500 pounds. An unwilling creature that succeeds on a Constitution saving throw is unaffected. The target can move only by pushing or pulling against a fixed object or surface within reach (such as a wall or a ceiling), which allows it to move as if it were climbing. You can change the target's altitude by up to 20 feet in either direction on your turn. If you are the target, you can move up or down as part of your move. Otherwise, you can spend 2 AP to move the target, which must remain within the glyph's range. When the glyph ends, the target floats gently to the ground if it is still aloft.</t>
   </si>
   <si>
     <t>Life Drinker</t>
@@ -3359,7 +3359,7 @@
     <t>Light</t>
   </si>
   <si>
-    <t>You touch one object that is no larger than 10 feet in any dimension. Until the glyph ends, the object sheds bright light in a 20-foot radius and dim light for an additional 20 feet. The light can be colored as you like. Completely covering the object with something opaque blocks the light. The glyph ends if you cast it again or dismiss it as an action. If you target an object held or worn by a hostile creature, that creature must succeed on a agility saving throw to avoid the glyph.</t>
+    <t>You touch one object that is no larger than 10 feet in any dimension. Until the glyph ends, the object sheds bright light in a 20-foot radius and dim light for an additional 20 feet. The light can be colored as you like. Completely covering the object with something opaque blocks the light. The glyph ends if you cast it again or dismiss it by spending 2 AP. If you target an object held or worn by a hostile creature, that creature must succeed on a agility saving throw to avoid the glyph.</t>
   </si>
   <si>
     <t>Lightning Arrow</t>
@@ -3528,7 +3528,7 @@
     <t>Major Image</t>
   </si>
   <si>
-    <t>You create the image of an object, a creature, or some other visible phenomenon that is no larger than a 20-foot cube. The image appears at a spot that you can see within range and lasts for the duration. It seems completely real, including sounds, smells, and temperature appropriate to the thing depicted. You can't create sufficient heat or cold to cause damage, a sound loud enough to deal thunder damage or deafen a creature, or a smell that might sicken a creature (like a troglodyte's stench). As long as you are within range of the illusion, you can use your action to cause the image to move to any other spot within range. As the image changes location, you can alter its appearance so that its movements appear natural for the image. For example, if you create an image of a creature and move it, you can alter the image so that it appears to be walking. Similarly, you can cause the illusion to make different sounds at different times, even making it carry on a conversation, for example. Physical interaction with the image reveals it to be an illusion, because things can pass through it. A creature that uses its action to examine the image can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through the image, and its other sensory qualities become faint to the creature.</t>
+    <t>You create the image of an object, a creature, or some other visible phenomenon that is no larger than a 20-foot cube. The image appears at a spot that you can see within range and lasts for the duration. It seems completely real, including sounds, smells, and temperature appropriate to the thing depicted. You can't create sufficient heat or cold to cause damage, a sound loud enough to deal thunder damage or deafen a creature, or a smell that might sicken a creature (like a troglodyte's stench). As long as you are within range of the illusion, you can spend 2 AP to cause the image to move to any other spot within range. As the image changes location, you can alter its appearance so that its movements appear natural for the image. For example, if you create an image of a creature and move it, you can alter the image so that it appears to be walking. Similarly, you can cause the illusion to make different sounds at different times, even making it carry on a conversation, for example. Physical interaction with the image reveals it to be an illusion, because things can pass through it. A creature that uses its action to examine the image can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through the image, and its other sensory qualities become faint to the creature.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 6th level or higher, the Glyph lasts until dispelled, without requiring your concentration.</t>
@@ -3605,7 +3605,7 @@
     <t>Mark of Recall</t>
   </si>
   <si>
-    <t>You touch an object weighing 10 pounds or less whose longest dimension is 6 feet or less. The glyph leaves an invisible mark on its surface and invisibly inscribes the name of the item on the sapphire you use as the material component. Each time you cast this glyph, you must use a different sapphire. At any time thereafter, you can use your action to speak the item's name and crush the sapphire. The item instantly appears in your hand regardless of physical or planar distances, and the glyph ends. If another creature is holding or carrying the item, crushing the sapphire doesn't transport the item to you, but instead you learn who the creature possessing the object is and roughly where that creature is located at that moment. Dispel magic or a similar effect successfully applied to the sapphire ends this glyph's effect.</t>
+    <t>You touch an object weighing 10 pounds or less whose longest dimension is 6 feet or less. The glyph leaves an invisible mark on its surface and invisibly inscribes the name of the item on the sapphire you use as the material component. Each time you cast this glyph, you must use a different sapphire. At any time thereafter, you can spend 2 AP to speak the item's name and crush the sapphire. The item instantly appears in your hand regardless of physical or planar distances, and the glyph ends. If another creature is holding or carrying the item, crushing the sapphire doesn't transport the item to you, but instead you learn who the creature possessing the object is and roughly where that creature is located at that moment. Dispel magic or a similar effect successfully applied to the sapphire ends this glyph's effect.</t>
   </si>
   <si>
     <t>Marvelous Construction Efficiency</t>
@@ -3659,7 +3659,7 @@
     <t>Maze</t>
   </si>
   <si>
-    <t>You banish a creature that you can see within range into a labyrinthine demiplane. The target remains there for the duration or until it escapes the maze. The target can use its action to altempt to escape. When it does so, it makes a DC 20 mind check. If it succeeds, it escapes, and the glyph ends (a minotaur or goristro Netherkin automatically succeeds). When the glyph ends, the target reappears in the space it left or, if that space is occupied, in the nearest unoccupied space.</t>
+    <t>You banish a creature that you can see within range into a labyrinthine demiplane. The target remains there for the duration or until it escapes the maze. The target can spend 2 AP to altempt to escape. When it does so, it makes a DC 20 mind check. If it succeeds, it escapes, and the glyph ends (a minotaur or goristro Netherkin automatically succeeds). When the glyph ends, the target reappears in the space it left or, if that space is occupied, in the nearest unoccupied space.</t>
   </si>
   <si>
     <t>Maze of Shades</t>
@@ -3699,7 +3699,7 @@
     <t>Meteor Orbit</t>
   </si>
   <si>
-    <t>You create six tiny meteors in your space. They float in the air and orbit you for the glyph's duration. When you cast the glyph - and as a bonus action on each of your turns thereafter - you can expend one or two of the meteors, sending them streaking toward a point or points you choose within 120 feet of you. Once a meteor reaches its destination or impacts against a solid surface, the meteor explodes. Each creature within 5 feet of the point whe re the meteor explodes must make a agility saving throw. A creature takes 2d6 fire damage on a failed save, or half as much damage on a successful one.</t>
+    <t>You create six tiny meteors in your space. They float in the air and orbit you for the glyph's duration. When you cast the glyph - and by spending 1 AP on each of your turns thereafter - you can expend one or two of the meteors, sending them streaking toward a point or points you choose within 120 feet of you. Once a meteor reaches its destination or impacts against a solid surface, the meteor explodes. Each creature within 5 feet of the point whe re the meteor explodes must make a agility saving throw. A creature takes 2d6 fire damage on a failed save, or half as much damage on a successful one.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 4th level or higher, the number of meteors created increases by two for each slot level above 3rd.</t>
@@ -3774,7 +3774,7 @@
     <t>Minor Illusion</t>
   </si>
   <si>
-    <t>You create a sound or an image of an object within range that lasts for the duration. The illusion also ends if you dismiss it as an action or cast this glyph again. If you create a sound, its volume can range from a whisper to a scream. It can be your voice, someone else's voice, a lion's roar, a beating of drums, or any other sound you choose. The sound continues unabated throughout the duration, or you can make discrete sounds at different times before the glyph ends. If you create an image of an object - such as a chair, muddy footprints, or a small chest - it must be no larger than a 5-foot cube. The image can't create sound, light, smell, or any other sensory effect. Physical interaction with the image reveals it to be an illusion, because things can pass through it. If a creature uses its action to examine the sound or image, the creature can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the illusion becomes faint to the creature.</t>
+    <t>You create a sound or an image of an object within range that lasts for the duration. The illusion also ends if you dismiss it by spending 2 AP or cast this glyph again. If you create a sound, its volume can range from a whisper to a scream. It can be your voice, someone else's voice, a lion's roar, a beating of drums, or any other sound you choose. The sound continues unabated throughout the duration, or you can make discrete sounds at different times before the glyph ends. If you create an image of an object - such as a chair, muddy footprints, or a small chest - it must be no larger than a 5-foot cube. The image can't create sound, light, smell, or any other sensory effect. Physical interaction with the image reveals it to be an illusion, because things can pass through it. If a creature uses its action to examine the sound or image, the creature can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the illusion becomes faint to the creature.</t>
   </si>
   <si>
     <t>Mirage Arcane</t>
@@ -3789,13 +3789,13 @@
     <t>Mirror Image</t>
   </si>
   <si>
-    <t>Three illusory duplicates of yourself appear in your space. Until the glyph ends, the duplicates move with you and mimic your actions, shifting position so it's impossible to track which image is real. You can use your action to dismiss the illusory duplicates. Each time a creature targets you with an attack during the glyph's duration, roll a d20 to determine whether the attack instead targets one of your duplicates. If you have three duplicates, you must roll a 6 or higher to change the attack's target to a duplicate. With two duplicates, you must roll an 8 or higher. With one duplicate, you must roll an 11 or higher. A duplicate's AC equals 10 + your agility modifier. If an attack hits a duplicate, the duplicate is destroyed. A duplicate can be destroyed only by an attack that hits it. It ignores all other damage and effects. The glyph ends when all three duplicates are destroyed. A creature is unaffected by this glyph if it can't see, if it relies on senses other than sight, such as blindsight, or if it can perceive illusions as false, as with truesight.</t>
+    <t>Three illusory duplicates of yourself appear in your space. Until the glyph ends, the duplicates move with you and mimic your actions, shifting position so it's impossible to track which image is real. You can spend 2 AP to dismiss the illusory duplicates. Each time a creature targets you with an attack during the glyph's duration, roll a d20 to determine whether the attack instead targets one of your duplicates. If you have three duplicates, you must roll a 6 or higher to change the attack's target to a duplicate. With two duplicates, you must roll an 8 or higher. With one duplicate, you must roll an 11 or higher. A duplicate's AC equals 10 + your agility modifier. If an attack hits a duplicate, the duplicate is destroyed. A duplicate can be destroyed only by an attack that hits it. It ignores all other damage and effects. The glyph ends when all three duplicates are destroyed. A creature is unaffected by this glyph if it can't see, if it relies on senses other than sight, such as blindsight, or if it can perceive illusions as false, as with truesight.</t>
   </si>
   <si>
     <t>Mislead</t>
   </si>
   <si>
-    <t>You become invisible at the same time that an illusory double of you appears where you are standing. The double lasts for the duration, but the invisibility ends if you attack or cast a glyph. You can use your action to move your illusory double up to twice your speed and make it gesture, speak, and behave in whatever way you choose. You can see through its eyes and hear through its ears as if you were located where it is. On each of your turns as a bonus action, you can switch from using its senses to using your own, or back again. While you are using its senses, you are blinded and deafened in regard to your own surroundings.</t>
+    <t>You become invisible at the same time that an illusory double of you appears where you are standing. The double lasts for the duration, but the invisibility ends if you attack or cast a glyph. You can spend 2 AP to move your illusory double up to twice your speed and make it gesture, speak, and behave in whatever way you choose. You can see through its eyes and hear through its ears as if you were located where it is. On each of your turns by spending 1 AP, you can switch from using its senses to using your own, or back again. While you are using its senses, you are blinded and deafened in regard to your own surroundings.</t>
   </si>
   <si>
     <t>Misty Step</t>
@@ -3816,7 +3816,7 @@
     <t>Mold Earth</t>
   </si>
   <si>
-    <t>You choose a portion of dirt or stone that you can see within range and that fits within a 5-foot cube. You manipulate it in one of the following ways: If you target an area of loose earth, you can instantaneously excavate it, move it along the ground, and deposit it up to 5 feet away. This movement doesn't involve enough force to cause damage; You cause shapes, colors, or both to appear on the dirt or stone, spelling out words, creating images, or shaping patterns. The changes last for 1 hour; If the dirt or stone you target is on the ground, you cause it to become difficult terrain. Alternatively, you can cause the ground to become normal terrain if it is already difficult terrain. This change lasts for 1 hour. If you cast this glyph multiple times, you can have no more than two of its non-instantaneous effects active at a time, and you can dismiss such an effect as an action.</t>
+    <t>You choose a portion of dirt or stone that you can see within range and that fits within a 5-foot cube. You manipulate it in one of the following ways: If you target an area of loose earth, you can instantaneously excavate it, move it along the ground, and deposit it up to 5 feet away. This movement doesn't involve enough force to cause damage; You cause shapes, colors, or both to appear on the dirt or stone, spelling out words, creating images, or shaping patterns. The changes last for 1 hour; If the dirt or stone you target is on the ground, you cause it to become difficult terrain. Alternatively, you can cause the ground to become normal terrain if it is already difficult terrain. This change lasts for 1 hour. If you cast this glyph multiple times, you can have no more than two of its non-instantaneous effects active at a time, and you can dismiss such an effect by spending 2 AP.</t>
   </si>
   <si>
     <t>Molotov</t>
@@ -3831,7 +3831,7 @@
     <t>Moonbeam</t>
   </si>
   <si>
-    <t>A silvery beam of pale light shines down in a 5-foot-radius, 40-foot-high cylinder centered on a point within range. Until the glyph ends, dim light fills the cylinder. When a creature enters the glyph's area for the first time on a turn or starts its turn there, it is engulfed in ghostly flames that cause searing pain, and it must make a Constitution saving throw. It takes 2d10 radiant damage on a failed save, or half as much damage on a successful one. A shapechanger makes its saving throw with disadvantage. If it fails, it also instantly reverts to its original form and can't assume a different form until it leaves the glyph's light. On each of your turns after you cast this glyph, you can use an action to move the beam 60 feet in any direction.</t>
+    <t>A silvery beam of pale light shines down in a 5-foot-radius, 40-foot-high cylinder centered on a point within range. Until the glyph ends, dim light fills the cylinder. When a creature enters the glyph's area for the first time on a turn or starts its turn there, it is engulfed in ghostly flames that cause searing pain, and it must make a Constitution saving throw. It takes 2d10 radiant damage on a failed save, or half as much damage on a successful one. A shapechanger makes its saving throw with disadvantage. If it fails, it also instantly reverts to its original form and can't assume a different form until it leaves the glyph's light. On each of your turns after you cast this glyph, you can spend 2 AP to move the beam 60 feet in any direction.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 3rd level or higher, the damage increases by 1d10 for each slot level above 2nd.</t>
@@ -3903,7 +3903,7 @@
     <t>Nemesis' Sword</t>
   </si>
   <si>
-    <t>You create a sword-shaped plane of force that hovers within range. It lasts for the duration. When the sword appears, you make a melee glyph attack against a target of your choice within 5 feet of the sword. On a hit, the target takes 3d10 force damage. Until the glyph ends, you can use a bonus action on each of your turns to move the sword up to 20 feet to a spot you can see and repeat this attack against the same target or a different one.</t>
+    <t>You create a sword-shaped plane of force that hovers within range. It lasts for the duration. When the sword appears, you make a melee glyph attack against a target of your choice within 5 feet of the sword. On a hit, the target takes 3d10 force damage. Until the glyph ends, you can spend 1 AP on each of your turns to move the sword up to 20 feet to a spot you can see and repeat this attack against the same target or a different one.</t>
   </si>
   <si>
     <t>Nephalsted's Transformation</t>
@@ -3927,7 +3927,7 @@
     <t>30 Feet</t>
   </si>
   <si>
-    <t>You summon a spirit that assumes the form of a loyal, majestic mount. Appearing in an unoccupied space within range, the spirit takes on a form you choose: Any non-humanoid creature, at least one size-category larger than you, whose CR is no greater than 5. The creature has the statistics provided in the Hunter's Manual for the chosen form, though it is a Celestial, a Daya, or a Netherkin (your choice) instead of its normal creature type. Additionally, if it has a Mind score of 5 or lower, its Mind becomes 6, and it gains the ability to understand one language of your choice that you speak. You control the mount in combat. While the mount is within 1 mile of you, you can communicate with it telepathically. While mounted on it, you can make any glyph you cast that targets only you also target the mount. The mount disappears temporarily when it drops to 0 hit points or when you dismiss it as an action. Casting this glyph again resummons the bonded mount, with all its hit points restored and any conditions removed. You can't have more than one mount bonded by this glyph, find greater steed, or find steed at the same time. As an action, you can release a mount from its bond, causing it to disappear permanently. Whenever the mount disappears, it leaves behind any objects it was wearing or carrying.</t>
+    <t>You summon a spirit that assumes the form of a loyal, majestic mount. Appearing in an unoccupied space within range, the spirit takes on a form you choose: Any non-humanoid creature, at least one size-category larger than you, whose CR is no greater than 5. The creature has the statistics provided in the Hunter's Manual for the chosen form, though it is a Celestial, a Daya, or a Netherkin (your choice) instead of its normal creature type. Additionally, if it has a Mind score of 5 or lower, its Mind becomes 6, and it gains the ability to understand one language of your choice that you speak. You control the mount in combat. While the mount is within 1 mile of you, you can communicate with it telepathically. While mounted on it, you can make any glyph you cast that targets only you also target the mount. The mount disappears temporarily when it drops to 0 hit points or when you dismiss it by spending 2 AP. Casting this glyph again resummons the bonded mount, with all its hit points restored and any conditions removed. You can't have more than one mount bonded by this glyph, find greater steed, or find steed at the same time. by spending 2 AP, you can release a mount from its bond, causing it to disappear permanently. Whenever the mount disappears, it leaves behind any objects it was wearing or carrying.</t>
   </si>
   <si>
     <t>Nova</t>
@@ -3957,7 +3957,7 @@
     <t>Paco's Irresistible Dance</t>
   </si>
   <si>
-    <t>Choose one creature that you can see within range. The target begins a comic dance in place: shuffling, tapping its feet, and capering for the duration. Creatures that can't be charmed are immune to this glyph. A dancing creature must use all its movement to dance without leaving its space and has disadvantage on agility saving throws and attack rolls. While the target is affected by this glyph, other creatures have advantage on attack rolls against it. As an action, a dancing creature makes a wits saving throw to regain control of itself. On a successful save, the glyph ends.</t>
+    <t>Choose one creature that you can see within range. The target begins a comic dance in place: shuffling, tapping its feet, and capering for the duration. Creatures that can't be charmed are immune to this glyph. A dancing creature must use all its movement to dance without leaving its space and has disadvantage on agility saving throws and attack rolls. While the target is affected by this glyph, other creatures have advantage on attack rolls against it. by spending 2 AP, a dancing creature makes a wits saving throw to regain control of itself. On a successful save, the glyph ends.</t>
   </si>
   <si>
     <t>Pass without Trace</t>
@@ -3975,7 +3975,7 @@
     <t>Phantasmal Force</t>
   </si>
   <si>
-    <t>You craft an illusion that takes root in the mind of a creature that you can see within range. The target must make an mind saving throw. On a failed save, you create a phantasmal object, creature, or other visible phenomenon of your choice that is no larger than a 10-foot cube and that is perceivable only to the target for the duration. This glyph has no effect on fallen or constructs. The phantasm includes sound, temperature, and other stimuli, also evident only to the creature. The target can use its action to examine the phantasm with an mind (Investigation) check against your glyph save DC. If the check succeeds, the target realizes that the phantasm is an illusion, and the glyph ends. While a target is affected by the glyph, the target treats the phantasm as if it were real. The target rationalizes any illogical outcomes from interacting with the phantasm. For example, a target attempting to walk across a phantasmal bridge that spans a chasm falls once it steps anta the bridge. If the target survives the fall, it still believes that the bridge exists and comes up with some other explanation for its fall - it was pushed, it slipped, or a strong wind might have knocked it off. An affected target is so convinced of the phantasm's reality that it can even take damage from the illusion. A phantasm created to appear as a creature can attack the target. Similarly, a phantasm created to appear as fire, a pool of acid, or lava can burn the target. Each round on your turn, the phantasm can deal 1d6 psychic damage to the target if it is in the phantasm's area or within 5 feet of the phantasm, provided that the illusion is of a creature or hazard that could logically deal damage, such as by attacking, The target perceives the damage as a type appropriate to the illusion.</t>
+    <t>You craft an illusion that takes root in the mind of a creature that you can see within range. The target must make an mind saving throw. On a failed save, you create a phantasmal object, creature, or other visible phenomenon of your choice that is no larger than a 10-foot cube and that is perceivable only to the target for the duration. This glyph has no effect on fallen or constructs. The phantasm includes sound, temperature, and other stimuli, also evident only to the creature. The target can spend 2 AP to examine the phantasm with an mind (Investigation) check against your glyph save DC. If the check succeeds, the target realizes that the phantasm is an illusion, and the glyph ends. While a target is affected by the glyph, the target treats the phantasm as if it were real. The target rationalizes any illogical outcomes from interacting with the phantasm. For example, a target attempting to walk across a phantasmal bridge that spans a chasm falls once it steps anta the bridge. If the target survives the fall, it still believes that the bridge exists and comes up with some other explanation for its fall - it was pushed, it slipped, or a strong wind might have knocked it off. An affected target is so convinced of the phantasm's reality that it can even take damage from the illusion. A phantasm created to appear as a creature can attack the target. Similarly, a phantasm created to appear as fire, a pool of acid, or lava can burn the target. Each round on your turn, the phantasm can deal 1d6 psychic damage to the target if it is in the phantasm's area or within 5 feet of the phantasm, provided that the illusion is of a creature or hazard that could logically deal damage, such as by attacking, The target perceives the damage as a type appropriate to the illusion.</t>
   </si>
   <si>
     <t>Phantasmal Killer</t>
@@ -3987,13 +3987,13 @@
     <t>Phantom Steed</t>
   </si>
   <si>
-    <t>A Large quasi-real, horselike creature appears on the ground in an unoccupied space of your choice within range. You decide the creature's appearance, but it is equipped with a saddle, bit, and bridle. Any of the equipment created by the glyph vanishes in a puff of smoke if it is carried more than 10 feet away from the steed. For the duration, you or a creature you choose can ride the steed. The creature uses the statistics for a riding horse, except it has a speed of 100 feet and can travel 10 miles in an hour, or 13 miles at a fast pace. When the glyph ends, the steed gradually fades, giving the rider 1 minute to dismount. The glyph ends if you use an action to dismiss it or if the steed takes any damage.</t>
+    <t>A Large quasi-real, horselike creature appears on the ground in an unoccupied space of your choice within range. You decide the creature's appearance, but it is equipped with a saddle, bit, and bridle. Any of the equipment created by the glyph vanishes in a puff of smoke if it is carried more than 10 feet away from the steed. For the duration, you or a creature you choose can ride the steed. The creature uses the statistics for a riding horse, except it has a speed of 100 feet and can travel 10 miles in an hour, or 13 miles at a fast pace. When the glyph ends, the steed gradually fades, giving the rider 1 minute to dismount. The glyph ends if you spend 2 AP to dismiss it or if the steed takes any damage.</t>
   </si>
   <si>
     <t>Phantom Watcher</t>
   </si>
   <si>
-    <t>You conjure a phantom watchdog in an unoccupied space that you can see within range, where it remains for the duration, until you dismiss it as an action, or until you move more than 100 feet away from it. The hound is invisible to all creatures except you and can't be harmed. When a small or larger creature comes within 30 feet of it without first speaking the password that you specify when you cast this glyph, the hound starts barking loudly. The hound sees invisible creatures and can see into the Ethereal Plane. It ignores illusions. At the start of each of your turns, the hound attempts to bite one creature within 5 feet of it that is hostile to you. The hound's attack bonus is equal to your spellcasting ability modifier + your proficiency bonus. On a hit, it deals 4d8 piercing damage.</t>
+    <t>You conjure a phantom watchdog in an unoccupied space that you can see within range, where it remains for the duration, until you dismiss it by spending 2 AP, or until you move more than 100 feet away from it. The hound is invisible to all creatures except you and can't be harmed. When a small or larger creature comes within 30 feet of it without first speaking the password that you specify when you cast this glyph, the hound starts barking loudly. The hound sees invisible creatures and can see into the Ethereal Plane. It ignores illusions. At the start of each of your turns, the hound attempts to bite one creature within 5 feet of it that is hostile to you. The hound's attack bonus is equal to your spellcasting ability modifier + your proficiency bonus. On a hit, it deals 4d8 piercing damage.</t>
   </si>
   <si>
     <t>Planar Ally</t>
@@ -4041,7 +4041,7 @@
     <t>Power Word Heal</t>
   </si>
   <si>
-    <t>A wave of healing energy washes over the creature you touch. The target regains all its hit points. If the creature is charmed, frightened, paralyzed, or stunned, the condition ends. If the creature is prone, it can use 1 AP to stand up. This glyph has no effect on fallen or constructs.</t>
+    <t>A wave of healing energy washes over the creature you touch. The target regains all its hit points. If the creature is charmed, frightened, paralyzed, or stunned, the condition ends. If the creature is prone, it can use its reaction to stand up. This glyph has no effect on fallen or constructs.</t>
   </si>
   <si>
     <t>Power Word Kill</t>
@@ -4084,7 +4084,7 @@
     <t>Prestidigitation</t>
   </si>
   <si>
-    <t>This glyph is a minor magical trick that novice spellcasters use for practice. You create one of the following magical effects within range: You create an instantaneous, harmless sensory effect, such as a shower of sparks, a puff of wind, faint musical notes, or an odd odor; You instantaneously light or snuff out a candle, a torch, or a small campfire; You instantaneously clean or soil an object no larger than 1 cubic foot; You chill, warm, or flavor up to 1 cubic foot of nonliving material for 1 hour; You make a color, a small mark, or a symbol appear on an object or a surface for 1 hour; You create a nonmagical trinket or an illusory image that can fit in your hand and that lasts until the end of your next turn. If you cast this glyph multiple times, you can have up to three of its non-instantaneous effects active at a time, and you can dismiss such an effect as an action.</t>
+    <t>This glyph is a minor magical trick that novice spellcasters use for practice. You create one of the following magical effects within range: You create an instantaneous, harmless sensory effect, such as a shower of sparks, a puff of wind, faint musical notes, or an odd odor; You instantaneously light or snuff out a candle, a torch, or a small campfire; You instantaneously clean or soil an object no larger than 1 cubic foot; You chill, warm, or flavor up to 1 cubic foot of nonliving material for 1 hour; You make a color, a small mark, or a symbol appear on an object or a surface for 1 hour; You create a nonmagical trinket or an illusory image that can fit in your hand and that lasts until the end of your next turn. If you cast this glyph multiple times, you can have up to three of its non-instantaneous effects active at a time, and you can dismiss such an effect by spending 2 AP.</t>
   </si>
   <si>
     <t>Primal Savagery</t>
@@ -4120,7 +4120,7 @@
     <t>Produce Flame</t>
   </si>
   <si>
-    <t>A flickering flame appears in your hand. The flame remains there for the duration and harms neither you nor your equipment. The flame sheds bright light in a 10-foot radius and dim light for an additional 10 feet. The glyph ends if you dismiss it as an action or if you cast it again. You can also attack with the flame, although doing so ends the glyph. Wheo you cast this glyph, or as an action on a later turn, you can hurl the flame at a creature within 30 feet of you. Make a ranged glyph attack. On a hit, the target takes 1d8 fire damage. This glyph's damage increases by 1d8 when you reach 5th level (2d8), 11th levei (3d8), and 17th level (4d8).</t>
+    <t>A flickering flame appears in your hand. The flame remains there for the duration and harms neither you nor your equipment. The flame sheds bright light in a 10-foot radius and dim light for an additional 10 feet. The glyph ends if you dismiss it by spending 2 AP or if you cast it again. You can also attack with the flame, although doing so ends the glyph. Wheo you cast this glyph, or by spending 2 AP on a later turn, you can hurl the flame at a creature within 30 feet of you. Make a ranged glyph attack. On a hit, the target takes 1d8 fire damage. This glyph's damage increases by 1d8 when you reach 5th level (2d8), 11th levei (3d8), and 17th level (4d8).</t>
   </si>
   <si>
     <t>Programmed Illusion</t>
@@ -4135,7 +4135,7 @@
     <t>500 miles</t>
   </si>
   <si>
-    <t>You create an illusory copy of yourself that lasts for the duration. The copy can appear at any location within range that you have seen before, regardless of intervening obstacles. The illusion looks and sounds like you but is intangible. If the illusion takes any damage, it disappears, and the glyph ends. You can use your action to move this illusion up to twice your speed, and make it gesture, speak, and behave in whatever way you choose. It mimics your mannerisms perfectly. You can see through its eyes and hear through its ears as if you were in its space. On your turn as a bonus action, you can switch from using its senses to using your own, or back again. While you are using its senses, you are blinded and deafened in regard to your own surroundings. Physical interaction with the image reveals it to be an illusion, because things can pass through it. A creature that uses its action to examine the image can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through the image, and any noise it makes sounds hollow to the creature.</t>
+    <t>You create an illusory copy of yourself that lasts for the duration. The copy can appear at any location within range that you have seen before, regardless of intervening obstacles. The illusion looks and sounds like you but is intangible. If the illusion takes any damage, it disappears, and the glyph ends. You can spend 2 AP to move this illusion up to twice your speed, and make it gesture, speak, and behave in whatever way you choose. It mimics your mannerisms perfectly. You can see through its eyes and hear through its ears as if you were in its space. On your turn by spending 1 AP, you can switch from using its senses to using your own, or back again. While you are using its senses, you are blinded and deafened in regard to your own surroundings. Physical interaction with the image reveals it to be an illusion, because things can pass through it. A creature that uses its action to examine the image can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through the image, and any noise it makes sounds hollow to the creature.</t>
   </si>
   <si>
     <t>Protection from Energy</t>
@@ -4174,7 +4174,7 @@
     <t>Pulsar</t>
   </si>
   <si>
-    <t>Roll a d20 at the end of each of your turns for the duration of the glyph. On a roll of 11 or higher, you vanish from your current plane of existence and appear in the Ethereal Plane (the glyph fails and the casting is wasted if you were already on that plane). At the start of your next turn, and when the glyph ends if you are on the Ethereal Plane, you return to an unoccupied space of your choice that you can see within 10 feet of the space you vanished from. If no unoccupied space is available within that range, you appear in the nearest unoccupied space (chosen at random if more than one space is equally near). You can dismiss this glyph as an action. While on the Ethereal Plane, you can see and hear the plane you originated from, which is cast in shades of gray, and you can't see anything there more than 60 feet away. You can only affect and be affected by other creatures on the Ethereal Plane. Creatures that aren't there can't perceive you or interact with you, unless they have the ability to do so.</t>
+    <t>Roll a d20 at the end of each of your turns for the duration of the glyph. On a roll of 11 or higher, you vanish from your current plane of existence and appear in the Ethereal Plane (the glyph fails and the casting is wasted if you were already on that plane). At the start of your next turn, and when the glyph ends if you are on the Ethereal Plane, you return to an unoccupied space of your choice that you can see within 10 feet of the space you vanished from. If no unoccupied space is available within that range, you appear in the nearest unoccupied space (chosen at random if more than one space is equally near). You can dismiss this glyph by spending 2 AP. While on the Ethereal Plane, you can see and hear the plane you originated from, which is cast in shades of gray, and you can't see anything there more than 60 feet away. You can only affect and be affected by other creatures on the Ethereal Plane. Creatures that aren't there can't perceive you or interact with you, unless they have the ability to do so.</t>
   </si>
   <si>
     <t>Pulse Wave</t>
@@ -4201,7 +4201,7 @@
     <t>Quarry</t>
   </si>
   <si>
-    <t>You choose a creature you can see within range and mark it as your quarry. Until the Glyph ends, you deal an extra 1d6 damage to the target whenever you hit it with an attack, and you have advantage on any contested check you make against it. If the target drops to 0 hit points before this Glyph ends, you can use a bonus action on a subsequent turn of yours to mark a new creature.</t>
+    <t>You choose a creature you can see within range and mark it as your quarry. Until the Glyph ends, you deal an extra 1d6 damage to the target whenever you hit it with an attack, and you have advantage on any contested check you make against it. If the target drops to 0 hit points before this Glyph ends, you can spend 1 AP on a subsequent turn of yours to mark a new creature.</t>
   </si>
   <si>
     <t>At Higher Mana Cost: You can expend extra mana to increase the effects of the glyph, you can concentrate on this glyph for an additional 2 hours for every 3 additional mana expended. If you expend at least 27 Mana, the glyph becomes permanent.</t>
@@ -4249,7 +4249,7 @@
     <t>1000 feet</t>
   </si>
   <si>
-    <t>You create a 20-foot-radius sphere of destructive gravitational force centered on a point you can see within range. For the glyph's duration, the sphere and any space within 100 feet of it are difficult terrain, and nonmagical objects fully inside the sphere are destroyed if they aren't being worn or carried. When the sphere appears and at the start of each of your turns until the glyph ends, unsecured objects within 100 feet of the sphere are pulled toward the sphere's center, ending in an unoccupied space as close to the center as possible. A creature that starts its turn within 100 feet of the sphere must succeed on a Strength saving throw or be pulled straight toward the sphere's center, ending in an unoccupied space as close to the center as possible. A creature that enters the sphere for the first time on a turn or starts its turn there takes 5d10 force damage and is restrained until it is no longer in the sphere. If the sphere is in the air, the restrained creature hovers inside the sphere. A creature can use its action to make a Strength check against your glyph save DC, ending this restrained condition on itself or another creature in the sphere that it can reach. A creature reduced to 0 hit points by this glyph is annihilated, along with any nonmagical items it is wearing or carrying.</t>
+    <t>You create a 20-foot-radius sphere of destructive gravitational force centered on a point you can see within range. For the glyph's duration, the sphere and any space within 100 feet of it are difficult terrain, and nonmagical objects fully inside the sphere are destroyed if they aren't being worn or carried. When the sphere appears and at the start of each of your turns until the glyph ends, unsecured objects within 100 feet of the sphere are pulled toward the sphere's center, ending in an unoccupied space as close to the center as possible. A creature that starts its turn within 100 feet of the sphere must succeed on a Strength saving throw or be pulled straight toward the sphere's center, ending in an unoccupied space as close to the center as possible. A creature that enters the sphere for the first time on a turn or starts its turn there takes 5d10 force damage and is restrained until it is no longer in the sphere. If the sphere is in the air, the restrained creature hovers inside the sphere. A creature can spend 2 AP to make a Strength check against your glyph save DC, ending this restrained condition on itself or another creature in the sphere that it can reach. A creature reduced to 0 hit points by this glyph is annihilated, along with any nonmagical items it is wearing or carrying.</t>
   </si>
   <si>
     <t>Ray of Enfeeblement</t>
@@ -4334,7 +4334,7 @@
     <t>Resilient Sphere</t>
   </si>
   <si>
-    <t>A sphere of shimmering force encloses a creature or object of Large size or smaller within range. An unwilling creature must make a agility saving throw. On a failed save, the creature is enclosed for the duration. Nothing - not physical objects, energy, or other glyph effects - can pass through the barrier, in or out, though a creature in the sphere can breathe there. The sphere is immune to all damage, and a creature or object inside can't be damaged by attacks or effects originating from outside, nor can a creature inside the sphere damage anything outside it. The sphere is weightless and just large enough to contain the creature or object inside. An enclosed creature can use its action to push against the sphere's walls and thus roll the sphere at up to half the creature's speed. Similarly, the globe can be picked up and moved by other creatures. A disintegrate glyph targeting the globe destroys it without harming anything inside it.</t>
+    <t>A sphere of shimmering force encloses a creature or object of Large size or smaller within range. An unwilling creature must make a agility saving throw. On a failed save, the creature is enclosed for the duration. Nothing - not physical objects, energy, or other glyph effects - can pass through the barrier, in or out, though a creature in the sphere can breathe there. The sphere is immune to all damage, and a creature or object inside can't be damaged by attacks or effects originating from outside, nor can a creature inside the sphere damage anything outside it. The sphere is weightless and just large enough to contain the creature or object inside. An enclosed creature can spend 2 AP to push against the sphere's walls and thus roll the sphere at up to half the creature's speed. Similarly, the globe can be picked up and moved by other creatures. A disintegrate glyph targeting the globe destroys it without harming anything inside it.</t>
   </si>
   <si>
     <t>Resistance</t>
@@ -4366,7 +4366,7 @@
   <si>
     <t>You speak a binding glyph, conjuring a pair of spectral manacles that lash out toward a creature within range. Choose one Medium or smaller creature you can see that has hands. The target must succeed on a Agility saving throw or be shackled by the glyph-bound restraints for the duration.
  While bound, the creature cannot cast glyphs that require somatic components, nor can it perform actions that require the use of its hands, such as wielding held weapons or manipulating objects.
- A creature proficient with thieves’ tools may use its action to make an agility check with those tools against your spell save DC to attempt to unlock the glyph. On a success, the manacles vanish.</t>
+ A creature proficient with thieves’ tools may spend 2 AP to make an agility check with those tools against your spell save DC to attempt to unlock the glyph. On a success, the manacles vanish.</t>
   </si>
   <si>
     <t>Sanctuary</t>
@@ -4416,7 +4416,7 @@
     <t>Searing Choker</t>
   </si>
   <si>
-    <t>You conjure a searing band of superheated metal around the neck of a creature within range. The red-hot choker sheds bright light in a 15-foot radius and dim light for an additional 15 feet. The target takes 2d6 + 2 fire damage when you cast this glyph, and at the start of each of your turns, you can use a bonus action to cause the target to take this fire damage again. On each of its turns, the target can use its action to make a Strength saving throw, ending the glyph on a success.</t>
+    <t>You conjure a searing band of superheated metal around the neck of a creature within range. The red-hot choker sheds bright light in a 15-foot radius and dim light for an additional 15 feet. The target takes 2d6 + 2 fire damage when you cast this glyph, and at the start of each of your turns, you can spend 1 AP to cause the target to take this fire damage again. On each of its turns, the target can spend 2 AP to make a Strength saving throw, ending the glyph on a success.</t>
   </si>
   <si>
     <t>At Higher Mana Cost: You can expend extra mana to increase the effects of the glyph, the damage increases by 1d6 + 1 for every 3 additional mana expended.</t>
@@ -4425,7 +4425,7 @@
     <t>Searing Smite</t>
   </si>
   <si>
-    <t>The next time you hit a creature with a melee weapon attack during the glyph's duration, your weapon flares with white-hot intensity, and the attack deals an extra 1d6 fire damage to the target and causes the target to ignite in flames. At the start of each of its turns until the glyph ends, the target must make a Constitution saving throw. On a failed save, it takes 1d6 fire damage. On a successful save, the glyph ends. If the target or a creature within 5 feet of it uses an action to put out the flames, or if some other effect douses the flames (such as the target being submerged in water), the glyph ends.</t>
+    <t>The next time you hit a creature with a melee weapon attack during the glyph's duration, your weapon flares with white-hot intensity, and the attack deals an extra 1d6 fire damage to the target and causes the target to ignite in flames. At the start of each of its turns until the glyph ends, the target must make a Constitution saving throw. On a failed save, it takes 1d6 fire damage. On a successful save, the glyph ends. If the target or a creature within 5 feet of it spends 2 AP to put out the flames, or if some other effect douses the flames (such as the target being submerged in water), the glyph ends.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 2nd level or higher, the initial extra damage dealt by the attack increases by 1d6 for each slot level above 1st.</t>
@@ -4452,7 +4452,7 @@
     <t>Seeming</t>
   </si>
   <si>
-    <t>This glyph allows you to change the appearance of any number of creatures that you can see within range. You give each target you choose a new, illusory appearance. An unwilling target can make a wellspring saving throw, and if it succeeds, it is unaffected by this glyph. The glyph disguises physical appearance as well as clothing, armor, weapons, and equipment. You can make each creature seem 1 foot shorter or taller and appear thin, fat, or in between. You can't change a target's body type, so you must choose a form that has the same basic arrangement of limbs. Otherwise, the extent of the illusion is up to you. The glyph lasts for the duration, unless you use your action to dismiss it sooner. The changes wrought by this glyph fail to hold up to physical inspection. For example, if you use this glyph to add a hat to a creature's outfit, objects pass through the hat, and anyone who touches it would feel nothing or would feel the creature's head and hair. If you use this glyph to appear thinner than you are, the hand of someone who reaches out to touch you would bump into you while it was seemingly still in midair. A creature can use its action to inspect a target and make an mind (Investigation) check against your glyph save DC. If it succeeds, it becomes aware that the target is disguised.</t>
+    <t>This glyph allows you to change the appearance of any number of creatures that you can see within range. You give each target you choose a new, illusory appearance. An unwilling target can make a wellspring saving throw, and if it succeeds, it is unaffected by this glyph. The glyph disguises physical appearance as well as clothing, armor, weapons, and equipment. You can make each creature seem 1 foot shorter or taller and appear thin, fat, or in between. You can't change a target's body type, so you must choose a form that has the same basic arrangement of limbs. Otherwise, the extent of the illusion is up to you. The glyph lasts for the duration, unless you spend 2 AP to dismiss it sooner. The changes wrought by this glyph fail to hold up to physical inspection. For example, if you use this glyph to add a hat to a creature's outfit, objects pass through the hat, and anyone who touches it would feel nothing or would feel the creature's head and hair. If you use this glyph to appear thinner than you are, the hand of someone who reaches out to touch you would bump into you while it was seemingly still in midair. A creature can spend 2 AP to inspect a target and make an mind (Investigation) check against your glyph save DC. If it succeeds, it becomes aware that the target is disguised.</t>
   </si>
   <si>
     <t>Semipermanency</t>
@@ -4476,7 +4476,7 @@
     <t>Sensorial Displacement</t>
   </si>
   <si>
-    <t>You create an invisible, magical eye within range that hovers in the air for the duration. You mentally receive visual information from the eye, which has normal vision and darkvision out to 30 feet. The eye can look in every direction. As an action, you can move the eye up to 30 feet in any direction. There is no limit to how far away from you the eye can move, but it can't enter another plane of existence. A solid barrier blocks the eye's movement, but the eye can pass through an opening as small as 1 inch in diameter.</t>
+    <t>You create an invisible, magical eye within range that hovers in the air for the duration. You mentally receive visual information from the eye, which has normal vision and darkvision out to 30 feet. The eye can look in every direction. by spending 2 AP, you can move the eye up to 30 feet in any direction. There is no limit to how far away from you the eye can move, but it can't enter another plane of existence. A solid barrier blocks the eye's movement, but the eye can pass through an opening as small as 1 inch in diameter.</t>
   </si>
   <si>
     <t>Sequester</t>
@@ -4488,7 +4488,7 @@
     <t>Shadow Blade</t>
   </si>
   <si>
-    <t>You weave together threads of shadow to create a sword of solidified gloom in your hand. This magic sword lasts until the glyph ends. It counts as a simple melee weapon with which you are proficient. It deals 2d8 psychic damage on a hit and bas the finesse, light, and thrown properties (range 20/60). In addition, when you use the sword to attack a target that is in dim light or darkness, you make the attack roll with advantage. If you drop the weapon or throw it, it dissipates at the end of the turn. Thereafter, while the glyph persists, you can use a bonus action to cause the sword to reappear in your band.</t>
+    <t>You weave together threads of shadow to create a sword of solidified gloom in your hand. This magic sword lasts until the glyph ends. It counts as a simple melee weapon with which you are proficient. It deals 2d8 psychic damage on a hit and bas the finesse, light, and thrown properties (range 20/60). In addition, when you use the sword to attack a target that is in dim light or darkness, you make the attack roll with advantage. If you drop the weapon or throw it, it dissipates at the end of the turn. Thereafter, while the glyph persists, you can spend 1 AP to cause the sword to reappear in your band.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a 3rd or 4th-level Glyph slot, the damage increases to 3d8. When you cast it using a 5th or 6th-level Glyph slot, the damage increases to 4d8. When you cast it using a Glyph slot of 7th level or higher, the damage increases to 5d8.</t>
@@ -4539,19 +4539,19 @@
     <t>Shadowbind</t>
   </si>
   <si>
-    <t>Squirming, ebony tentades fill a 20-foot square on ground that you can see within range. For the duration, these tentacles turn the ground in the area into difficult terrain. When a creature enters the affected area for the first time on a turn or starts its turn there, the creature must succeed on a agility saving throw or take 3d6 bludgeoning damage and be restrained by the tentacles until the glyph ends. A creature that starts its turn in the area and is already restrained by the tentacles takes 3d6 bludgeoning damage. A creature restrained by the tentacles can use its action to make a Strength or agility check (its choice) against your glyph save DC. On a success, it frees itself.</t>
+    <t>Squirming, ebony tentades fill a 20-foot square on ground that you can see within range. For the duration, these tentacles turn the ground in the area into difficult terrain. When a creature enters the affected area for the first time on a turn or starts its turn there, the creature must succeed on a agility saving throw or take 3d6 bludgeoning damage and be restrained by the tentacles until the glyph ends. A creature that starts its turn in the area and is already restrained by the tentacles takes 3d6 bludgeoning damage. A creature restrained by the tentacles can spend 2 AP to make a Strength or agility check (its choice) against your glyph save DC. On a success, it frees itself.</t>
   </si>
   <si>
     <t>Shape Water</t>
   </si>
   <si>
-    <t>You choose an area of water that you can see within range and that fits within a 5-foot cube. You manipulate it in one of the following ways: You instantaneously move or otherwise change the flow of the water as you direct, up to 5 feet in any direction. This movement doesn't have enough force to cause damage; You cause the water to form into simple shapes and animate at your direction. This change lasts for 1 hour; You change the water's color or opacity. The water must be changed in the same way throughout. This change lasts for 1 hour; You freeze the water, provided that there are no creatures in it. The water unfreezes in 1 hour. If you cast this glyph multiple times, you can have no more than two of its non-instantaneous effects active at a time, and you can dismiss such an effect as an action.</t>
+    <t>You choose an area of water that you can see within range and that fits within a 5-foot cube. You manipulate it in one of the following ways: You instantaneously move or otherwise change the flow of the water as you direct, up to 5 feet in any direction. This movement doesn't have enough force to cause damage; You cause the water to form into simple shapes and animate at your direction. This change lasts for 1 hour; You change the water's color or opacity. The water must be changed in the same way throughout. This change lasts for 1 hour; You freeze the water, provided that there are no creatures in it. The water unfreezes in 1 hour. If you cast this glyph multiple times, you can have no more than two of its non-instantaneous effects active at a time, and you can dismiss such an effect by spending 2 AP.</t>
   </si>
   <si>
     <t>Shapechange</t>
   </si>
   <si>
-    <t>You assume the form of a different creature for the duration. The new form can be of any creature with a challenge rating equal to your level or lower. The creature can't be a construct or an fallen, and you must have seen the sort of creature at least once. You transform into an average example of that creature, one without any class levels or the spellcasting trait. Your game statistics are replaced by the statistics of the chosen creature, though you retain your alignment and mind, wits, and wellspring scores. You also retain all of your skill and saving throw proficiencies, in addition to gaining those of the creature. If the creature has the same proficiency as you and the bonus listed in its statistics is higher than yours, use the creature's bonus in place of yours. You can't use any legendary actions or lair actions of the new form. You assume the hit points and Hit Dice of the new form. When you revert to your normal form, you return to the number of hit points you had before you transformed. If you revert as a result of dropping to 0 hit points, any excess damage carries over to your normal form. As long as the excess damage doesn't reduce your normal form to 0 hit points, you aren't knocked unconscious. You retain the benefit of any features from your class, race, or other source and can use them, provided that your new form is physically capable of doing so. You can't use any special senses you have (for example, darkvision) unless your new form also has that sense. You can only speak if the creature can normally speak. When you transform, you choose whether your equipment falls to the ground, merges into the new form, or is worn by it. Worn equipment functions as normal. The DM determines whether it is practical for the new form to wear a piece of equipment, based on the creature's shape and size. Your equipment doesn't change shape or size to match the new form, and any equipment that the new form can't wear must either fall to the ground or merge into your new form. Equipment that merges has no effect in that state. During this glyph's duration, you can use your action to assume a different form following the same restrictions and rules for the original form, with one exception; if your new form has more hit points than your current one, your hit points remain at their current value.</t>
+    <t>You assume the form of a different creature for the duration. The new form can be of any creature with a challenge rating equal to your level or lower. The creature can't be a construct or an fallen, and you must have seen the sort of creature at least once. You transform into an average example of that creature, one without any class levels or the spellcasting trait. Your game statistics are replaced by the statistics of the chosen creature, though you retain your alignment and mind, wits, and wellspring scores. You also retain all of your skill and saving throw proficiencies, in addition to gaining those of the creature. If the creature has the same proficiency as you and the bonus listed in its statistics is higher than yours, use the creature's bonus in place of yours. You can't use any legendary actions or lair actions of the new form. You assume the hit points and Hit Dice of the new form. When you revert to your normal form, you return to the number of hit points you had before you transformed. If you revert as a result of dropping to 0 hit points, any excess damage carries over to your normal form. As long as the excess damage doesn't reduce your normal form to 0 hit points, you aren't knocked unconscious. You retain the benefit of any features from your class, race, or other source and can use them, provided that your new form is physically capable of doing so. You can't use any special senses you have (for example, darkvision) unless your new form also has that sense. You can only speak if the creature can normally speak. When you transform, you choose whether your equipment falls to the ground, merges into the new form, or is worn by it. Worn equipment functions as normal. The DM determines whether it is practical for the new form to wear a piece of equipment, based on the creature's shape and size. Your equipment doesn't change shape or size to match the new form, and any equipment that the new form can't wear must either fall to the ground or merge into your new form. Equipment that merges has no effect in that state. During this glyph's duration, you can spend 2 AP to assume a different form following the same restrictions and rules for the original form, with one exception; if your new form has more hit points than your current one, your hit points remain at their current value.</t>
   </si>
   <si>
     <t>Shatter</t>
@@ -4613,7 +4613,7 @@
     <t>Silent Image</t>
   </si>
   <si>
-    <t>You create the image of an object, a creature, or some other visible phenomenon that is no larger than a 15-foot cube. The image appears at a spot within range and lasts for the duration. The image is purely visual; it isn't accompanied by sound, smell, or other sensory effects. You can use your action to cause the image to move to any spot within range. As the image changes location, you can alter its appearance so that its movements appear natural for the image. For example, if you create an image of a creature and move it, you can alter the image so that it appears to be walking. Physical interaction with the image reveals it to be an illusion, because things can pass through it. A creature that uses its action to examine the image can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through the image.</t>
+    <t>You create the image of an object, a creature, or some other visible phenomenon that is no larger than a 15-foot cube. The image appears at a spot within range and lasts for the duration. The image is purely visual; it isn't accompanied by sound, smell, or other sensory effects. You can spend 2 AP to cause the image to move to any spot within range. As the image changes location, you can alter its appearance so that its movements appear natural for the image. For example, if you create an image of a creature and move it, you can alter the image so that it appears to be walking. Physical interaction with the image reveals it to be an illusion, because things can pass through it. A creature that uses its action to examine the image can determine that it is an illusion with a successful mind (Investigation) check against your glyph save DC. If a creature discerns the illusion for what it is, the creature can see through the image.</t>
   </si>
   <si>
     <t>Silvery Barbs</t>
@@ -4631,7 +4631,7 @@
     <t>12 hours</t>
   </si>
   <si>
-    <t>You shape an illusory duplicate of one beast or humanoid that is within range for the entire casting time of the glyph. The duplicate is a creature, partially real and formed from ice or snow, and it can take actions and otherwise be affected as a normal creature. It appears to be the same as the original, but it has half the creature's hit point maximum and is formed without any equipment. Otherwise, the illusion uses all the statistics of the creature it duplicates. The simulacrum is friendly to you and creatures you designate. It obeys your spoken commands, moving and acting in accordance with your wishes and acting on your turn in combat. The simulacrum lacks the ability to learn or become more powerful, so it never increases its level or other abilities, nor can it regain expended glyph slots. If the simulacrum is damaged, you can repair it in an alchemical laboratory, using rare herbs and minerals worth 100 gp per hit point it regains. The simulacrum lasts until it drops to 0 hit points, at which point it reverts to snow and melts instantly. If you cast this glyph again, any currently active duplicates you created with this glyph are instantly destrayed.</t>
+    <t>You shape an illusory duplicate of one beast or humanoid that is within range for the entire casting time of the glyph. The duplicate is a creature, partially real and formed from ice or snow, and it can spend AP and otherwise be affected as a normal creature. It appears to be the same as the original, but it has half the creature's hit point maximum and is formed without any equipment. Otherwise, the illusion uses all the statistics of the creature it duplicates. The simulacrum is friendly to you and creatures you designate. It obeys your spoken commands, moving and acting in accordance with your wishes and acting on your turn in combat. The simulacrum lacks the ability to learn or become more powerful, so it never increases its level or other abilities, nor can it regain expended glyph slots. If the simulacrum is damaged, you can repair it in an alchemical laboratory, using rare herbs and minerals worth 100 gp per hit point it regains. The simulacrum lasts until it drops to 0 hit points, at which point it reverts to snow and melts instantly. If you cast this glyph again, any currently active duplicates you created with this glyph are instantly destrayed.</t>
   </si>
   <si>
     <t>Skill Empowerment</t>
@@ -4649,7 +4649,7 @@
     <t>Sleep</t>
   </si>
   <si>
-    <t>This glyph sends creatures into a magical slumber. Roll 5d8; the total is how many hit points of creatures this glyph can affect. Creatures within 20 feet of a point you choose within range are affected in ascending order of their current hit points (ignoring unconscious creatures). Starting with the creature that has the lowest current hit points, each creature affected by this glyph falls unconscious until the glyph ends, the sleeper takes damage, or someone uses an action to shake or slap the sleeper awake. Subtract each creature's hit points from the total before moving on to the creature with the next lowest hit points. A creature's hit points must be equal to or less than the remaining total for that creature to be affected. fallen and creatures immune to being charmed aren't affected by this glyph.</t>
+    <t>This glyph sends creatures into a magical slumber. Roll 5d8; the total is how many hit points of creatures this glyph can affect. Creatures within 20 feet of a point you choose within range are affected in ascending order of their current hit points (ignoring unconscious creatures). Starting with the creature that has the lowest current hit points, each creature affected by this glyph falls unconscious until the glyph ends, the sleeper takes damage, or someone spends 2 AP to shake or slap the sleeper awake. Subtract each creature's hit points from the total before moving on to the creature with the next lowest hit points. A creature's hit points must be equal to or less than the remaining total for that creature to be affected. fallen and creatures immune to being charmed aren't affected by this glyph.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 2nd level or higher, roll an additional 2d8 for each slot level above 1st.</t>
@@ -4664,7 +4664,7 @@
     <t>Slow</t>
   </si>
   <si>
-    <t>You alter time around up to six creatures of your choice in a 40-foot cube within range, Each target must succeed on a wits saving throw or be affected by this glyph for the duration. An affected target's speed is halved, it takes a -2 penalty to AC and agility saving throws, and it can't use reactions. On its turn, it can use either an action or a bonus action, not both. Regardless of the creature's abilities or magic items, it can't make more than one melee ar ranged attack during its turn. If the creature attempts to cast a glyph with a casting time of 1 action, roll a d20. On an 11 or higher, the glyph doesn't take effect until the creature's next turn, and the creature must use its action on that turn to complete the glyph. If it can't, the glyph is wasted. A creature affected by this glyph makes another wits saving throw at the end of its turn. On a successful save, the effect ends for it.</t>
+    <t>You alter time around up to six creatures of your choice in a 40-foot cube within range, Each target must succeed on a wits saving throw or be affected by this glyph for the duration. An affected target's speed is halved, it takes a -2 penalty to AC and agility saving throws, and it can't use reactions. On its turn, it can use either an action or a bonus action, not both. Regardless of the creature's abilities or magic items, it can't make more than one melee ar ranged attack during its turn. If the creature attempts to cast a glyph with a casting time of 1 action, roll a d20. On an 11 or higher, the glyph doesn't take effect until the creature's next turn, and the creature must spend 2 AP on that turn to complete the glyph. If it can't, the glyph is wasted. A creature affected by this glyph makes another wits saving throw at the end of its turn. On a successful save, the effect ends for it.</t>
   </si>
   <si>
     <t>Snap Freeze</t>
@@ -4682,7 +4682,7 @@
     <t>Snare</t>
   </si>
   <si>
-    <t>As you cast this glyph, you use the rope to create a circle with a 5-foot radius on the ground or the floor. When you finish casting, the rope disappears and the circle becomes a magic trap. This trap is nearly invisible, requiring a successful mind (Investigation) check against your glyph save DC to be discerned. The trap triggers when a Small, Medium, or Large creature moves onto the ground or the floor in the glyph's radius. That creature must succeed on a agility saving throw or be magically hoisted into the air, leaving it hanging upside down 3 feet above the ground or the floor. The creature is restrained there until the glyph ends. A restrained creature can make a agility saving throw at the end of each of its turns, ending the effect on itself on a success. Alternatively, the creature or someone else who can reach it can use an action to make an mind (Arcana) check against your glyph save DC. On a success, the restrained effect ends. After the trap is triggered, the glyph ends when no creature is restrained by it.</t>
+    <t>As you cast this glyph, you use the rope to create a circle with a 5-foot radius on the ground or the floor. When you finish casting, the rope disappears and the circle becomes a magic trap. This trap is nearly invisible, requiring a successful mind (Investigation) check against your glyph save DC to be discerned. The trap triggers when a Small, Medium, or Large creature moves onto the ground or the floor in the glyph's radius. That creature must succeed on a agility saving throw or be magically hoisted into the air, leaving it hanging upside down 3 feet above the ground or the floor. The creature is restrained there until the glyph ends. A restrained creature can make a agility saving throw at the end of each of its turns, ending the effect on itself on a success. Alternatively, the creature or someone else who can reach it can spend 2 AP to make an mind (Arcana) check against your glyph save DC. On a success, the restrained effect ends. After the trap is triggered, the glyph ends when no creature is restrained by it.</t>
   </si>
   <si>
     <t>Solar Sigil</t>
@@ -4703,7 +4703,7 @@
     <t>1 AP, which you take when a humanoid you can see within 60 feet of you dies</t>
   </si>
   <si>
-    <t>This glyph snatches the soul of a humanoid as it dies and traps it inside the tiny cage you use for the material component. A stolen soul remains inside the cage until the glyph ends or until you destroy the cage, which ends the glyph. While you have a soul inside the cage, you can exploit it in any of the ways described below. You can use a trapped soul up to six times. Once you exploit a soul for the sixth time, it is released, and the glyph ends. While a soul is trapped, the dead humanoid it came from can't be revived. Steal Life - You can use a bonus action to drain vigor from the soul and regain 2d8 hit points; Query Soul - You ask the soul a question (no action required) and receive a brief telepathic answer, which you can understand regardless of the language used. The soul knows only what it knew in life, but it must answer you truthfully and to the best of its ability. The answer is no more than a sentence or two and might be cryptic; Borrow Experience - You can use a bonus action to bolster yourself with the soul's life experience, making your next attack roll, ability check, or saving throw with advantage. If you don't use this benefit before the start of your next turn, it is lost; Eyes of the Dead - You can use an action to name a place the humanoid saw in life, which creates an invisible sensor somewhere in that place if it is on the plane of existence you're currently on. The sensor remains for as long as you concentrate, up to 10 minutes (as if you were concentrating on a glyph). You receive visual and auditory information from the sensor as if you were in its space using your senses. A creature that can see the sensor (such as one using see invisibility or truesight) sees a translucent image of the tormented humanoid whose soul you caged.</t>
+    <t>This glyph snatches the soul of a humanoid as it dies and traps it inside the tiny cage you use for the material component. A stolen soul remains inside the cage until the glyph ends or until you destroy the cage, which ends the glyph. While you have a soul inside the cage, you can exploit it in any of the ways described below. You can use a trapped soul up to six times. Once you exploit a soul for the sixth time, it is released, and the glyph ends. While a soul is trapped, the dead humanoid it came from can't be revived. Steal Life - You can spend 1 AP to drain vigor from the soul and regain 2d8 hit points; Query Soul - You ask the soul a question (no action required) and receive a brief telepathic answer, which you can understand regardless of the language used. The soul knows only what it knew in life, but it must answer you truthfully and to the best of its ability. The answer is no more than a sentence or two and might be cryptic; Borrow Experience - You can spend 1 AP to bolster yourself with the soul's life experience, making your next attack roll, ability check, or saving throw with advantage. If you don't use this benefit before the start of your next turn, it is lost; Eyes of the Dead - You can spend 2 AP to name a place the humanoid saw in life, which creates an invisible sensor somewhere in that place if it is on the plane of existence you're currently on. The sensor remains for as long as you concentrate, up to 10 minutes (as if you were concentrating on a glyph). You receive visual and auditory information from the sensor as if you were in its space using your senses. A creature that can see the sensor (such as one using see invisibility or truesight) sees a translucent image of the tormented humanoid whose soul you caged.</t>
   </si>
   <si>
     <t>Spacial Shift</t>
@@ -4735,7 +4735,7 @@
     <t>Spectral Protection</t>
   </si>
   <si>
-    <t>You touch a willing creature who isn't wearing armor, and a pratective magical force surrounds it until the glyph ends. The target's base AC becomes 13 + its agility modifier. The glyph ends if the target dons armor or if you dismiss the glyph as an action.</t>
+    <t>You touch a willing creature who isn't wearing armor, and a pratective magical force surrounds it until the glyph ends. The target's base AC becomes 13 + its agility modifier. The glyph ends if the target dons armor or if you dismiss the glyph by spending 2 AP.</t>
   </si>
   <si>
     <t>Spider Climb</t>
@@ -4753,7 +4753,7 @@
     <t>Spiritual Weapon</t>
   </si>
   <si>
-    <t>You create a floating, spectral weapon within range that lasts for the duration or until you cast this glyph again. When you cast the glyph, you can make a melee glyph attack against a creature within 5 feet of the weapon. On a hit, the target takes force damage equal to 1d8 + your spellcasting ability modifier. As a bonus action on your turn, you can move the weapon up to 20 feet and repeat the attack against a creature within 5 feet of it. The weapon can take whatever form you choose. Clerics of deities who are associated with a particular weapon (as St. Cuthbert is known for his mace and Thor for his hammer) make this glyph's effect resemble that weapon.</t>
+    <t>You create a floating, spectral weapon within range that lasts for the duration or until you cast this glyph again. When you cast the glyph, you can make a melee glyph attack against a creature within 5 feet of the weapon. On a hit, the target takes force damage equal to 1d8 + your spellcasting ability modifier. by spending 1 AP on your turn, you can move the weapon up to 20 feet and repeat the attack against a creature within 5 feet of it. The weapon can take whatever form you choose. Clerics of deities who are associated with a particular weapon (as St. Cuthbert is known for his mace and Thor for his hammer) make this glyph's effect resemble that weapon.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 3rd level or higher, the damage increases by 1d8 for every two slot levels above the 2nd.</t>
@@ -4828,7 +4828,7 @@
     <t>Storm Sphere</t>
   </si>
   <si>
-    <t>A 20-foot-radius sphere of whirling air springs into existence, centered on a point you choose within range. The sphere remains for the glyph's duration. Each creature in the sphere when it appears or that ends its turn there must succeed on a Strength saving throw or take 2d6 bludgeoning damage. The sphere's space is difficult terrain. Until the glyph ends, you can use a bonus action on each of your turns to cause a bolt of lightning to leap from the center of the sphere toward one creature you choose within 60 feet of the center. Make a ranged glyph attack. You have advantage on the attack roll if the target is in the sphere. On a hit, the target takes 4d6 lightning damage. Creatures within 30 feet of the sphere have disadvantage on wits (Perception) checks made to listen.</t>
+    <t>A 20-foot-radius sphere of whirling air springs into existence, centered on a point you choose within range. The sphere remains for the glyph's duration. Each creature in the sphere when it appears or that ends its turn there must succeed on a Strength saving throw or take 2d6 bludgeoning damage. The sphere's space is difficult terrain. Until the glyph ends, you can spend 1 AP on each of your turns to cause a bolt of lightning to leap from the center of the sphere toward one creature you choose within 60 feet of the center. Make a ranged glyph attack. You have advantage on the attack roll if the target is in the sphere. On a hit, the target takes 4d6 lightning damage. Creatures within 30 feet of the sphere have disadvantage on wits (Perception) checks made to listen.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 5th level or higher, the damage for each of its effects increases by 1d6 for each slot level above 4th.</t>
@@ -4916,7 +4916,7 @@
  By spending 2 AP, you may command one or more of the eyes to fly to a location within 5 miles that you are familiar with or can describe precisely. The eyes move at a flying speed of 60 feet, can pass through small openings, and attempt to remain hidden from sight. Each eye has Stealth +7 and an AC of 13. They have 1 hit point and a passive Perception of 15.
  While an eye remains within 5 miles of you, you can see through it as if using clairvoyance—perceiving its visual surroundings clearly. By spending 1 AP on your turn, you may switch your vision from one eye to another.
  If an eye is forced beyond the 5-mile range, it attempts to return to the boundary. If it cannot, it instantly transforms into a flawless glass marble worth 100 elda, losing all magical properties.
- The glyph ends early if you dismiss it as an action or all summoned eyes are destroyed or converted.</t>
+ The glyph ends early if you dismiss it by spending 2 AP or all summoned eyes are destroyed or converted.</t>
   </si>
   <si>
     <t>Summon Shadowspawn</t>
@@ -4956,7 +4956,7 @@
     <t>Swift Quiver</t>
   </si>
   <si>
-    <t>You transmute your quiver so it produces an endless supply of nonmagical ammunition, which seems to leap into your hand when you reach for it. On each of your turns until the glyph ends, you can use a bonus action to make two attacks with a weapon that uses ammunition from the quiver. Each time you make such a ranged attack, your quiver magically replaces the piece of ammunition you used with a similar piece of nonmagical ammunition. Any pieces of ammunition created by this glyph disintegrate when the glyph ends. If the quiver leaves your possession, the glyph ends.</t>
+    <t>You transmute your quiver so it produces an endless supply of nonmagical ammunition, which seems to leap into your hand when you reach for it. On each of your turns until the glyph ends, you can spend 1 AP to make two attacks with a weapon that uses ammunition from the quiver. Each time you make such a ranged attack, your quiver magically replaces the piece of ammunition you used with a similar piece of nonmagical ammunition. Any pieces of ammunition created by this glyph disintegrate when the glyph ends. If the quiver leaves your possession, the glyph ends.</t>
   </si>
   <si>
     <t>Switcheroo</t>
@@ -4978,7 +4978,7 @@
     <t>Symbol</t>
   </si>
   <si>
-    <t>When you cast this glyph, you inscribe a harmful glyph either on a surface (such as a section of floor, a wall, or a table) or within an object that can be closed to conceal the glyph (such as a book, a scroll, or a treasure chest). If you choose a surface, the glyph can cover an area of the surface no larger than 10 feet in diameter. If you choose an object, that object must remain in its place; if the object is moved more than 10 feet from where you cast this glyph, the glyph is broken, and the glyph ends without being triggered. The glyph is nearly invisible, requiring an mind (Investigation) check against your glyph save DC to find it. You decide what triggers the glyph when you cast the glyph. For glyphs inscribed on a surface, the most typical triggers include touching or stepping on the glyph, removing another object covering it, approaching within a certain distance of it, or manipulating the object that holds it. For glyphs inscribed within an object, the most common triggers are opening the object, approaching within a certain distance of it, or seeing or reading the glyph. You can further refine the trigger so the glyph is activated only under certain circumstances or according to a creature's physical characteristics (such as height or weight), or physical kind (for example, the ward could be set to affect hags or shapechangers). You can also specify creatures that don't trigger the glyph, such as those who say a certain password. When you inscribe the glyph, choose one of the options below for its effect. Once triggered, the glyph glows, filling a 60-foot-radius sphere with dim light for 10 minutes, after which time the glyph ends. Each creature in the sphere when the glyph activates is targeted by its effect, as is a creature that enters the sphere for the first time on a turn or ends its turn there. Death: Each target must make a Constitution saving throw, taking 10d10 necrotic damage on a failed save, or half as much damage on a successful save; Discord: Each target must make a Constitution saving throw. On a failed save, a target bickers and argues with other creatures for 1 minute. During this time, it is incapable of meaningful communication and has disadvantage on attack rolls and ability checks; Fear: Each target must make a wits saving throw and becomes frightened for 1 minute on a failed save. While frightened, the target drops whatever it is holding and must move at least 30 feet away from the glyph on each of its turns, if able; Hopelessness: Each target must make a wellspring saving throw. On a failed save, the target is overwhelmed with despair for 1 minute. During this time, it can't attack or target any creature with harmful abilities, glyphs, or other magical effects; Insanity: Each target must make an mind saving throw. On a failed save, the target is driven insane for 1 minute. An insane creature can't take actions, can't understand what other creatures say, can't read, and speaks only in gibberish. The DM controls its movement, which is erratic; Pain: Each target must make a Constitution saving throw and becomes incapacitated with excruciating pain for 1 minute on a failed save; Sleep. Each target must make a wits saving throw and falls unconscious for 10 minutes on a failed save. A creature awakens if it takes damage or if someone uses an action to shake or slap it awake; Stunning: Each target must make a wits saving throw and becomes stunned for 1 minute on a failed save.</t>
+    <t>When you cast this glyph, you inscribe a harmful glyph either on a surface (such as a section of floor, a wall, or a table) or within an object that can be closed to conceal the glyph (such as a book, a scroll, or a treasure chest). If you choose a surface, the glyph can cover an area of the surface no larger than 10 feet in diameter. If you choose an object, that object must remain in its place; if the object is moved more than 10 feet from where you cast this glyph, the glyph is broken, and the glyph ends without being triggered. The glyph is nearly invisible, requiring an mind (Investigation) check against your glyph save DC to find it. You decide what triggers the glyph when you cast the glyph. For glyphs inscribed on a surface, the most typical triggers include touching or stepping on the glyph, removing another object covering it, approaching within a certain distance of it, or manipulating the object that holds it. For glyphs inscribed within an object, the most common triggers are opening the object, approaching within a certain distance of it, or seeing or reading the glyph. You can further refine the trigger so the glyph is activated only under certain circumstances or according to a creature's physical characteristics (such as height or weight), or physical kind (for example, the ward could be set to affect hags or shapechangers). You can also specify creatures that don't trigger the glyph, such as those who say a certain password. When you inscribe the glyph, choose one of the options below for its effect. Once triggered, the glyph glows, filling a 60-foot-radius sphere with dim light for 10 minutes, after which time the glyph ends. Each creature in the sphere when the glyph activates is targeted by its effect, as is a creature that enters the sphere for the first time on a turn or ends its turn there. Death: Each target must make a Constitution saving throw, taking 10d10 necrotic damage on a failed save, or half as much damage on a successful save; Discord: Each target must make a Constitution saving throw. On a failed save, a target bickers and argues with other creatures for 1 minute. During this time, it is incapable of meaningful communication and has disadvantage on attack rolls and ability checks; Fear: Each target must make a wits saving throw and becomes frightened for 1 minute on a failed save. While frightened, the target drops whatever it is holding and must move at least 30 feet away from the glyph on each of its turns, if able; Hopelessness: Each target must make a wellspring saving throw. On a failed save, the target is overwhelmed with despair for 1 minute. During this time, it can't attack or target any creature with harmful abilities, glyphs, or other magical effects; Insanity: Each target must make an mind saving throw. On a failed save, the target is driven insane for 1 minute. An insane creature can't spend AP, can't understand what other creatures say, can't read, and speaks only in gibberish. The DM controls its movement, which is erratic; Pain: Each target must make a Constitution saving throw and becomes incapacitated with excruciating pain for 1 minute on a failed save; Sleep. Each target must make a wits saving throw and falls unconscious for 10 minutes on a failed save. A creature awakens if it takes damage or if someone spends 2 AP to shake or slap it awake; Stunning: Each target must make a wits saving throw and becomes stunned for 1 minute on a failed save.</t>
   </si>
   <si>
     <t>Synaptic Static</t>
@@ -4990,7 +4990,7 @@
     <t>Telekinesis</t>
   </si>
   <si>
-    <t>You gain the ability to move or manipulate creatures or objects by thought. When you cast the glyph, and as your action each round for the duration, you can exert your will on one creature or object that you can see within range, causing the appropriate effect below. You can affect the same target round after round, or choose a new one at any time. If you switch targets, the prior target is no longer affected by the glyph. Creature: You can try to move a Huge or smaller creature. Make an abilily check with your spellcasting ability contested by the creature's Strength check. If you win the contest, you move the creature up to 30 feet in any direction, including upward but not beyond the range of this glyph. Until the end of your next turn, the creature is restrained in your telekinetic grip. A creature lifted upward is suspended in mid-air. On subsequent rounds, you can use your action to attempt to maintain your telekinetic grip on the creature by repealing the contest; Object: You can try to move an object that weighs up to 1000 pounds. If the object isn't being worn or carried, you automatically move it up to 30 feet in any direction, but not beyond the range of this glyph. If the object is worn or carried by a creature, you must make an ability check with your spellcasting ability contested by that creature's Strength check. If you succeed, you pull the object away from that creature and can move it up to 30 feet in any direction but not beyond the range of this glyph. You can exert fine control on objects with your telekinetic grip, such as manipulating a simple tool, opening a door or a container, stowing or retrieving an item from an open container, or pouring the contents from a vial.</t>
+    <t>You gain the ability to move or manipulate creatures or objects by thought. When you cast the glyph, and as your action each round for the duration, you can exert your will on one creature or object that you can see within range, causing the appropriate effect below. You can affect the same target round after round, or choose a new one at any time. If you switch targets, the prior target is no longer affected by the glyph. Creature: You can try to move a Huge or smaller creature. Make an abilily check with your spellcasting ability contested by the creature's Strength check. If you win the contest, you move the creature up to 30 feet in any direction, including upward but not beyond the range of this glyph. Until the end of your next turn, the creature is restrained in your telekinetic grip. A creature lifted upward is suspended in mid-air. On subsequent rounds, you can spend 2 AP to attempt to maintain your telekinetic grip on the creature by repealing the contest; Object: You can try to move an object that weighs up to 1000 pounds. If the object isn't being worn or carried, you automatically move it up to 30 feet in any direction, but not beyond the range of this glyph. If the object is worn or carried by a creature, you must make an ability check with your spellcasting ability contested by that creature's Strength check. If you succeed, you pull the object away from that creature and can move it up to 30 feet in any direction but not beyond the range of this glyph. You can exert fine control on objects with your telekinetic grip, such as manipulating a simple tool, opening a door or a container, stowing or retrieving an item from an open container, or pouring the contents from a vial.</t>
   </si>
   <si>
     <t>Telepathy</t>
@@ -5052,7 +5052,7 @@
     <t>Thaumaturgy</t>
   </si>
   <si>
-    <t>You manifest a minor wonder, a sign of supernatural power, within range. You create one of the following magical effects within range: Your voice booms up to three times as loud as normal for 1 minute; You cause flames to flicker, brighten, dim, or change color for 1 minute; You cause harmless tremors in the ground for 1 minute; You create an instantaneous sound that originates from a point of your choice within range, such as a rumble of thunder, the cry of a raven, or ominous whispers; You instantaneously cause an unlocked door or window to fly open or slam shut; You alter the appearance of your eyes for 1 minute. If you cast this glyph multiple times, you can have up to three of its 1-minute effects active at a time, and you can dismiss such an effect as an action.</t>
+    <t>You manifest a minor wonder, a sign of supernatural power, within range. You create one of the following magical effects within range: Your voice booms up to three times as loud as normal for 1 minute; You cause flames to flicker, brighten, dim, or change color for 1 minute; You cause harmless tremors in the ground for 1 minute; You create an instantaneous sound that originates from a point of your choice within range, such as a rumble of thunder, the cry of a raven, or ominous whispers; You instantaneously cause an unlocked door or window to fly open or slam shut; You alter the appearance of your eyes for 1 minute. If you cast this glyph multiple times, you can have up to three of its 1-minute effects active at a time, and you can dismiss such an effect by spending 2 AP.</t>
   </si>
   <si>
     <t>Thorn Whip</t>
@@ -5120,7 +5120,7 @@
     <t>Tiny Servant</t>
   </si>
   <si>
-    <t>You touch one Tiny, nonmagical object that isn't attached to another object or a surface and isn't being carried by another creature. The target animates and sprouts little arms and legs, becoming a creature under your control until the glyph ends or the creature drops to 0 hit points. See the stat block for its statistics. As a bonus action, you can mentally command the creature if it is within 120 feet of you (if you control multiple creatures with this glyph, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a simple, general command, such as to fetch a key, stand watch, or stack some books. If you issue no commands, the servant does nothing other than defend itself against hostile creatures. Once given an order, the servant continues to follow that order until its task is complete. When the creature drops to 0 hit points, it reverts to its original form, and any remaining damage carries over to that form.</t>
+    <t>You touch one Tiny, nonmagical object that isn't attached to another object or a surface and isn't being carried by another creature. The target animates and sprouts little arms and legs, becoming a creature under your control until the glyph ends or the creature drops to 0 hit points. See the stat block for its statistics. by spending 1 AP, you can mentally command the creature if it is within 120 feet of you (if you control multiple creatures with this glyph, you can command any or all of them at the same time, issuing the same command to each one). You decide what action the creature will take and where it will move during its next turn, or you can issue a simple, general command, such as to fetch a key, stand watch, or stack some books. If you issue no commands, the servant does nothing other than defend itself against hostile creatures. Once given an order, the servant continues to follow that order until its task is complete. When the creature drops to 0 hit points, it reverts to its original form, and any remaining damage carries over to that form.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 4th level or higher, you can animate two additional objects for each slot level above 3rd.</t>
@@ -5147,7 +5147,7 @@
     <t>Transmute Rock</t>
   </si>
   <si>
-    <t>You choose an area of stone or mud that you can see that fits within a 40-foot cube and is within range, and choose one of the following effects. Transmute Rock to Mud: Nonmagical rock of any sort in the area becomes an equal volume of thick, flowing mud that remains for the glyph's duration. The ground in the glyph's area becomes muddy enough that creatures can sink into it. Each foot that a creature moves through the mud costs 4 feet of movement, and any creature on the ground when you cast the glyph must make a Strength saving throw. A creature must also make the saving throw when it moves into the area for the first time on a turn or ends its turn there. On a failed save, a creature sinks into the mud and is restrained, though it can use an action to end the restrained condition on itself by pulling itself free of the mud. If you cast the glyph on a ceiling, the mud falls. Any creature under the mud when it falls must make a agility saving throw. A creature takes 4d8 bludgeoning damage on a failed save, or half as much damage on a successful one; Transmute Mud to Rock: Nonmagical mud or quicksand in the area no more than 10 feet deep transforms into soft stone for the glyph's duration. Any creature in the mud when it transforms must make a agility saving throw. On a successful save, a creature is shunted safely to the surface in an unoccupied space. On a failed save, a creature becomes restrained by the rock. A restrained creature, or another creature within reach, can use an action to try to break the rock by succeeding on a DC 20 Strength check or by dealing damage to it. The rock has AC 15 and 25 hit points, and it is immune to poison and psychic damage.</t>
+    <t>You choose an area of stone or mud that you can see that fits within a 40-foot cube and is within range, and choose one of the following effects. Transmute Rock to Mud: Nonmagical rock of any sort in the area becomes an equal volume of thick, flowing mud that remains for the glyph's duration. The ground in the glyph's area becomes muddy enough that creatures can sink into it. Each foot that a creature moves through the mud costs 4 feet of movement, and any creature on the ground when you cast the glyph must make a Strength saving throw. A creature must also make the saving throw when it moves into the area for the first time on a turn or ends its turn there. On a failed save, a creature sinks into the mud and is restrained, though it can spend 2 AP to end the restrained condition on itself by pulling itself free of the mud. If you cast the glyph on a ceiling, the mud falls. Any creature under the mud when it falls must make a agility saving throw. A creature takes 4d8 bludgeoning damage on a failed save, or half as much damage on a successful one; Transmute Mud to Rock: Nonmagical mud or quicksand in the area no more than 10 feet deep transforms into soft stone for the glyph's duration. Any creature in the mud when it transforms must make a agility saving throw. On a successful save, a creature is shunted safely to the surface in an unoccupied space. On a failed save, a creature becomes restrained by the rock. A restrained creature, or another creature within reach, can spend 2 AP to try to break the rock by succeeding on a DC 20 Strength check or by dealing damage to it. The rock has AC 15 and 25 hit points, and it is immune to poison and psychic damage.</t>
   </si>
   <si>
     <t>Transport via Plants</t>
@@ -5159,7 +5159,7 @@
     <t>Traverse Dreamspace</t>
   </si>
   <si>
-    <t>You and up to eight willing creatures within range project your dreamspace bodies into the dreamspace Plane (the glyph fails and the casting is wasted if you are already on that plane). The material body you leave behind is unconscious and in a state of suspended animation; it doesn't need food or air and doesn't age. Your dreamspace body resembles your mortal form in almost every way, replicating your game statistics and possessions. The principal difference is the addition of a silvery cord that extends from between your shoulder blades and trails behind you, fading to invisibility after 1 foot. This cord is your tether to your material body. As long as the tether remains intact, you can find your way home. If the cord is cut (something that can happen only when an effect specifically states that it does), your soul and body are separated, killing you instantly. Your dreamspace form can freely travel through the dreamspace Plane and can pass through portals there leading to any other plane. If you enter a new plane or return to the plane you were on when casting this glyph, your body and possessions are transported along the silver cord, allowing you to re-enter your body as you enter the new plane. Your dreamspace form is a separate incarnation. Any damage or other effects that apply to it have no effect on your physical body, nor do they persist when you return to it. The glyph ends for you and your companions when you use your action to dismiss it. When the glyph ends, the affected creature returns to its physical body, and it awakens. The glyph might also end early for you or one of your companions. A successful dispel magic glyph used against an dreamspace or physical body ends the glyph for that creature. If a creature's original body or its dreamspace form drops to 0 hit points, the glyph ends for that creature. If the glyph ends and the silver cord is intact, the cord pulls the creature's dreamspace form back to its body, ending its state of suspended animation. If you are returned to your body prematurely, your companions remain in their dreamspace forms and must find their own way back to their bodies, usually by dropping to 0 hit points.</t>
+    <t>You and up to eight willing creatures within range project your dreamspace bodies into the dreamspace Plane (the glyph fails and the casting is wasted if you are already on that plane). The material body you leave behind is unconscious and in a state of suspended animation; it doesn't need food or air and doesn't age. Your dreamspace body resembles your mortal form in almost every way, replicating your game statistics and possessions. The principal difference is the addition of a silvery cord that extends from between your shoulder blades and trails behind you, fading to invisibility after 1 foot. This cord is your tether to your material body. As long as the tether remains intact, you can find your way home. If the cord is cut (something that can happen only when an effect specifically states that it does), your soul and body are separated, killing you instantly. Your dreamspace form can freely travel through the dreamspace Plane and can pass through portals there leading to any other plane. If you enter a new plane or return to the plane you were on when casting this glyph, your body and possessions are transported along the silver cord, allowing you to re-enter your body as you enter the new plane. Your dreamspace form is a separate incarnation. Any damage or other effects that apply to it have no effect on your physical body, nor do they persist when you return to it. The glyph ends for you and your companions when you spend 2 AP to dismiss it. When the glyph ends, the affected creature returns to its physical body, and it awakens. The glyph might also end early for you or one of your companions. A successful dispel magic glyph used against an dreamspace or physical body ends the glyph for that creature. If a creature's original body or its dreamspace form drops to 0 hit points, the glyph ends for that creature. If the glyph ends and the silver cord is intact, the cord pulls the creature's dreamspace form back to its body, ending its state of suspended animation. If you are returned to your body prematurely, your companions remain in their dreamspace forms and must find their own way back to their bodies, usually by dropping to 0 hit points.</t>
   </si>
   <si>
     <t>Tree Stride</t>
@@ -5255,13 +5255,13 @@
     <t>Unseen Servant</t>
   </si>
   <si>
-    <t>This glyph creates an invisible, mindless, shapeless force that performs simple tasks at your command until the glyph ends. The servant springs into existence in an unoccupied space on the ground within range. It has AC 10, 1 hit point, and a Strength of 2, and it can't attack. If it drops to 0 hit points, the glyph ends. Once on each of your turns as a bonus action, you can mentally command the servant to move up to 15 feet and interact with an object. The servant can perform simple tasks that a human servant could do, such as felching things, cleaning, mending, folding clothes, lighting fires, serving food, and pouring wine. Once you give the command, the servant performs the task to the best of its ability until it completes the task, then waits for your next command. If you command the servant to perform a task that would move it more than 60 feet away from you, the glyph ends.</t>
+    <t>This glyph creates an invisible, mindless, shapeless force that performs simple tasks at your command until the glyph ends. The servant springs into existence in an unoccupied space on the ground within range. It has AC 10, 1 hit point, and a Strength of 2, and it can't attack. If it drops to 0 hit points, the glyph ends. Once on each of your turns by spending 1 AP, you can mentally command the servant to move up to 15 feet and interact with an object. The servant can perform simple tasks that a human servant could do, such as felching things, cleaning, mending, folding clothes, lighting fires, serving food, and pouring wine. Once you give the command, the servant performs the task to the best of its ability until it completes the task, then waits for your next command. If you command the servant to perform a task that would move it more than 60 feet away from you, the glyph ends.</t>
   </si>
   <si>
     <t>Vampiric Touch</t>
   </si>
   <si>
-    <t>The touch of your shadow-wreathed hand can siphon life force from others to heal your wounds. Make a melee glyph attack against a creature within your reach. On a hit, the target takes 3d6 necrotic damage, and you regain hit points equal to half the amount of necrotic damage dealt. Until the glyph ends, you can make the attack again on each of your turns as an action.</t>
+    <t>The touch of your shadow-wreathed hand can siphon life force from others to heal your wounds. Make a melee glyph attack against a creature within your reach. On a hit, the target takes 3d6 necrotic damage, and you regain hit points equal to half the amount of necrotic damage dealt. Until the glyph ends, you can make the attack again on each of your turns by spending 2 AP.</t>
   </si>
   <si>
     <t>Venomous Smite</t>
@@ -5270,7 +5270,7 @@
     <t>You inscribe a toxic glyph of corruption into your weapon, infusing your next strike with putrid arcane venom.
  The next time you hit a creature with a melee weapon attack before the glyph ends, the weapon flares with green energy, and the target takes an additional 1d8 poison damage. If the target is a creature, it must succeed on a Constitution saving throw or become poisoned until the glyph ends.
  This poisoned condition also counts as a magical disease for effects that interact with disease or immunity.
- A creature poisoned in this way can use its action to attempt to purge the infection, making a Constitution check against your glyph save DC. On a success, the glyph is broken, and the poisoned condition ends.</t>
+ A creature poisoned in this way can spend 2 AP to attempt to purge the infection, making a Constitution check against your glyph save DC. On a success, the glyph is broken, and the poisoned condition ends.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a tier 3 or higher, the extra damage increases by 1d8.</t>
@@ -5297,7 +5297,7 @@
     <t>Viserion's Platinum Shield</t>
   </si>
   <si>
-    <t>You create a field of silvery light that surrounds a creature of your choice within range (you can choose yourself). The field sheds dim light out to 5 feet. While surrounded by the field, a creature gains the following benefits: Cover. The creature has half cover; Damage Resistance. The creature has resistance to acid, cold, fire, lightning, and poison damage; Evasion. If the creature is subjected to an effect that allows it to make a agility saving throw to take only half damage, the creature instead takes no damage if it succeeds on the saving throw, and only half damage if it fails. As a bonus action on subsequent turns, you can move the field to another creature within 60 feet of the field.</t>
+    <t>You create a field of silvery light that surrounds a creature of your choice within range (you can choose yourself). The field sheds dim light out to 5 feet. While surrounded by the field, a creature gains the following benefits: Cover. The creature has half cover; Damage Resistance. The creature has resistance to acid, cold, fire, lightning, and poison damage; Evasion. If the creature is subjected to an effect that allows it to make a agility saving throw to take only half damage, the creature instead takes no damage if it succeeds on the saving throw, and only half damage if it fails. by spending 1 AP on subsequent turns, you can move the field to another creature within 60 feet of the field.</t>
   </si>
   <si>
     <t>Vitriolic Sphere</t>
@@ -5340,7 +5340,7 @@
     <t>Waking Dream</t>
   </si>
   <si>
-    <t>You step into the border regions of the Ethereal Plane, in the area where it overlaps with your current plane. You remain in the Border Ethereal for the duration or until you use your action to dismiss the glyph. During this time, you can move in any direction. If you move up or down, every foot of movement costs an extra fool. You can see and hear the plane you originated from, but everything there looks gray, and you can't see anything more than 60 feet away. While on the Ethereal Plane, you can only affect and be affected by other creatures on that plane. Creatures that aren't on the Ethereal Plane can't perceive you and can't interact with you, unless a special ability or magic has given them the ability to do so. You ignore all objects and effects that aren't on the Ethereal Plane, allowing you to move through objects you perceive on the plane you originated from. When the glyph ends, you immediately return to the plane you originated from in the spot you currently occupy. If you occupy the same spot as a solid object or creature when this happens, you are immediately shunted to the nearest unoccupied space that you can occupy and take force damage equal to twice the number of feet you are moved. This glyph has no effect if you cast it while you are on the Ethereal Plane or a plane that doesn't border it, such as one of the Outer Planes.</t>
+    <t>You step into the border regions of the Ethereal Plane, in the area where it overlaps with your current plane. You remain in the Border Ethereal for the duration or until you spend 2 AP to dismiss the glyph. During this time, you can move in any direction. If you move up or down, every foot of movement costs an extra fool. You can see and hear the plane you originated from, but everything there looks gray, and you can't see anything more than 60 feet away. While on the Ethereal Plane, you can only affect and be affected by other creatures on that plane. Creatures that aren't on the Ethereal Plane can't perceive you and can't interact with you, unless a special ability or magic has given them the ability to do so. You ignore all objects and effects that aren't on the Ethereal Plane, allowing you to move through objects you perceive on the plane you originated from. When the glyph ends, you immediately return to the plane you originated from in the spot you currently occupy. If you occupy the same spot as a solid object or creature when this happens, you are immediately shunted to the nearest unoccupied space that you can occupy and take force damage equal to twice the number of feet you are moved. This glyph has no effect if you cast it while you are on the Ethereal Plane or a plane that doesn't border it, such as one of the Outer Planes.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 8th levet or higher, you can target up to three willing crealures (including you) for each slot level above 7th. The creatures must be within 10 feet of you when you cast the Glyph.</t>
@@ -5370,7 +5370,7 @@
     <t>Wall of Light</t>
   </si>
   <si>
-    <t>A shimmering wall of bright Light appears at a point you choose within range. The wall appears in any orientation you choose: horizontally, vertically, or diagonally. It can be free floating, or it can rest on a solid surface. The wall can be up to 60 feet long, 10 feet high, and 5 feet thick. The wall blocks line of sight, but creatures and objects can pass through it. It emits bright light out to 120 feet and dim light for an additional 120 feet. When the wall appears, each creature in its area must make a Constitution saving throw. On a failed save, a creature takes 4d8 radiant damage, and it is blinded for 1 minute. On a successful save, it takes half as much damage and isn't blinded. A blinded creature can make a Constitution saving throw at the end of each of its turns, ending the effect on itself on a success. A creature that ends its turn in the wall's area takes 4d8 radiant damage. Until the glyph ends, you can use an action to launch a beam of radiance from the wall at one creature you can see within 60 feet of it. Make a ranged glyph attack. On a hit, the target takes 4d8 radiant damage. Whether you hit or miss, reduce the length of the wall by 10 feet. If the wall's length drops to 0 feet, the glyph ends.</t>
+    <t>A shimmering wall of bright Light appears at a point you choose within range. The wall appears in any orientation you choose: horizontally, vertically, or diagonally. It can be free floating, or it can rest on a solid surface. The wall can be up to 60 feet long, 10 feet high, and 5 feet thick. The wall blocks line of sight, but creatures and objects can pass through it. It emits bright light out to 120 feet and dim light for an additional 120 feet. When the wall appears, each creature in its area must make a Constitution saving throw. On a failed save, a creature takes 4d8 radiant damage, and it is blinded for 1 minute. On a successful save, it takes half as much damage and isn't blinded. A blinded creature can make a Constitution saving throw at the end of each of its turns, ending the effect on itself on a success. A creature that ends its turn in the wall's area takes 4d8 radiant damage. Until the glyph ends, you can spend 2 AP to launch a beam of radiance from the wall at one creature you can see within 60 feet of it. Make a ranged glyph attack. On a hit, the target takes 4d8 radiant damage. Whether you hit or miss, reduce the length of the wall by 10 feet. If the wall's length drops to 0 feet, the glyph ends.</t>
   </si>
   <si>
     <t>Wall of Sand</t>
@@ -5382,7 +5382,7 @@
     <t>Wall of Stone</t>
   </si>
   <si>
-    <t>A nonmagical wall of solid stone springs into existence at a point you choose within range. The wall is 6 inches thick and is composed of ten 10-foot-by-10-foot panels. Each panel must be contiguous wilh at least one other panel. Alternatively, you can create 10-foot-by-20-foot panels that are only 3 inches thick. If the wall cuts through a creature's space when it appears, the creature is pushed to one side of the wall (your choice). If a creature would be surrounded on all sides by the wall (or the wall and another solid surface), that creature can make a agility saving throw. On a success, it can use 1 AP to move up to its speed so that it is no longer enclosed by the wall. The wall can have any shape you desire, though it can't occupy the same space as a creature or object. The wall doesn't need to be vertical or rest on any firm foundation. It must, however, merge with and be solidly supported by existing stone. Thus, you can use this glyph to bridge a chasm or create a ramp. If you create a span greater than 20 feet in length, you must halve the size of each panel to create supports. You can crudely shape the wall to create crenellations, battlements, and so on. The wall is an object made of stone that can be damaged and thus breached. Each panel has AC 15 and 30 hit points per inch of thickness. Reducing a panel to 0 hit points destroys it and might cause connected panels to collapse at the DM's discretion. If you maintain your concentration on this glyph for its whole duration, the wall becomes permanent and can't be dispelled. Otherwise, the wall disappears when the glyph ends.</t>
+    <t>A nonmagical wall of solid stone springs into existence at a point you choose within range. The wall is 6 inches thick and is composed of ten 10-foot-by-10-foot panels. Each panel must be contiguous wilh at least one other panel. Alternatively, you can create 10-foot-by-20-foot panels that are only 3 inches thick. If the wall cuts through a creature's space when it appears, the creature is pushed to one side of the wall (your choice). If a creature would be surrounded on all sides by the wall (or the wall and another solid surface), that creature can make a agility saving throw. On a success, it can use its reaction to move up to its speed so that it is no longer enclosed by the wall. The wall can have any shape you desire, though it can't occupy the same space as a creature or object. The wall doesn't need to be vertical or rest on any firm foundation. It must, however, merge with and be solidly supported by existing stone. Thus, you can use this glyph to bridge a chasm or create a ramp. If you create a span greater than 20 feet in length, you must halve the size of each panel to create supports. You can crudely shape the wall to create crenellations, battlements, and so on. The wall is an object made of stone that can be damaged and thus breached. Each panel has AC 15 and 30 hit points per inch of thickness. Reducing a panel to 0 hit points destroys it and might cause connected panels to collapse at the DM's discretion. If you maintain your concentration on this glyph for its whole duration, the wall becomes permanent and can't be dispelled. Otherwise, the wall disappears when the glyph ends.</t>
   </si>
   <si>
     <t>Wall of Thorns</t>
@@ -5403,7 +5403,7 @@
     <t>Warding Bond</t>
   </si>
   <si>
-    <t>This glyph wards a willing creature you touch and creates a mystic connection between you and the target until the glyph ends. While the target is within 60 feel of you, it gains a +1 bonus to AC and saving throws, and it has resistance to all damage. Also, each time it takes damage, you take the same amount of damage. The glyph ends if you drop to 0 hit points or if you and the target become separated by more than 60 feet. It also ends if the glyph is cast again on either of the connected creatures. You can also dismiss the glyph as an action.</t>
+    <t>This glyph wards a willing creature you touch and creates a mystic connection between you and the target until the glyph ends. While the target is within 60 feel of you, it gains a +1 bonus to AC and saving throws, and it has resistance to all damage. Also, each time it takes damage, you take the same amount of damage. The glyph ends if you drop to 0 hit points or if you and the target become separated by more than 60 feet. It also ends if the glyph is cast again on either of the connected creatures. You can also dismiss the glyph by spending 2 AP.</t>
   </si>
   <si>
     <t>Warding Wind</t>
@@ -5427,13 +5427,13 @@
     <t>Watery Sphere</t>
   </si>
   <si>
-    <t>You conjure up a sphere of water with a 5-foot radius at a point you can see within range. The sphere can hover but no more than 10 feet off the ground. The sphere remains for the glyph's duration. Any creature in the sphere's space must make a Strength saving throw. On a successful save, a creature is ejected from that space to the nearest unoccupied space of the creature's choice outside the sphere. A Huge or larger creature succeeds on the saving throw automatically, and a Large or smaller creature can choose to fail it. On a failed save, a creature is restrained by the sphere and is engulfed by the water. At the end of each of its turns, a restrained target can repeat the saving throw, ending the effect on itself on a success. The sphere can restrain as many as four Medium or smaller creatures or one Large creature. If the sphere restrains a creature that causes it to exceed this capacity, a random creature that was already restrained by the sphere falls out of it and lands prone in a space within 5 feet of it. As an action, you can move the sphere up to 30 feet in a straight line. If it moves over a pit, a cliff, or other drop-off, it safely descends until it is hovering 10 feet above the ground. Any creature restrained by the sphere moves with it. You can ram the sphere into creatures, forcing them to make the saving throw. When the glyph ends, the sphere falls to the ground and extinguishes all normal flames within 30 feet of it. Any creature restrained by the sphere is knocked prone in the space where it falls. The water then vanishes.</t>
+    <t>You conjure up a sphere of water with a 5-foot radius at a point you can see within range. The sphere can hover but no more than 10 feet off the ground. The sphere remains for the glyph's duration. Any creature in the sphere's space must make a Strength saving throw. On a successful save, a creature is ejected from that space to the nearest unoccupied space of the creature's choice outside the sphere. A Huge or larger creature succeeds on the saving throw automatically, and a Large or smaller creature can choose to fail it. On a failed save, a creature is restrained by the sphere and is engulfed by the water. At the end of each of its turns, a restrained target can repeat the saving throw, ending the effect on itself on a success. The sphere can restrain as many as four Medium or smaller creatures or one Large creature. If the sphere restrains a creature that causes it to exceed this capacity, a random creature that was already restrained by the sphere falls out of it and lands prone in a space within 5 feet of it. by spending 2 AP, you can move the sphere up to 30 feet in a straight line. If it moves over a pit, a cliff, or other drop-off, it safely descends until it is hovering 10 feet above the ground. Any creature restrained by the sphere moves with it. You can ram the sphere into creatures, forcing them to make the saving throw. When the glyph ends, the sphere falls to the ground and extinguishes all normal flames within 30 feet of it. Any creature restrained by the sphere is knocked prone in the space where it falls. The water then vanishes.</t>
   </si>
   <si>
     <t>Web</t>
   </si>
   <si>
-    <t>You conjure a mass of thick, sticky webbing at a point of your choice within range. The webs fill a 20-foot cube from that point for the duration. The webs are difficult terrain and lightly obscure their area. If the webs aren't anchored between two solid masses (such as walls or trees) or layered across a floor, wall, or ceiling, the conjured web collapses on itself, and the glyph ends at the start of your next turn. Webs layered over a flat surface have a depth of 5 feet. Each creature that starts its turn in the webs or that enters them during its turn must make a agility saving throw. On a failed save, the creature is restrained as long as it remains in the webs or until it breaks free. A creature restrained by the webs can use its action to make a Strength check against your glyph save DC. If it succeeds, it is no longer restrained. The webs are flammable. Any 5-foot cube of webs exposed to fire burns away in 1 round, dealing 2d4 fire damage to any creature that starts its turn in the fire.</t>
+    <t>You conjure a mass of thick, sticky webbing at a point of your choice within range. The webs fill a 20-foot cube from that point for the duration. The webs are difficult terrain and lightly obscure their area. If the webs aren't anchored between two solid masses (such as walls or trees) or layered across a floor, wall, or ceiling, the conjured web collapses on itself, and the glyph ends at the start of your next turn. Webs layered over a flat surface have a depth of 5 feet. Each creature that starts its turn in the webs or that enters them during its turn must make a agility saving throw. On a failed save, the creature is restrained as long as it remains in the webs or until it breaks free. A creature restrained by the webs can spend 2 AP to make a Strength check against your glyph save DC. If it succeeds, it is no longer restrained. The webs are flammable. Any 5-foot cube of webs exposed to fire burns away in 1 round, dealing 2d4 fire damage to any creature that starts its turn in the fire.</t>
   </si>
   <si>
     <t>Weird</t>
@@ -5464,7 +5464,7 @@
     <t>Whirlwind</t>
   </si>
   <si>
-    <t>A whirlwind howls down to a point that you can see on the ground within range. The whirlwind is a 10-foot-radius, 30-foot-high cylinder centered on that point. Until the glyph ends, you can use your action to move the whirlwind up to 30 feet in any direction along the ground. The whirlwind sucks up any Medium or smaller objects that aren't secured to anything and that aren't worn or carried by anyone. A creature must make a agility saving throw the first time on a turn that it enters the whirlwind or that the whirlwind enters its space, including when the whirlwind first appears. A creature takes 10d6 bludgeoning damage on a failed save, or half as much damage on a successful one. In addition, a Large or smaller creature that fails the save must succeed on a Strength saving throw or become restrained in the whirlwind until the glyph ends. When a creature starts its turn restrained by the whirlwind, the creature is pulled 5 feet higher inside it, unless the creature is at the top. A restrained creature moves with the whirlwind and falls when the glyph ends, unless the creature has some means to stay aloft. A restrained creature can use an action to make a Strength or agility check against your glyph save DC. If successful, the creature is no longer restrained by the whirlwind and is hurled 3d6 x 10 feet away from it in a random direction.</t>
+    <t>A whirlwind howls down to a point that you can see on the ground within range. The whirlwind is a 10-foot-radius, 30-foot-high cylinder centered on that point. Until the glyph ends, you can spend 2 AP to move the whirlwind up to 30 feet in any direction along the ground. The whirlwind sucks up any Medium or smaller objects that aren't secured to anything and that aren't worn or carried by anyone. A creature must make a agility saving throw the first time on a turn that it enters the whirlwind or that the whirlwind enters its space, including when the whirlwind first appears. A creature takes 10d6 bludgeoning damage on a failed save, or half as much damage on a successful one. In addition, a Large or smaller creature that fails the save must succeed on a Strength saving throw or become restrained in the whirlwind until the glyph ends. When a creature starts its turn restrained by the whirlwind, the creature is pulled 5 feet higher inside it, unless the creature is at the top. A restrained creature moves with the whirlwind and falls when the glyph ends, unless the creature has some means to stay aloft. A restrained creature can spend 2 AP to make a Strength or agility check against your glyph save DC. If successful, the creature is no longer restrained by the whirlwind and is hurled 3d6 x 10 feet away from it in a random direction.</t>
   </si>
   <si>
     <t>Wind Walk</t>
@@ -5482,7 +5482,7 @@
     <t>Witch Bolt</t>
   </si>
   <si>
-    <t>A beam of crackling, blue energy lances out toward a creature within range, forming a sustained are of lightning between you and the target. Make a ranged glyph attack against that creature. On a hit, the target takes 1d12 lightning damage, and on each ofyour turns for the duration, you can use your action to deal 1d12 lightning damage to the target automatically. The glyph ends if you use your action to do anything else. The glyph also ends if the target is ever outside the glyph's range or if it has total cover from you.</t>
+    <t>A beam of crackling, blue energy lances out toward a creature within range, forming a sustained are of lightning between you and the target. Make a ranged glyph attack against that creature. On a hit, the target takes 1d12 lightning damage, and on each ofyour turns for the duration, you can spend 2 AP to deal 1d12 lightning damage to the target automatically. The glyph ends if you spend 2 AP to do anything else. The glyph also ends if the target is ever outside the glyph's range or if it has total cover from you.</t>
   </si>
   <si>
     <t>When you cast this Glyph using a Glyph slot of 2nd level or higher, the initial damage increases by 1d12 for each slot level above 1st.</t>
@@ -5523,19 +5523,19 @@
     <t>Wrath of Nature</t>
   </si>
   <si>
-    <t>You call out to the spirits of nature to rouse them against your enemies. Choose a point you can see within range. The spirits cause trees, rocks, and grasses in a 60-foot cube centered on that point to become animated until the glyph ends. Grasses and Undergrowth: Any area of ground in the cube that is covered by grass or undergrowth is difficult terrain for your enemies; Trees: At the start of each of your turns, each of your enemies within 10 feet of any tree in the cube must succeed on a agility saving throw or take 4d6 slashing damage from whipping branches; Roots and Vines: At the end of each of your turns, one creature of your choice that is on the ground in the cube must succeed on a Strength saving throw or become restrained until the glyph ends. A restrained creature can use an action to make a Strength (Athletics) check against your glyph save DC, ending the effect on itself on a success; Rocks: As a bonus action on your turn, you can cause a loose rock in the cube to launch at a creature you can see in the cube. Make a ranged glyph attack against the target. On a bit, the target takes 3d8 nonmagical bludgeoning damage, and it must succeed on a Strength saving throw or fall prone.</t>
+    <t>You call out to the spirits of nature to rouse them against your enemies. Choose a point you can see within range. The spirits cause trees, rocks, and grasses in a 60-foot cube centered on that point to become animated until the glyph ends. Grasses and Undergrowth: Any area of ground in the cube that is covered by grass or undergrowth is difficult terrain for your enemies; Trees: At the start of each of your turns, each of your enemies within 10 feet of any tree in the cube must succeed on a agility saving throw or take 4d6 slashing damage from whipping branches; Roots and Vines: At the end of each of your turns, one creature of your choice that is on the ground in the cube must succeed on a Strength saving throw or become restrained until the glyph ends. A restrained creature can spend 2 AP to make a Strength (Athletics) check against your glyph save DC, ending the effect on itself on a success; Rocks: by spending 1 AP on your turn, you can cause a loose rock in the cube to launch at a creature you can see in the cube. Make a ranged glyph attack against the target. On a bit, the target takes 3d8 nonmagical bludgeoning damage, and it must succeed on a Strength saving throw or fall prone.</t>
   </si>
   <si>
     <t>Wrathful Smite</t>
   </si>
   <si>
-    <t>The next time you hit with a melee weapon attack during this glyph's duration, your attack deals an extra 1d6 psychic damage. Additionally, if the target is a creature, it must make a wits saving throw or be frightened of you until the glyph ends. As an action, the creature can make a wits check against your glyph save DC to steel its resolve and end this glyph.</t>
+    <t>The next time you hit with a melee weapon attack during this glyph's duration, your attack deals an extra 1d6 psychic damage. Additionally, if the target is a creature, it must make a wits saving throw or be frightened of you until the glyph ends. by spending 2 AP, the creature can make a wits check against your glyph save DC to steel its resolve and end this glyph.</t>
   </si>
   <si>
     <t>Wristpocket</t>
   </si>
   <si>
-    <t>You flick your wrist, causing one object in your hand to vanish. The object, which only you can be holding and can weigh no more than 5 pounds, is transported to an extradimensional space, where it remains for the duration. Until the glyph ends, you can use your action to summon the object to your free hand, and you can use your action to return the object to the extradimensional space. An object still in the pocket plane when the glyph ends appears in your space, at your feet.</t>
+    <t>You flick your wrist, causing one object in your hand to vanish. The object, which only you can be holding and can weigh no more than 5 pounds, is transported to an extradimensional space, where it remains for the duration. Until the glyph ends, you can spend 2 AP to summon the object to your free hand, and you can spend 2 AP to return the object to the extradimensional space. An object still in the pocket plane when the glyph ends appears in your space, at your feet.</t>
   </si>
   <si>
     <t>Zephyr Strike</t>
@@ -8611,7 +8611,7 @@
       <c r="K64" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="L64" s="8" t="s">
+      <c r="L64" s="15" t="s">
         <v>217</v>
       </c>
       <c r="M64" s="8" t="s">
@@ -10279,7 +10279,7 @@
       <c r="K104" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="L104" s="8" t="s">
+      <c r="L104" s="15" t="s">
         <v>325</v>
       </c>
       <c r="M104" s="9"/>
@@ -11977,7 +11977,7 @@
       <c r="K144" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="L144" s="8" t="s">
+      <c r="L144" s="15" t="s">
         <v>430</v>
       </c>
       <c r="M144" s="9"/>
@@ -12381,7 +12381,7 @@
       <c r="K154" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="L154" s="8" t="s">
+      <c r="L154" s="15" t="s">
         <v>457</v>
       </c>
       <c r="M154" s="8" t="s">
@@ -14439,7 +14439,7 @@
       <c r="K203" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="L203" s="13" t="s">
+      <c r="L203" s="12" t="s">
         <v>586</v>
       </c>
       <c r="M203" s="12" t="s">
@@ -14907,7 +14907,7 @@
       <c r="K214" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="L214" s="8" t="s">
+      <c r="L214" s="15" t="s">
         <v>616</v>
       </c>
       <c r="M214" s="9"/>
@@ -19855,7 +19855,7 @@
       <c r="K333" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="L333" s="12" t="s">
+      <c r="L333" s="13" t="s">
         <v>917</v>
       </c>
       <c r="M333" s="14"/>
@@ -28925,7 +28925,7 @@
       <c r="K552" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="L552" s="8" t="s">
+      <c r="L552" s="15" t="s">
         <v>1453</v>
       </c>
       <c r="M552" s="9"/>
@@ -30881,7 +30881,7 @@
       <c r="K599" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="L599" s="12" t="s">
+      <c r="L599" s="13" t="s">
         <v>1565</v>
       </c>
       <c r="M599" s="14"/>

--- a/src/sheet.xlsx
+++ b/src/sheet.xlsx
@@ -5655,28 +5655,28 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -5694,13 +5694,13 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -5709,22 +5709,22 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">

--- a/src/sheet.xlsx
+++ b/src/sheet.xlsx
@@ -195,7 +195,7 @@
     <t>You abandon every restraint placed upon your Wellspring and command the entirety of your life and mana to erupt outward at once.
 When you invoke this Glyph, your Wellspring becomes momentarily uncontainable. Aether tears through your body and bursts forth in a violent wave centered on you.
 Each other creature within a 30-foot radius must make a Wellspring saving throw.
-On a failed save, a creature takes Aetherial damage equal to the sum of your current Hit Points and current Mana Points at the moment the Glyph is invoked. On a successful save, the creature takes half as much damage.
+On a failed save, a creature takes Aetherial damage equal to the sum of your maximum Hit Points and Maximum Mana Points at the moment the Glyph is invoked. On a successful save, the creature takes half as much damage.
 This damage ignores resistance to Aetherial damage. A creature immune to Aetherial damage instead has its immunity treated as resistance against this damage.
 Immediately after the eruption, your maximum Hit Points and maximum Mana Points are each reduced to 1. Your current Hit Points and Mana Points are likewise reduced to 1 if they are higher.
 This reduction cannot be prevented, restored, transferred, or removed by healing, regeneration, restoration magic, or any other effect short of completing a Long Rest. Upon completing a Long Rest, your normal Hit Point and Mana Point maximums are restored.
